--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="F14" t="n">
-        <v>11.14</v>
+        <v>11.48</v>
       </c>
       <c r="G14" t="n">
-        <v>304.7</v>
+        <v>313.4</v>
       </c>
       <c r="H14" t="n">
-        <v>64.59999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-140.27</v>
+        <v>51.3</v>
       </c>
       <c r="K14" t="n">
-        <v>245.02</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>282.33</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:29:21</t>
+          <t>05:29:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="F15" t="n">
-        <v>11.59</v>
+        <v>11.99</v>
       </c>
       <c r="G15" t="n">
-        <v>315.7</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>64.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>148.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>31.79</v>
+        <v>-190.74</v>
       </c>
       <c r="L15" t="n">
-        <v>151.67</v>
+        <v>203.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:31:01</t>
+          <t>05:30:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.93</v>
+        <v>2.54</v>
       </c>
       <c r="F16" t="n">
-        <v>11.21</v>
+        <v>11.71</v>
       </c>
       <c r="G16" t="n">
-        <v>309.3</v>
+        <v>301.3</v>
       </c>
       <c r="H16" t="n">
-        <v>65.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-93.02</v>
+        <v>-80.29000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-103.99</v>
+        <v>-41.97</v>
       </c>
       <c r="L16" t="n">
-        <v>139.52</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:35:33</t>
+          <t>05:36:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="F17" t="n">
-        <v>12.41</v>
+        <v>11.54</v>
       </c>
       <c r="G17" t="n">
-        <v>309.3</v>
+        <v>311</v>
       </c>
       <c r="H17" t="n">
-        <v>66.2</v>
+        <v>63.8</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>256.17</v>
+        <v>-113.52</v>
       </c>
       <c r="K17" t="n">
-        <v>-183.44</v>
+        <v>0.11</v>
       </c>
       <c r="L17" t="n">
-        <v>315.08</v>
+        <v>113.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:37:05</t>
+          <t>05:37:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="F18" t="n">
-        <v>11.02</v>
+        <v>10.92</v>
       </c>
       <c r="G18" t="n">
-        <v>316.8</v>
+        <v>303.7</v>
       </c>
       <c r="H18" t="n">
-        <v>76.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>90.7</v>
+        <v>113.1</v>
       </c>
       <c r="K18" t="n">
-        <v>28.17</v>
+        <v>-123.9</v>
       </c>
       <c r="L18" t="n">
-        <v>94.98</v>
+        <v>167.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:38:47</t>
+          <t>05:39:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.11</v>
+        <v>3.49</v>
       </c>
       <c r="F19" t="n">
-        <v>11.42</v>
+        <v>11.96</v>
       </c>
       <c r="G19" t="n">
-        <v>306.2</v>
+        <v>309</v>
       </c>
       <c r="H19" t="n">
-        <v>67.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-218.23</v>
+        <v>-70.45999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>66.25</v>
+        <v>145.49</v>
       </c>
       <c r="L19" t="n">
-        <v>228.06</v>
+        <v>161.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:43:44</t>
+          <t>05:43:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="F20" t="n">
-        <v>12.19</v>
+        <v>12.12</v>
       </c>
       <c r="G20" t="n">
-        <v>307.2</v>
+        <v>319.1</v>
       </c>
       <c r="H20" t="n">
-        <v>67</v>
+        <v>68.7</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-51.82</v>
+        <v>-323.37</v>
       </c>
       <c r="K20" t="n">
-        <v>-263.93</v>
+        <v>258.24</v>
       </c>
       <c r="L20" t="n">
-        <v>268.97</v>
+        <v>413.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:45:33</t>
+          <t>05:45:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="F21" t="n">
-        <v>12.39</v>
+        <v>12.01</v>
       </c>
       <c r="G21" t="n">
-        <v>306.7</v>
+        <v>308.7</v>
       </c>
       <c r="H21" t="n">
-        <v>68.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-249.79</v>
+        <v>222.35</v>
       </c>
       <c r="K21" t="n">
-        <v>-140.44</v>
+        <v>84.72</v>
       </c>
       <c r="L21" t="n">
-        <v>286.56</v>
+        <v>237.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:48:12</t>
+          <t>05:47:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.09</v>
+        <v>2.78</v>
       </c>
       <c r="F22" t="n">
-        <v>11.09</v>
+        <v>11.85</v>
       </c>
       <c r="G22" t="n">
-        <v>299.7</v>
+        <v>311.5</v>
       </c>
       <c r="H22" t="n">
-        <v>65.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>160.85</v>
+        <v>126.39</v>
       </c>
       <c r="K22" t="n">
-        <v>10.32</v>
+        <v>-88.64</v>
       </c>
       <c r="L22" t="n">
-        <v>161.18</v>
+        <v>154.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:51:17</t>
+          <t>05:52:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.17</v>
+        <v>4.23</v>
       </c>
       <c r="F23" t="n">
-        <v>11.98</v>
+        <v>12.03</v>
       </c>
       <c r="G23" t="n">
-        <v>304.4</v>
+        <v>321.4</v>
       </c>
       <c r="H23" t="n">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-216.91</v>
+        <v>222.8</v>
       </c>
       <c r="K23" t="n">
-        <v>126.15</v>
+        <v>-165.87</v>
       </c>
       <c r="L23" t="n">
-        <v>250.93</v>
+        <v>277.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:53:23</t>
+          <t>05:54:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.02</v>
+        <v>3.39</v>
       </c>
       <c r="F24" t="n">
-        <v>12.38</v>
+        <v>11.84</v>
       </c>
       <c r="G24" t="n">
-        <v>309.6</v>
+        <v>307.7</v>
       </c>
       <c r="H24" t="n">
-        <v>65</v>
+        <v>66.3</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-313.33</v>
+        <v>-320.87</v>
       </c>
       <c r="K24" t="n">
-        <v>218.02</v>
+        <v>342.94</v>
       </c>
       <c r="L24" t="n">
-        <v>381.72</v>
+        <v>469.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:55:16</t>
+          <t>05:56:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="F25" t="n">
-        <v>11.32</v>
+        <v>11.98</v>
       </c>
       <c r="G25" t="n">
-        <v>312.4</v>
+        <v>318.5</v>
       </c>
       <c r="H25" t="n">
-        <v>70.90000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-631.92</v>
+        <v>183.47</v>
       </c>
       <c r="K25" t="n">
-        <v>-263.63</v>
+        <v>675.4299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>684.71</v>
+        <v>699.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:00:43</t>
+          <t>06:01:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.29</v>
+        <v>2.73</v>
       </c>
       <c r="F26" t="n">
-        <v>11.02</v>
+        <v>11.66</v>
       </c>
       <c r="G26" t="n">
-        <v>312.7</v>
+        <v>318.8</v>
       </c>
       <c r="H26" t="n">
-        <v>64.7</v>
+        <v>61.5</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>26.98</v>
+        <v>67.52</v>
       </c>
       <c r="K26" t="n">
-        <v>103.68</v>
+        <v>-221.57</v>
       </c>
       <c r="L26" t="n">
-        <v>107.13</v>
+        <v>231.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:02:30</t>
+          <t>06:03:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.51</v>
+        <v>3.16</v>
       </c>
       <c r="F27" t="n">
-        <v>11.21</v>
+        <v>11.74</v>
       </c>
       <c r="G27" t="n">
-        <v>327.2</v>
+        <v>309.9</v>
       </c>
       <c r="H27" t="n">
-        <v>63.8</v>
+        <v>65.8</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>-547.86</v>
+        <v>198.02</v>
       </c>
       <c r="K27" t="n">
-        <v>994.51</v>
+        <v>-597.54</v>
       </c>
       <c r="L27" t="n">
-        <v>1135.43</v>
+        <v>629.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:03:57</t>
+          <t>06:05:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="F28" t="n">
-        <v>11.87</v>
+        <v>12.5</v>
       </c>
       <c r="G28" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H28" t="n">
-        <v>69.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-299.4</v>
+        <v>824.97</v>
       </c>
       <c r="K28" t="n">
-        <v>-372.78</v>
+        <v>109.77</v>
       </c>
       <c r="L28" t="n">
-        <v>478.13</v>
+        <v>832.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:12:30</t>
+          <t>06:15:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="F29" t="n">
-        <v>11.33</v>
+        <v>12.47</v>
       </c>
       <c r="G29" t="n">
-        <v>320.3</v>
+        <v>313</v>
       </c>
       <c r="H29" t="n">
-        <v>69.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>117.42</v>
+        <v>-22.98</v>
       </c>
       <c r="K29" t="n">
-        <v>-271.53</v>
+        <v>226.09</v>
       </c>
       <c r="L29" t="n">
-        <v>295.83</v>
+        <v>227.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:14:39</t>
+          <t>06:17:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.01</v>
+        <v>3.36</v>
       </c>
       <c r="F30" t="n">
-        <v>11.02</v>
+        <v>11.39</v>
       </c>
       <c r="G30" t="n">
-        <v>321</v>
+        <v>312.4</v>
       </c>
       <c r="H30" t="n">
-        <v>69.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-123.86</v>
+        <v>-206.31</v>
       </c>
       <c r="K30" t="n">
-        <v>-49.98</v>
+        <v>-113.73</v>
       </c>
       <c r="L30" t="n">
-        <v>133.57</v>
+        <v>235.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:15:44</t>
+          <t>06:18:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="F31" t="n">
-        <v>11.64</v>
+        <v>11.36</v>
       </c>
       <c r="G31" t="n">
-        <v>317.1</v>
+        <v>299</v>
       </c>
       <c r="H31" t="n">
-        <v>63.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-77.37</v>
+        <v>156.19</v>
       </c>
       <c r="K31" t="n">
-        <v>-91.78</v>
+        <v>139.73</v>
       </c>
       <c r="L31" t="n">
-        <v>120.04</v>
+        <v>209.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:20:27</t>
+          <t>06:24:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="F32" t="n">
-        <v>11.43</v>
+        <v>11.25</v>
       </c>
       <c r="G32" t="n">
-        <v>315.1</v>
+        <v>305.3</v>
       </c>
       <c r="H32" t="n">
-        <v>60.5</v>
+        <v>73.5</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-123.05</v>
+        <v>-14.52</v>
       </c>
       <c r="K32" t="n">
-        <v>19.17</v>
+        <v>-84.65000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>124.53</v>
+        <v>85.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:21:54</t>
+          <t>06:25:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.08</v>
+        <v>3.39</v>
       </c>
       <c r="F33" t="n">
-        <v>11.62</v>
+        <v>12.08</v>
       </c>
       <c r="G33" t="n">
-        <v>309.7</v>
+        <v>294.9</v>
       </c>
       <c r="H33" t="n">
-        <v>62.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-354.7</v>
+        <v>-162.04</v>
       </c>
       <c r="K33" t="n">
-        <v>-184.16</v>
+        <v>168.85</v>
       </c>
       <c r="L33" t="n">
-        <v>399.66</v>
+        <v>234.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:22:40</t>
+          <t>06:27:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.62</v>
+        <v>4.89</v>
       </c>
       <c r="F34" t="n">
-        <v>12.15</v>
+        <v>11.64</v>
       </c>
       <c r="G34" t="n">
-        <v>316.1</v>
+        <v>309.5</v>
       </c>
       <c r="H34" t="n">
-        <v>67.3</v>
+        <v>65.3</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>217.19</v>
+        <v>413.92</v>
       </c>
       <c r="K34" t="n">
-        <v>-66.91</v>
+        <v>138.79</v>
       </c>
       <c r="L34" t="n">
-        <v>227.26</v>
+        <v>436.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:27:54</t>
+          <t>06:31:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="F35" t="n">
-        <v>11.35</v>
+        <v>10.75</v>
       </c>
       <c r="G35" t="n">
-        <v>297.4</v>
+        <v>301.2</v>
       </c>
       <c r="H35" t="n">
-        <v>66.7</v>
+        <v>57.2</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>162.76</v>
+        <v>-57.51</v>
       </c>
       <c r="K35" t="n">
-        <v>-83.81</v>
+        <v>-362.96</v>
       </c>
       <c r="L35" t="n">
-        <v>183.07</v>
+        <v>367.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:29:03</t>
+          <t>06:33:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="F36" t="n">
-        <v>11.41</v>
+        <v>12.1</v>
       </c>
       <c r="G36" t="n">
-        <v>312.9</v>
+        <v>304.4</v>
       </c>
       <c r="H36" t="n">
-        <v>68.8</v>
+        <v>67.2</v>
       </c>
       <c r="I36" t="n">
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-118.56</v>
+        <v>336.21</v>
       </c>
       <c r="K36" t="n">
-        <v>-274.95</v>
+        <v>-89.77</v>
       </c>
       <c r="L36" t="n">
-        <v>299.42</v>
+        <v>347.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:31:12</t>
+          <t>06:34:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.49</v>
+        <v>4.22</v>
       </c>
       <c r="F37" t="n">
-        <v>11.67</v>
+        <v>11.48</v>
       </c>
       <c r="G37" t="n">
-        <v>327.8</v>
+        <v>296.6</v>
       </c>
       <c r="H37" t="n">
-        <v>68.3</v>
+        <v>77.3</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-205.73</v>
+        <v>-499.35</v>
       </c>
       <c r="K37" t="n">
-        <v>-177.22</v>
+        <v>-522.48</v>
       </c>
       <c r="L37" t="n">
-        <v>271.53</v>
+        <v>722.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:35:32</t>
+          <t>06:38:57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="F38" t="n">
-        <v>12.29</v>
+        <v>11.89</v>
       </c>
       <c r="G38" t="n">
-        <v>319.4</v>
+        <v>318.3</v>
       </c>
       <c r="H38" t="n">
-        <v>60.3</v>
+        <v>66.7</v>
       </c>
       <c r="I38" t="n">
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-576.42</v>
+        <v>371.05</v>
       </c>
       <c r="K38" t="n">
-        <v>-125.55</v>
+        <v>564.64</v>
       </c>
       <c r="L38" t="n">
-        <v>589.9400000000001</v>
+        <v>675.64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:38:12</t>
+          <t>06:41:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="F39" t="n">
-        <v>12.32</v>
+        <v>11.49</v>
       </c>
       <c r="G39" t="n">
-        <v>314.6</v>
+        <v>299.1</v>
       </c>
       <c r="H39" t="n">
-        <v>65.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>186.66</v>
+        <v>379.05</v>
       </c>
       <c r="K39" t="n">
-        <v>-396.54</v>
+        <v>-313.02</v>
       </c>
       <c r="L39" t="n">
-        <v>438.28</v>
+        <v>491.59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:39:42</t>
+          <t>06:43:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.43</v>
+        <v>2.55</v>
       </c>
       <c r="F40" t="n">
-        <v>11.49</v>
+        <v>11.96</v>
       </c>
       <c r="G40" t="n">
-        <v>295.6</v>
+        <v>310.1</v>
       </c>
       <c r="H40" t="n">
-        <v>62.9</v>
+        <v>62.7</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-229.22</v>
+        <v>-155.11</v>
       </c>
       <c r="K40" t="n">
-        <v>-315.82</v>
+        <v>-29.56</v>
       </c>
       <c r="L40" t="n">
-        <v>390.24</v>
+        <v>157.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:43:42</t>
+          <t>06:46:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.58</v>
+        <v>3.77</v>
       </c>
       <c r="F41" t="n">
-        <v>11.86</v>
+        <v>11.08</v>
       </c>
       <c r="G41" t="n">
-        <v>310.6</v>
+        <v>316</v>
       </c>
       <c r="H41" t="n">
-        <v>68.8</v>
+        <v>63.7</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-236.62</v>
+        <v>-147.34</v>
       </c>
       <c r="K41" t="n">
-        <v>-299.36</v>
+        <v>146.87</v>
       </c>
       <c r="L41" t="n">
-        <v>381.58</v>
+        <v>208.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:45:48</t>
+          <t>06:48:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="F42" t="n">
-        <v>11.34</v>
+        <v>11.58</v>
       </c>
       <c r="G42" t="n">
-        <v>315.6</v>
+        <v>313.6</v>
       </c>
       <c r="H42" t="n">
-        <v>68.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>129.11</v>
+        <v>110.24</v>
       </c>
       <c r="K42" t="n">
-        <v>-226.18</v>
+        <v>-256.34</v>
       </c>
       <c r="L42" t="n">
-        <v>260.43</v>
+        <v>279.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:47:32</t>
+          <t>06:49:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="F43" t="n">
-        <v>11.49</v>
+        <v>11.88</v>
       </c>
       <c r="G43" t="n">
-        <v>304.2</v>
+        <v>309.4</v>
       </c>
       <c r="H43" t="n">
-        <v>73.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="I43" t="n">
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>790.51</v>
+        <v>-475.25</v>
       </c>
       <c r="K43" t="n">
-        <v>728.78</v>
+        <v>-227.21</v>
       </c>
       <c r="L43" t="n">
-        <v>1075.19</v>
+        <v>526.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:01:06</t>
+          <t>07:01:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.84</v>
+        <v>2.97</v>
       </c>
       <c r="F44" t="n">
-        <v>12.36</v>
+        <v>11.54</v>
       </c>
       <c r="G44" t="n">
-        <v>307.7</v>
+        <v>307.3</v>
       </c>
       <c r="H44" t="n">
-        <v>69.7</v>
+        <v>68.2</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-42.37</v>
+        <v>-28.23</v>
       </c>
       <c r="K44" t="n">
-        <v>54.19</v>
+        <v>-182.24</v>
       </c>
       <c r="L44" t="n">
-        <v>68.78</v>
+        <v>184.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:02:18</t>
+          <t>07:02:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="F45" t="n">
-        <v>12.25</v>
+        <v>11.94</v>
       </c>
       <c r="G45" t="n">
-        <v>317.5</v>
+        <v>318</v>
       </c>
       <c r="H45" t="n">
-        <v>68</v>
+        <v>63.2</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-30.97</v>
+        <v>347.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-179.19</v>
+        <v>-328.49</v>
       </c>
       <c r="L45" t="n">
-        <v>181.85</v>
+        <v>478.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:04:11</t>
+          <t>07:03:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.84</v>
+        <v>3.95</v>
       </c>
       <c r="F46" t="n">
-        <v>11.37</v>
+        <v>11.99</v>
       </c>
       <c r="G46" t="n">
-        <v>315.9</v>
+        <v>317.4</v>
       </c>
       <c r="H46" t="n">
-        <v>65.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I46" t="n">
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>183.62</v>
+        <v>-101.28</v>
       </c>
       <c r="K46" t="n">
-        <v>101.38</v>
+        <v>-162.64</v>
       </c>
       <c r="L46" t="n">
-        <v>209.75</v>
+        <v>191.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:08:20</t>
+          <t>07:09:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.14</v>
+        <v>3.98</v>
       </c>
       <c r="F47" t="n">
-        <v>11.02</v>
+        <v>11.62</v>
       </c>
       <c r="G47" t="n">
-        <v>308.6</v>
+        <v>308.2</v>
       </c>
       <c r="H47" t="n">
-        <v>64.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-67.19</v>
+        <v>-284.57</v>
       </c>
       <c r="K47" t="n">
-        <v>-56.59</v>
+        <v>170.08</v>
       </c>
       <c r="L47" t="n">
-        <v>87.84</v>
+        <v>331.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:10:42</t>
+          <t>07:11:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.18</v>
+        <v>2.89</v>
       </c>
       <c r="F48" t="n">
-        <v>12.28</v>
+        <v>11.87</v>
       </c>
       <c r="G48" t="n">
-        <v>318.2</v>
+        <v>303</v>
       </c>
       <c r="H48" t="n">
-        <v>69.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>98.31</v>
+        <v>-69.13</v>
       </c>
       <c r="K48" t="n">
-        <v>289.16</v>
+        <v>-35.38</v>
       </c>
       <c r="L48" t="n">
-        <v>305.42</v>
+        <v>77.65000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:13:26</t>
+          <t>07:13:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.83</v>
+        <v>3.07</v>
       </c>
       <c r="F49" t="n">
-        <v>11.57</v>
+        <v>11.39</v>
       </c>
       <c r="G49" t="n">
-        <v>304.5</v>
+        <v>314.4</v>
       </c>
       <c r="H49" t="n">
-        <v>65.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-83.55</v>
+        <v>-40.11</v>
       </c>
       <c r="K49" t="n">
-        <v>-230.4</v>
+        <v>-363.75</v>
       </c>
       <c r="L49" t="n">
-        <v>245.08</v>
+        <v>365.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:17:37</t>
+          <t>07:16:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="F50" t="n">
-        <v>11.41</v>
+        <v>11.65</v>
       </c>
       <c r="G50" t="n">
-        <v>316.8</v>
+        <v>316.4</v>
       </c>
       <c r="H50" t="n">
-        <v>64</v>
+        <v>59.5</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-104.39</v>
+        <v>144.35</v>
       </c>
       <c r="K50" t="n">
-        <v>-572.75</v>
+        <v>-371.16</v>
       </c>
       <c r="L50" t="n">
-        <v>582.1900000000001</v>
+        <v>398.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:18:52</t>
+          <t>07:18:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="F51" t="n">
-        <v>11.95</v>
+        <v>11.47</v>
       </c>
       <c r="G51" t="n">
         <v>315</v>
       </c>
       <c r="H51" t="n">
-        <v>66.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-54.95</v>
+        <v>40.57</v>
       </c>
       <c r="K51" t="n">
-        <v>349.46</v>
+        <v>332.48</v>
       </c>
       <c r="L51" t="n">
-        <v>353.76</v>
+        <v>334.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:21:14</t>
+          <t>07:20:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.79</v>
+        <v>3.73</v>
       </c>
       <c r="F52" t="n">
-        <v>12.36</v>
+        <v>11.43</v>
       </c>
       <c r="G52" t="n">
-        <v>316.6</v>
+        <v>316.1</v>
       </c>
       <c r="H52" t="n">
-        <v>70.3</v>
+        <v>64</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>97.23</v>
+        <v>163.12</v>
       </c>
       <c r="K52" t="n">
-        <v>-26.5</v>
+        <v>-137.4</v>
       </c>
       <c r="L52" t="n">
-        <v>100.78</v>
+        <v>213.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:25:32</t>
+          <t>07:25:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="F53" t="n">
-        <v>11.78</v>
+        <v>12.22</v>
       </c>
       <c r="G53" t="n">
-        <v>310.5</v>
+        <v>316.5</v>
       </c>
       <c r="H53" t="n">
-        <v>64.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I53" t="n">
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>230.56</v>
+        <v>161.48</v>
       </c>
       <c r="K53" t="n">
-        <v>373.13</v>
+        <v>-148.6</v>
       </c>
       <c r="L53" t="n">
-        <v>438.61</v>
+        <v>219.45</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:26:17</t>
+          <t>07:27:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.72</v>
+        <v>3.46</v>
       </c>
       <c r="F54" t="n">
-        <v>11.56</v>
+        <v>11.37</v>
       </c>
       <c r="G54" t="n">
-        <v>311</v>
+        <v>314.8</v>
       </c>
       <c r="H54" t="n">
-        <v>70.2</v>
+        <v>66.2</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-305.28</v>
+        <v>52.46</v>
       </c>
       <c r="K54" t="n">
-        <v>-354.27</v>
+        <v>111.02</v>
       </c>
       <c r="L54" t="n">
-        <v>467.66</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:27:19</t>
+          <t>07:28:54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="F55" t="n">
-        <v>11.63</v>
+        <v>11.8</v>
       </c>
       <c r="G55" t="n">
-        <v>307.5</v>
+        <v>318</v>
       </c>
       <c r="H55" t="n">
-        <v>70.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-318.93</v>
+        <v>-234.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-422.87</v>
+        <v>-73.12</v>
       </c>
       <c r="L55" t="n">
-        <v>529.66</v>
+        <v>245.46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:32:29</t>
+          <t>07:34:34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.92</v>
+        <v>3.65</v>
       </c>
       <c r="F56" t="n">
-        <v>11.45</v>
+        <v>11.53</v>
       </c>
       <c r="G56" t="n">
-        <v>309.4</v>
+        <v>319.4</v>
       </c>
       <c r="H56" t="n">
-        <v>64</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>519.3099999999999</v>
+        <v>-757.1900000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-561.96</v>
+        <v>144.29</v>
       </c>
       <c r="L56" t="n">
-        <v>765.17</v>
+        <v>770.8200000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:34:46</t>
+          <t>07:36:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="F57" t="n">
-        <v>11.69</v>
+        <v>11.38</v>
       </c>
       <c r="G57" t="n">
-        <v>325.6</v>
+        <v>304.7</v>
       </c>
       <c r="H57" t="n">
-        <v>60.8</v>
+        <v>66.7</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>308.58</v>
+        <v>516.91</v>
       </c>
       <c r="K57" t="n">
-        <v>309.5</v>
+        <v>231.87</v>
       </c>
       <c r="L57" t="n">
-        <v>437.05</v>
+        <v>566.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:35:56</t>
+          <t>07:38:41</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="F58" t="n">
-        <v>11.39</v>
+        <v>11.91</v>
       </c>
       <c r="G58" t="n">
-        <v>316.4</v>
+        <v>305.5</v>
       </c>
       <c r="H58" t="n">
-        <v>75.40000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>186.29</v>
+        <v>-756.65</v>
       </c>
       <c r="K58" t="n">
-        <v>-402.24</v>
+        <v>-438.52</v>
       </c>
       <c r="L58" t="n">
-        <v>443.28</v>
+        <v>874.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:44:07</t>
+          <t>07:47:22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.66</v>
+        <v>4.04</v>
       </c>
       <c r="F59" t="n">
-        <v>11.17</v>
+        <v>11.59</v>
       </c>
       <c r="G59" t="n">
-        <v>299.4</v>
+        <v>314.2</v>
       </c>
       <c r="H59" t="n">
-        <v>70.3</v>
+        <v>63.6</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-121.33</v>
+        <v>-89.56</v>
       </c>
       <c r="K59" t="n">
-        <v>84.06</v>
+        <v>94.2</v>
       </c>
       <c r="L59" t="n">
-        <v>147.6</v>
+        <v>129.98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:46:20</t>
+          <t>07:48:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.69</v>
+        <v>3.45</v>
       </c>
       <c r="F60" t="n">
-        <v>10.99</v>
+        <v>11.81</v>
       </c>
       <c r="G60" t="n">
-        <v>302.4</v>
+        <v>311.4</v>
       </c>
       <c r="H60" t="n">
-        <v>67.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>94.65000000000001</v>
+        <v>-30.98</v>
       </c>
       <c r="K60" t="n">
-        <v>-101.45</v>
+        <v>45.4</v>
       </c>
       <c r="L60" t="n">
-        <v>138.74</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:47:48</t>
+          <t>07:50:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.03</v>
+        <v>3.85</v>
       </c>
       <c r="F61" t="n">
-        <v>12.27</v>
+        <v>11.17</v>
       </c>
       <c r="G61" t="n">
-        <v>298.3</v>
+        <v>316.6</v>
       </c>
       <c r="H61" t="n">
-        <v>73.7</v>
+        <v>68</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>127.29</v>
+        <v>-115.31</v>
       </c>
       <c r="K61" t="n">
-        <v>-158.22</v>
+        <v>-29.04</v>
       </c>
       <c r="L61" t="n">
-        <v>203.07</v>
+        <v>118.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:52:27</t>
+          <t>07:56:45</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="F62" t="n">
-        <v>11.95</v>
+        <v>11.25</v>
       </c>
       <c r="G62" t="n">
-        <v>306.8</v>
+        <v>292.4</v>
       </c>
       <c r="H62" t="n">
-        <v>72.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>68.33</v>
+        <v>-239.2</v>
       </c>
       <c r="K62" t="n">
-        <v>-37.85</v>
+        <v>130.38</v>
       </c>
       <c r="L62" t="n">
-        <v>78.11</v>
+        <v>272.43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:54:52</t>
+          <t>07:57:58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
       <c r="F63" t="n">
-        <v>11.94</v>
+        <v>11.62</v>
       </c>
       <c r="G63" t="n">
-        <v>302</v>
+        <v>305.9</v>
       </c>
       <c r="H63" t="n">
-        <v>72</v>
+        <v>69.3</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>131.53</v>
+        <v>-21.15</v>
       </c>
       <c r="K63" t="n">
-        <v>-114.8</v>
+        <v>164.45</v>
       </c>
       <c r="L63" t="n">
-        <v>174.58</v>
+        <v>165.81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:56:42</t>
+          <t>07:58:53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="F64" t="n">
-        <v>12.27</v>
+        <v>11.74</v>
       </c>
       <c r="G64" t="n">
-        <v>312.4</v>
+        <v>319.6</v>
       </c>
       <c r="H64" t="n">
-        <v>59.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-48.6</v>
+        <v>-69.44</v>
       </c>
       <c r="K64" t="n">
-        <v>278.06</v>
+        <v>-24.34</v>
       </c>
       <c r="L64" t="n">
-        <v>282.28</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:00:56</t>
+          <t>08:02:51</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.15</v>
+        <v>3.69</v>
       </c>
       <c r="F65" t="n">
-        <v>11.58</v>
+        <v>11.74</v>
       </c>
       <c r="G65" t="n">
-        <v>319.8</v>
+        <v>303.2</v>
       </c>
       <c r="H65" t="n">
-        <v>65.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>356.82</v>
+        <v>197.68</v>
       </c>
       <c r="K65" t="n">
-        <v>-295.39</v>
+        <v>117.24</v>
       </c>
       <c r="L65" t="n">
-        <v>463.22</v>
+        <v>229.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:02:51</t>
+          <t>08:05:20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.72</v>
+        <v>4.17</v>
       </c>
       <c r="F66" t="n">
-        <v>12.02</v>
+        <v>11.68</v>
       </c>
       <c r="G66" t="n">
-        <v>309.6</v>
+        <v>308.4</v>
       </c>
       <c r="H66" t="n">
-        <v>71.3</v>
+        <v>63.7</v>
       </c>
       <c r="I66" t="n">
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-173.75</v>
+        <v>144.94</v>
       </c>
       <c r="K66" t="n">
-        <v>61.48</v>
+        <v>273.47</v>
       </c>
       <c r="L66" t="n">
-        <v>184.31</v>
+        <v>309.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:04:45</t>
+          <t>08:06:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.85</v>
+        <v>3.06</v>
       </c>
       <c r="F67" t="n">
-        <v>11.41</v>
+        <v>12.41</v>
       </c>
       <c r="G67" t="n">
-        <v>314.6</v>
+        <v>310.4</v>
       </c>
       <c r="H67" t="n">
-        <v>70</v>
+        <v>67.3</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-52.94</v>
+        <v>190.67</v>
       </c>
       <c r="K67" t="n">
-        <v>220.68</v>
+        <v>-198.5</v>
       </c>
       <c r="L67" t="n">
-        <v>226.94</v>
+        <v>275.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:08:41</t>
+          <t>08:12:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="F68" t="n">
-        <v>12.14</v>
+        <v>11.55</v>
       </c>
       <c r="G68" t="n">
-        <v>304.7</v>
+        <v>303.9</v>
       </c>
       <c r="H68" t="n">
-        <v>75.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-97.3</v>
+        <v>-434.07</v>
       </c>
       <c r="K68" t="n">
-        <v>105.66</v>
+        <v>128.06</v>
       </c>
       <c r="L68" t="n">
-        <v>143.63</v>
+        <v>452.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:10:14</t>
+          <t>08:13:25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.43</v>
+        <v>3.78</v>
       </c>
       <c r="F69" t="n">
-        <v>11.31</v>
+        <v>11.54</v>
       </c>
       <c r="G69" t="n">
-        <v>307.9</v>
+        <v>310.6</v>
       </c>
       <c r="H69" t="n">
-        <v>72.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>366.46</v>
+        <v>-538.59</v>
       </c>
       <c r="K69" t="n">
-        <v>-20.19</v>
+        <v>-175.3</v>
       </c>
       <c r="L69" t="n">
-        <v>367.02</v>
+        <v>566.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:12:33</t>
+          <t>08:15:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="F70" t="n">
-        <v>11.42</v>
+        <v>11.37</v>
       </c>
       <c r="G70" t="n">
-        <v>302.5</v>
+        <v>302</v>
       </c>
       <c r="H70" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-481.76</v>
+        <v>-761.51</v>
       </c>
       <c r="K70" t="n">
-        <v>-197.35</v>
+        <v>-139.47</v>
       </c>
       <c r="L70" t="n">
-        <v>520.62</v>
+        <v>774.1799999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:18:48</t>
+          <t>08:21:07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.98</v>
+        <v>3.91</v>
       </c>
       <c r="F71" t="n">
-        <v>11.02</v>
+        <v>11.84</v>
       </c>
       <c r="G71" t="n">
-        <v>303.5</v>
+        <v>294.2</v>
       </c>
       <c r="H71" t="n">
-        <v>76.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-284.54</v>
+        <v>-23.06</v>
       </c>
       <c r="K71" t="n">
-        <v>-84.81</v>
+        <v>-1024</v>
       </c>
       <c r="L71" t="n">
-        <v>296.91</v>
+        <v>1024.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:19:50</t>
+          <t>08:23:50</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="F72" t="n">
-        <v>11.44</v>
+        <v>11.68</v>
       </c>
       <c r="G72" t="n">
-        <v>320.3</v>
+        <v>309.2</v>
       </c>
       <c r="H72" t="n">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>499.31</v>
+        <v>-216.67</v>
       </c>
       <c r="K72" t="n">
-        <v>-45.32</v>
+        <v>366.6</v>
       </c>
       <c r="L72" t="n">
-        <v>501.36</v>
+        <v>425.84</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:21:00</t>
+          <t>08:25:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="F73" t="n">
-        <v>12.03</v>
+        <v>11.19</v>
       </c>
       <c r="G73" t="n">
-        <v>313.1</v>
+        <v>308.6</v>
       </c>
       <c r="H73" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="I73" t="n">
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>765.76</v>
+        <v>-116.1</v>
       </c>
       <c r="K73" t="n">
-        <v>-387.02</v>
+        <v>-341.65</v>
       </c>
       <c r="L73" t="n">
-        <v>858</v>
+        <v>360.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:30:57</t>
+          <t>08:35:38</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="F74" t="n">
-        <v>11.83</v>
+        <v>11.34</v>
       </c>
       <c r="G74" t="n">
-        <v>307.9</v>
+        <v>318.4</v>
       </c>
       <c r="H74" t="n">
-        <v>65.59999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-28.29</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-103.26</v>
+        <v>-309.83</v>
       </c>
       <c r="L74" t="n">
-        <v>107.07</v>
+        <v>319.68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:33:02</t>
+          <t>08:37:44</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.46</v>
+        <v>4.42</v>
       </c>
       <c r="F75" t="n">
-        <v>11.21</v>
+        <v>10.81</v>
       </c>
       <c r="G75" t="n">
-        <v>309.8</v>
+        <v>299.9</v>
       </c>
       <c r="H75" t="n">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.98</v>
+        <v>-276.37</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3</v>
+        <v>268.63</v>
       </c>
       <c r="L75" t="n">
-        <v>78.98</v>
+        <v>385.41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:33:56</t>
+          <t>08:39:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="F76" t="n">
-        <v>12.15</v>
+        <v>11.4</v>
       </c>
       <c r="G76" t="n">
-        <v>310</v>
+        <v>329.2</v>
       </c>
       <c r="H76" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>67.23999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="K76" t="n">
-        <v>22.67</v>
+        <v>-110.66</v>
       </c>
       <c r="L76" t="n">
-        <v>70.95999999999999</v>
+        <v>145.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:38:48</t>
+          <t>08:42:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="F77" t="n">
-        <v>11.77</v>
+        <v>10.96</v>
       </c>
       <c r="G77" t="n">
-        <v>320.8</v>
+        <v>327.4</v>
       </c>
       <c r="H77" t="n">
-        <v>69.5</v>
+        <v>75</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-107.92</v>
+        <v>-158.04</v>
       </c>
       <c r="K77" t="n">
-        <v>-29.32</v>
+        <v>-141.98</v>
       </c>
       <c r="L77" t="n">
-        <v>111.83</v>
+        <v>212.45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:40:07</t>
+          <t>08:44:14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.28</v>
+        <v>3.58</v>
       </c>
       <c r="F78" t="n">
-        <v>11.62</v>
+        <v>12.26</v>
       </c>
       <c r="G78" t="n">
-        <v>302.6</v>
+        <v>292.2</v>
       </c>
       <c r="H78" t="n">
-        <v>64.3</v>
+        <v>63.2</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-416.3</v>
+        <v>-18.94</v>
       </c>
       <c r="K78" t="n">
-        <v>127.94</v>
+        <v>-174.79</v>
       </c>
       <c r="L78" t="n">
-        <v>435.52</v>
+        <v>175.81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:41:23</t>
+          <t>08:46:24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="F79" t="n">
-        <v>11.42</v>
+        <v>11.55</v>
       </c>
       <c r="G79" t="n">
-        <v>319.4</v>
+        <v>315.1</v>
       </c>
       <c r="H79" t="n">
-        <v>65.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>-122.29</v>
+        <v>16.89</v>
       </c>
       <c r="K79" t="n">
-        <v>-152.63</v>
+        <v>130.07</v>
       </c>
       <c r="L79" t="n">
-        <v>195.58</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:45:53</t>
+          <t>08:49:46</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="F80" t="n">
-        <v>11.65</v>
+        <v>12.3</v>
       </c>
       <c r="G80" t="n">
-        <v>332.3</v>
+        <v>318.4</v>
       </c>
       <c r="H80" t="n">
-        <v>67.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-115.64</v>
+        <v>250.33</v>
       </c>
       <c r="K80" t="n">
-        <v>4.99</v>
+        <v>-392.81</v>
       </c>
       <c r="L80" t="n">
-        <v>115.75</v>
+        <v>465.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:46:51</t>
+          <t>08:51:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.44</v>
+        <v>4.18</v>
       </c>
       <c r="F81" t="n">
-        <v>11.75</v>
+        <v>11.68</v>
       </c>
       <c r="G81" t="n">
         <v>312.6</v>
       </c>
       <c r="H81" t="n">
-        <v>63.1</v>
+        <v>73.5</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>320.89</v>
+        <v>-149.32</v>
       </c>
       <c r="K81" t="n">
-        <v>53.79</v>
+        <v>326.35</v>
       </c>
       <c r="L81" t="n">
-        <v>325.36</v>
+        <v>358.89</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:47:31</t>
+          <t>08:53:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.24</v>
+        <v>3.79</v>
       </c>
       <c r="F82" t="n">
-        <v>12.18</v>
+        <v>11.72</v>
       </c>
       <c r="G82" t="n">
-        <v>312</v>
+        <v>317.9</v>
       </c>
       <c r="H82" t="n">
-        <v>72.2</v>
+        <v>71.2</v>
       </c>
       <c r="I82" t="n">
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-374.3</v>
+        <v>-309.57</v>
       </c>
       <c r="K82" t="n">
-        <v>-256.97</v>
+        <v>-181.31</v>
       </c>
       <c r="L82" t="n">
-        <v>454.02</v>
+        <v>358.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:54:03</t>
+          <t>08:58:40</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.03</v>
+        <v>3.91</v>
       </c>
       <c r="F83" t="n">
-        <v>11.5</v>
+        <v>11.98</v>
       </c>
       <c r="G83" t="n">
-        <v>300.5</v>
+        <v>321.5</v>
       </c>
       <c r="H83" t="n">
-        <v>66.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-64.78</v>
+        <v>-597.58</v>
       </c>
       <c r="K83" t="n">
-        <v>-131.13</v>
+        <v>-237.67</v>
       </c>
       <c r="L83" t="n">
-        <v>146.26</v>
+        <v>643.11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:55:30</t>
+          <t>09:00:18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.19</v>
+        <v>4.36</v>
       </c>
       <c r="F84" t="n">
-        <v>11.98</v>
+        <v>11.89</v>
       </c>
       <c r="G84" t="n">
-        <v>313.1</v>
+        <v>306.2</v>
       </c>
       <c r="H84" t="n">
-        <v>69.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>103.07</v>
+        <v>307.06</v>
       </c>
       <c r="K84" t="n">
-        <v>88.08</v>
+        <v>-404.31</v>
       </c>
       <c r="L84" t="n">
-        <v>135.58</v>
+        <v>507.69</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:57:56</t>
+          <t>09:02:09</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.72</v>
+        <v>3.11</v>
       </c>
       <c r="F85" t="n">
-        <v>10.98</v>
+        <v>11.95</v>
       </c>
       <c r="G85" t="n">
-        <v>302.8</v>
+        <v>296.2</v>
       </c>
       <c r="H85" t="n">
-        <v>69.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-316.19</v>
+        <v>-90.92</v>
       </c>
       <c r="K85" t="n">
-        <v>-47.94</v>
+        <v>282.88</v>
       </c>
       <c r="L85" t="n">
-        <v>319.8</v>
+        <v>297.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:03:26</t>
+          <t>09:07:44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.21</v>
+        <v>4.3</v>
       </c>
       <c r="F86" t="n">
-        <v>11.37</v>
+        <v>12.37</v>
       </c>
       <c r="G86" t="n">
-        <v>309.2</v>
+        <v>302</v>
       </c>
       <c r="H86" t="n">
-        <v>64.59999999999999</v>
+        <v>59</v>
       </c>
       <c r="I86" t="n">
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-113.27</v>
+        <v>-49.85</v>
       </c>
       <c r="K86" t="n">
-        <v>-566.77</v>
+        <v>-387.17</v>
       </c>
       <c r="L86" t="n">
-        <v>577.97</v>
+        <v>390.36</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:04:11</t>
+          <t>09:09:18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.94</v>
+        <v>3.63</v>
       </c>
       <c r="F87" t="n">
-        <v>11.97</v>
+        <v>11.95</v>
       </c>
       <c r="G87" t="n">
-        <v>293.4</v>
+        <v>315.6</v>
       </c>
       <c r="H87" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-250.26</v>
+        <v>-568.84</v>
       </c>
       <c r="K87" t="n">
-        <v>638.95</v>
+        <v>-553.1799999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>686.21</v>
+        <v>793.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:06:32</t>
+          <t>09:10:25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.74</v>
+        <v>4.36</v>
       </c>
       <c r="F88" t="n">
-        <v>11.76</v>
+        <v>11.8</v>
       </c>
       <c r="G88" t="n">
-        <v>315.6</v>
+        <v>312.9</v>
       </c>
       <c r="H88" t="n">
-        <v>71.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I88" t="n">
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>489.15</v>
+        <v>286.68</v>
       </c>
       <c r="K88" t="n">
-        <v>645.48</v>
+        <v>-329.81</v>
       </c>
       <c r="L88" t="n">
-        <v>809.89</v>
+        <v>436.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>51.3</v>
+        <v>57.58</v>
       </c>
       <c r="K14" t="n">
-        <v>84.29000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>98.68000000000001</v>
+        <v>110.74</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>69.59999999999999</v>
+        <v>69.69</v>
       </c>
       <c r="K15" t="n">
-        <v>-190.74</v>
+        <v>-190.98</v>
       </c>
       <c r="L15" t="n">
-        <v>203.04</v>
+        <v>203.29</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-80.29000000000001</v>
+        <v>-97.67</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.97</v>
+        <v>-51.06</v>
       </c>
       <c r="L16" t="n">
-        <v>90.59999999999999</v>
+        <v>110.21</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-113.52</v>
+        <v>-182.17</v>
       </c>
       <c r="K17" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="L17" t="n">
-        <v>113.52</v>
+        <v>182.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>113.1</v>
+        <v>136.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-123.9</v>
+        <v>-149.21</v>
       </c>
       <c r="L18" t="n">
-        <v>167.76</v>
+        <v>202.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-70.45999999999999</v>
+        <v>-99.25</v>
       </c>
       <c r="K19" t="n">
-        <v>145.49</v>
+        <v>204.94</v>
       </c>
       <c r="L19" t="n">
-        <v>161.65</v>
+        <v>227.71</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-323.37</v>
+        <v>-387.71</v>
       </c>
       <c r="K20" t="n">
-        <v>258.24</v>
+        <v>309.62</v>
       </c>
       <c r="L20" t="n">
-        <v>413.83</v>
+        <v>496.16</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>222.35</v>
+        <v>315.02</v>
       </c>
       <c r="K21" t="n">
-        <v>84.72</v>
+        <v>120.02</v>
       </c>
       <c r="L21" t="n">
-        <v>237.94</v>
+        <v>337.11</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>126.39</v>
+        <v>197.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-88.64</v>
+        <v>-138.84</v>
       </c>
       <c r="L22" t="n">
-        <v>154.37</v>
+        <v>241.81</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>222.8</v>
+        <v>430.04</v>
       </c>
       <c r="K23" t="n">
-        <v>-165.87</v>
+        <v>-320.15</v>
       </c>
       <c r="L23" t="n">
-        <v>277.76</v>
+        <v>536.13</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-320.87</v>
+        <v>-439.82</v>
       </c>
       <c r="K24" t="n">
-        <v>342.94</v>
+        <v>470.08</v>
       </c>
       <c r="L24" t="n">
-        <v>469.64</v>
+        <v>643.75</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>183.47</v>
+        <v>226.58</v>
       </c>
       <c r="K25" t="n">
-        <v>675.4299999999999</v>
+        <v>834.15</v>
       </c>
       <c r="L25" t="n">
-        <v>699.91</v>
+        <v>864.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>67.52</v>
+        <v>133.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-221.57</v>
+        <v>-437.93</v>
       </c>
       <c r="L26" t="n">
-        <v>231.63</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>198.02</v>
+        <v>270.53</v>
       </c>
       <c r="K27" t="n">
-        <v>-597.54</v>
+        <v>-816.35</v>
       </c>
       <c r="L27" t="n">
-        <v>629.49</v>
+        <v>860.01</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>824.97</v>
+        <v>1156.21</v>
       </c>
       <c r="K28" t="n">
-        <v>109.77</v>
+        <v>153.84</v>
       </c>
       <c r="L28" t="n">
-        <v>832.24</v>
+        <v>1166.4</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-22.98</v>
+        <v>-26.08</v>
       </c>
       <c r="K29" t="n">
-        <v>226.09</v>
+        <v>256.58</v>
       </c>
       <c r="L29" t="n">
-        <v>227.26</v>
+        <v>257.9</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-206.31</v>
+        <v>-225.87</v>
       </c>
       <c r="K30" t="n">
-        <v>-113.73</v>
+        <v>-124.51</v>
       </c>
       <c r="L30" t="n">
-        <v>235.58</v>
+        <v>257.91</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>156.19</v>
+        <v>176.8</v>
       </c>
       <c r="K31" t="n">
-        <v>139.73</v>
+        <v>158.16</v>
       </c>
       <c r="L31" t="n">
-        <v>209.57</v>
+        <v>237.22</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-14.52</v>
+        <v>-23.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-84.65000000000001</v>
+        <v>-135.98</v>
       </c>
       <c r="L32" t="n">
-        <v>85.88</v>
+        <v>137.97</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-162.04</v>
+        <v>-192.5</v>
       </c>
       <c r="K33" t="n">
-        <v>168.85</v>
+        <v>200.59</v>
       </c>
       <c r="L33" t="n">
-        <v>234.03</v>
+        <v>278.01</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>413.92</v>
+        <v>480.84</v>
       </c>
       <c r="K34" t="n">
-        <v>138.79</v>
+        <v>161.23</v>
       </c>
       <c r="L34" t="n">
-        <v>436.57</v>
+        <v>507.15</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-57.51</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-362.96</v>
+        <v>-444.33</v>
       </c>
       <c r="L35" t="n">
-        <v>367.49</v>
+        <v>449.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>336.21</v>
+        <v>391.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-89.77</v>
+        <v>-104.45</v>
       </c>
       <c r="L36" t="n">
-        <v>347.99</v>
+        <v>404.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-499.35</v>
+        <v>-566.2</v>
       </c>
       <c r="K37" t="n">
-        <v>-522.48</v>
+        <v>-592.4299999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>722.73</v>
+        <v>819.49</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>371.05</v>
+        <v>477.32</v>
       </c>
       <c r="K38" t="n">
-        <v>564.64</v>
+        <v>726.36</v>
       </c>
       <c r="L38" t="n">
-        <v>675.64</v>
+        <v>869.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>379.05</v>
+        <v>469.05</v>
       </c>
       <c r="K39" t="n">
-        <v>-313.02</v>
+        <v>-387.34</v>
       </c>
       <c r="L39" t="n">
-        <v>491.59</v>
+        <v>608.3099999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-155.11</v>
+        <v>-271.84</v>
       </c>
       <c r="K40" t="n">
-        <v>-29.56</v>
+        <v>-51.81</v>
       </c>
       <c r="L40" t="n">
-        <v>157.9</v>
+        <v>276.73</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-147.34</v>
+        <v>-375.71</v>
       </c>
       <c r="K41" t="n">
-        <v>146.87</v>
+        <v>374.51</v>
       </c>
       <c r="L41" t="n">
-        <v>208.03</v>
+        <v>530.49</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>110.24</v>
+        <v>239.38</v>
       </c>
       <c r="K42" t="n">
-        <v>-256.34</v>
+        <v>-556.61</v>
       </c>
       <c r="L42" t="n">
-        <v>279.04</v>
+        <v>605.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-475.25</v>
+        <v>-781.9400000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-227.21</v>
+        <v>-373.83</v>
       </c>
       <c r="L43" t="n">
-        <v>526.77</v>
+        <v>866.7</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-28.23</v>
+        <v>-28.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-182.24</v>
+        <v>-182.33</v>
       </c>
       <c r="L44" t="n">
-        <v>184.42</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>347.58</v>
+        <v>360.3</v>
       </c>
       <c r="K45" t="n">
-        <v>-328.49</v>
+        <v>-340.51</v>
       </c>
       <c r="L45" t="n">
-        <v>478.25</v>
+        <v>495.75</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-101.28</v>
+        <v>-133.83</v>
       </c>
       <c r="K46" t="n">
-        <v>-162.64</v>
+        <v>-214.91</v>
       </c>
       <c r="L46" t="n">
-        <v>191.59</v>
+        <v>253.17</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-284.57</v>
+        <v>-319.71</v>
       </c>
       <c r="K47" t="n">
-        <v>170.08</v>
+        <v>191.08</v>
       </c>
       <c r="L47" t="n">
-        <v>331.52</v>
+        <v>372.45</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.13</v>
+        <v>-119.64</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.38</v>
+        <v>-61.23</v>
       </c>
       <c r="L48" t="n">
-        <v>77.65000000000001</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.11</v>
+        <v>-39.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-363.75</v>
+        <v>-358.07</v>
       </c>
       <c r="L49" t="n">
-        <v>365.96</v>
+        <v>360.24</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>144.35</v>
+        <v>170.44</v>
       </c>
       <c r="K50" t="n">
-        <v>-371.16</v>
+        <v>-438.24</v>
       </c>
       <c r="L50" t="n">
-        <v>398.24</v>
+        <v>470.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>40.57</v>
+        <v>49.67</v>
       </c>
       <c r="K51" t="n">
-        <v>332.48</v>
+        <v>407.09</v>
       </c>
       <c r="L51" t="n">
-        <v>334.95</v>
+        <v>410.11</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>163.12</v>
+        <v>270.72</v>
       </c>
       <c r="K52" t="n">
-        <v>-137.4</v>
+        <v>-228.02</v>
       </c>
       <c r="L52" t="n">
-        <v>213.28</v>
+        <v>353.95</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>161.48</v>
+        <v>289.76</v>
       </c>
       <c r="K53" t="n">
-        <v>-148.6</v>
+        <v>-266.65</v>
       </c>
       <c r="L53" t="n">
-        <v>219.45</v>
+        <v>393.77</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>52.46</v>
+        <v>140.46</v>
       </c>
       <c r="K54" t="n">
-        <v>111.02</v>
+        <v>297.25</v>
       </c>
       <c r="L54" t="n">
-        <v>122.79</v>
+        <v>328.76</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-234.31</v>
+        <v>-418.04</v>
       </c>
       <c r="K55" t="n">
-        <v>-73.12</v>
+        <v>-130.45</v>
       </c>
       <c r="L55" t="n">
-        <v>245.46</v>
+        <v>437.92</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-757.1900000000001</v>
+        <v>-1036.7</v>
       </c>
       <c r="K56" t="n">
-        <v>144.29</v>
+        <v>197.56</v>
       </c>
       <c r="L56" t="n">
-        <v>770.8200000000001</v>
+        <v>1055.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>516.91</v>
+        <v>745.99</v>
       </c>
       <c r="K57" t="n">
-        <v>231.87</v>
+        <v>334.64</v>
       </c>
       <c r="L57" t="n">
-        <v>566.53</v>
+        <v>817.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-756.65</v>
+        <v>-997.15</v>
       </c>
       <c r="K58" t="n">
-        <v>-438.52</v>
+        <v>-577.91</v>
       </c>
       <c r="L58" t="n">
-        <v>874.54</v>
+        <v>1152.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-89.56</v>
+        <v>-134.37</v>
       </c>
       <c r="K59" t="n">
-        <v>94.2</v>
+        <v>141.31</v>
       </c>
       <c r="L59" t="n">
-        <v>129.98</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.98</v>
+        <v>-68.92</v>
       </c>
       <c r="K60" t="n">
-        <v>45.4</v>
+        <v>101.02</v>
       </c>
       <c r="L60" t="n">
-        <v>54.96</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-115.31</v>
+        <v>-168.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.04</v>
+        <v>-42.52</v>
       </c>
       <c r="L61" t="n">
-        <v>118.91</v>
+        <v>174.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-239.2</v>
+        <v>-226.78</v>
       </c>
       <c r="K62" t="n">
-        <v>130.38</v>
+        <v>123.61</v>
       </c>
       <c r="L62" t="n">
-        <v>272.43</v>
+        <v>258.28</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-21.15</v>
+        <v>-31.11</v>
       </c>
       <c r="K63" t="n">
-        <v>164.45</v>
+        <v>241.93</v>
       </c>
       <c r="L63" t="n">
-        <v>165.81</v>
+        <v>243.92</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-69.44</v>
+        <v>-156.76</v>
       </c>
       <c r="K64" t="n">
-        <v>-24.34</v>
+        <v>-54.96</v>
       </c>
       <c r="L64" t="n">
-        <v>73.58</v>
+        <v>166.12</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>197.68</v>
+        <v>298.31</v>
       </c>
       <c r="K65" t="n">
-        <v>117.24</v>
+        <v>176.93</v>
       </c>
       <c r="L65" t="n">
-        <v>229.84</v>
+        <v>346.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>144.94</v>
+        <v>203.32</v>
       </c>
       <c r="K66" t="n">
-        <v>273.47</v>
+        <v>383.63</v>
       </c>
       <c r="L66" t="n">
-        <v>309.51</v>
+        <v>434.18</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>190.67</v>
+        <v>231.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-198.5</v>
+        <v>-241.43</v>
       </c>
       <c r="L67" t="n">
-        <v>275.24</v>
+        <v>334.77</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-434.07</v>
+        <v>-594.35</v>
       </c>
       <c r="K68" t="n">
-        <v>128.06</v>
+        <v>175.35</v>
       </c>
       <c r="L68" t="n">
-        <v>452.57</v>
+        <v>619.67</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-538.59</v>
+        <v>-741.96</v>
       </c>
       <c r="K69" t="n">
-        <v>-175.3</v>
+        <v>-241.49</v>
       </c>
       <c r="L69" t="n">
-        <v>566.4</v>
+        <v>780.27</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-761.51</v>
+        <v>-983.55</v>
       </c>
       <c r="K70" t="n">
-        <v>-139.47</v>
+        <v>-180.14</v>
       </c>
       <c r="L70" t="n">
-        <v>774.1799999999999</v>
+        <v>999.91</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-23.06</v>
+        <v>-30.71</v>
       </c>
       <c r="K71" t="n">
-        <v>-1024</v>
+        <v>-1363.8</v>
       </c>
       <c r="L71" t="n">
-        <v>1024.26</v>
+        <v>1364.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-216.67</v>
+        <v>-374.51</v>
       </c>
       <c r="K72" t="n">
-        <v>366.6</v>
+        <v>633.6799999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>425.84</v>
+        <v>736.0700000000001</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-116.1</v>
+        <v>-210.4</v>
       </c>
       <c r="K73" t="n">
-        <v>-341.65</v>
+        <v>-619.14</v>
       </c>
       <c r="L73" t="n">
-        <v>360.83</v>
+        <v>653.91</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-78.73999999999999</v>
+        <v>-86.15000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-309.83</v>
+        <v>-339.01</v>
       </c>
       <c r="L74" t="n">
-        <v>319.68</v>
+        <v>349.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-276.37</v>
+        <v>-314.32</v>
       </c>
       <c r="K75" t="n">
-        <v>268.63</v>
+        <v>305.52</v>
       </c>
       <c r="L75" t="n">
-        <v>385.41</v>
+        <v>438.34</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>95.2</v>
+        <v>128.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-110.66</v>
+        <v>-149.83</v>
       </c>
       <c r="L76" t="n">
-        <v>145.98</v>
+        <v>197.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-158.04</v>
+        <v>-180.18</v>
       </c>
       <c r="K77" t="n">
-        <v>-141.98</v>
+        <v>-161.86</v>
       </c>
       <c r="L77" t="n">
-        <v>212.45</v>
+        <v>242.2</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-18.94</v>
+        <v>-25.9</v>
       </c>
       <c r="K78" t="n">
-        <v>-174.79</v>
+        <v>-239.04</v>
       </c>
       <c r="L78" t="n">
-        <v>175.81</v>
+        <v>240.44</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>16.89</v>
+        <v>28.04</v>
       </c>
       <c r="K79" t="n">
-        <v>130.07</v>
+        <v>215.93</v>
       </c>
       <c r="L79" t="n">
-        <v>131.16</v>
+        <v>217.74</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>250.33</v>
+        <v>315.58</v>
       </c>
       <c r="K80" t="n">
-        <v>-392.81</v>
+        <v>-495.21</v>
       </c>
       <c r="L80" t="n">
-        <v>465.8</v>
+        <v>587.22</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-149.32</v>
+        <v>-212.16</v>
       </c>
       <c r="K81" t="n">
-        <v>326.35</v>
+        <v>463.7</v>
       </c>
       <c r="L81" t="n">
-        <v>358.89</v>
+        <v>509.93</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-309.57</v>
+        <v>-417.07</v>
       </c>
       <c r="K82" t="n">
-        <v>-181.31</v>
+        <v>-244.26</v>
       </c>
       <c r="L82" t="n">
-        <v>358.76</v>
+        <v>483.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-597.58</v>
+        <v>-806.42</v>
       </c>
       <c r="K83" t="n">
-        <v>-237.67</v>
+        <v>-320.73</v>
       </c>
       <c r="L83" t="n">
-        <v>643.11</v>
+        <v>867.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>307.06</v>
+        <v>474.37</v>
       </c>
       <c r="K84" t="n">
-        <v>-404.31</v>
+        <v>-624.62</v>
       </c>
       <c r="L84" t="n">
-        <v>507.69</v>
+        <v>784.33</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-90.92</v>
+        <v>-137.16</v>
       </c>
       <c r="K85" t="n">
-        <v>282.88</v>
+        <v>426.74</v>
       </c>
       <c r="L85" t="n">
-        <v>297.13</v>
+        <v>448.24</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-49.85</v>
+        <v>-96.59</v>
       </c>
       <c r="K86" t="n">
-        <v>-387.17</v>
+        <v>-750.15</v>
       </c>
       <c r="L86" t="n">
-        <v>390.36</v>
+        <v>756.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-568.84</v>
+        <v>-783.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-553.1799999999999</v>
+        <v>-761.46</v>
       </c>
       <c r="L87" t="n">
-        <v>793.46</v>
+        <v>1092.22</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>286.68</v>
+        <v>531.88</v>
       </c>
       <c r="K88" t="n">
-        <v>-329.81</v>
+        <v>-611.91</v>
       </c>
       <c r="L88" t="n">
-        <v>436.99</v>
+        <v>810.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>57.58</v>
+        <v>40.76</v>
       </c>
       <c r="K14" t="n">
-        <v>94.59999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="L14" t="n">
-        <v>110.74</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>69.69</v>
+        <v>46.52</v>
       </c>
       <c r="K15" t="n">
-        <v>-190.98</v>
+        <v>-127.47</v>
       </c>
       <c r="L15" t="n">
-        <v>203.29</v>
+        <v>135.7</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-97.67</v>
+        <v>-68.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.06</v>
+        <v>-35.58</v>
       </c>
       <c r="L16" t="n">
-        <v>110.21</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-182.17</v>
+        <v>-112.05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="L17" t="n">
-        <v>182.17</v>
+        <v>112.05</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>136.21</v>
+        <v>85.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-149.21</v>
+        <v>-93.53</v>
       </c>
       <c r="L18" t="n">
-        <v>202.03</v>
+        <v>126.64</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-99.25</v>
+        <v>-59.49</v>
       </c>
       <c r="K19" t="n">
-        <v>204.94</v>
+        <v>122.84</v>
       </c>
       <c r="L19" t="n">
-        <v>227.71</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-387.71</v>
+        <v>-204.44</v>
       </c>
       <c r="K20" t="n">
-        <v>309.62</v>
+        <v>163.27</v>
       </c>
       <c r="L20" t="n">
-        <v>496.16</v>
+        <v>261.64</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>315.02</v>
+        <v>167.64</v>
       </c>
       <c r="K21" t="n">
-        <v>120.02</v>
+        <v>63.87</v>
       </c>
       <c r="L21" t="n">
-        <v>337.11</v>
+        <v>179.39</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>197.98</v>
+        <v>108.64</v>
       </c>
       <c r="K22" t="n">
-        <v>-138.84</v>
+        <v>-76.19</v>
       </c>
       <c r="L22" t="n">
-        <v>241.81</v>
+        <v>132.69</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>430.04</v>
+        <v>195.85</v>
       </c>
       <c r="K23" t="n">
-        <v>-320.15</v>
+        <v>-145.81</v>
       </c>
       <c r="L23" t="n">
-        <v>536.13</v>
+        <v>244.17</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-439.82</v>
+        <v>-203.92</v>
       </c>
       <c r="K24" t="n">
-        <v>470.08</v>
+        <v>217.95</v>
       </c>
       <c r="L24" t="n">
-        <v>643.75</v>
+        <v>298.47</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>226.58</v>
+        <v>104.68</v>
       </c>
       <c r="K25" t="n">
-        <v>834.15</v>
+        <v>385.37</v>
       </c>
       <c r="L25" t="n">
-        <v>864.37</v>
+        <v>399.34</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>133.44</v>
+        <v>58.72</v>
       </c>
       <c r="K26" t="n">
-        <v>-437.93</v>
+        <v>-192.7</v>
       </c>
       <c r="L26" t="n">
-        <v>457.81</v>
+        <v>201.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>270.53</v>
+        <v>118.66</v>
       </c>
       <c r="K27" t="n">
-        <v>-816.35</v>
+        <v>-358.08</v>
       </c>
       <c r="L27" t="n">
-        <v>860.01</v>
+        <v>377.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>1156.21</v>
+        <v>481.6</v>
       </c>
       <c r="K28" t="n">
-        <v>153.84</v>
+        <v>64.08</v>
       </c>
       <c r="L28" t="n">
-        <v>1166.4</v>
+        <v>485.84</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.08</v>
+        <v>-16.41</v>
       </c>
       <c r="K29" t="n">
-        <v>256.58</v>
+        <v>161.45</v>
       </c>
       <c r="L29" t="n">
-        <v>257.9</v>
+        <v>162.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-225.87</v>
+        <v>-143.34</v>
       </c>
       <c r="K30" t="n">
-        <v>-124.51</v>
+        <v>-79.01000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>257.91</v>
+        <v>163.68</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>176.8</v>
+        <v>114.06</v>
       </c>
       <c r="K31" t="n">
-        <v>158.16</v>
+        <v>102.04</v>
       </c>
       <c r="L31" t="n">
-        <v>237.22</v>
+        <v>153.04</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-23.32</v>
+        <v>-15.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-135.98</v>
+        <v>-89.77</v>
       </c>
       <c r="L32" t="n">
-        <v>137.97</v>
+        <v>91.09</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-192.5</v>
+        <v>-116.25</v>
       </c>
       <c r="K33" t="n">
-        <v>200.59</v>
+        <v>121.13</v>
       </c>
       <c r="L33" t="n">
-        <v>278.01</v>
+        <v>167.89</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>480.84</v>
+        <v>293.04</v>
       </c>
       <c r="K34" t="n">
-        <v>161.23</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>507.15</v>
+        <v>309.08</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-70.40000000000001</v>
+        <v>-37.27</v>
       </c>
       <c r="K35" t="n">
-        <v>-444.33</v>
+        <v>-235.24</v>
       </c>
       <c r="L35" t="n">
-        <v>449.87</v>
+        <v>238.18</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>391.22</v>
+        <v>218.86</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.45</v>
+        <v>-58.43</v>
       </c>
       <c r="L36" t="n">
-        <v>404.92</v>
+        <v>226.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-566.2</v>
+        <v>-299.28</v>
       </c>
       <c r="K37" t="n">
-        <v>-592.4299999999999</v>
+        <v>-313.14</v>
       </c>
       <c r="L37" t="n">
-        <v>819.49</v>
+        <v>433.16</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>477.32</v>
+        <v>217.98</v>
       </c>
       <c r="K38" t="n">
-        <v>726.36</v>
+        <v>331.71</v>
       </c>
       <c r="L38" t="n">
-        <v>869.15</v>
+        <v>396.92</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>469.05</v>
+        <v>223.85</v>
       </c>
       <c r="K39" t="n">
-        <v>-387.34</v>
+        <v>-184.86</v>
       </c>
       <c r="L39" t="n">
-        <v>608.3099999999999</v>
+        <v>290.32</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-271.84</v>
+        <v>-134.8</v>
       </c>
       <c r="K40" t="n">
-        <v>-51.81</v>
+        <v>-25.69</v>
       </c>
       <c r="L40" t="n">
-        <v>276.73</v>
+        <v>137.23</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-375.71</v>
+        <v>-156.95</v>
       </c>
       <c r="K41" t="n">
-        <v>374.51</v>
+        <v>156.45</v>
       </c>
       <c r="L41" t="n">
-        <v>530.49</v>
+        <v>221.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>239.38</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-556.61</v>
+        <v>-232.1</v>
       </c>
       <c r="L42" t="n">
-        <v>605.9</v>
+        <v>252.65</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-781.9400000000001</v>
+        <v>-324.68</v>
       </c>
       <c r="K43" t="n">
-        <v>-373.83</v>
+        <v>-155.22</v>
       </c>
       <c r="L43" t="n">
-        <v>866.7</v>
+        <v>359.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-28.25</v>
+        <v>-19.97</v>
       </c>
       <c r="K44" t="n">
-        <v>-182.33</v>
+        <v>-128.88</v>
       </c>
       <c r="L44" t="n">
-        <v>184.5</v>
+        <v>130.42</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>360.3</v>
+        <v>219.4</v>
       </c>
       <c r="K45" t="n">
-        <v>-340.51</v>
+        <v>-207.35</v>
       </c>
       <c r="L45" t="n">
-        <v>495.75</v>
+        <v>301.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-133.83</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-214.91</v>
+        <v>-131.57</v>
       </c>
       <c r="L46" t="n">
-        <v>253.17</v>
+        <v>154.99</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-319.71</v>
+        <v>-199.97</v>
       </c>
       <c r="K47" t="n">
-        <v>191.08</v>
+        <v>119.51</v>
       </c>
       <c r="L47" t="n">
-        <v>372.45</v>
+        <v>232.96</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-119.64</v>
+        <v>-75.06</v>
       </c>
       <c r="K48" t="n">
-        <v>-61.23</v>
+        <v>-38.41</v>
       </c>
       <c r="L48" t="n">
-        <v>134.4</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-39.48</v>
+        <v>-24.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-358.07</v>
+        <v>-221.49</v>
       </c>
       <c r="L49" t="n">
-        <v>360.24</v>
+        <v>222.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>170.44</v>
+        <v>90.7</v>
       </c>
       <c r="K50" t="n">
-        <v>-438.24</v>
+        <v>-233.21</v>
       </c>
       <c r="L50" t="n">
-        <v>470.22</v>
+        <v>250.23</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>49.67</v>
+        <v>26.6</v>
       </c>
       <c r="K51" t="n">
-        <v>407.09</v>
+        <v>217.97</v>
       </c>
       <c r="L51" t="n">
-        <v>410.11</v>
+        <v>219.59</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>270.72</v>
+        <v>139.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-228.02</v>
+        <v>-117.36</v>
       </c>
       <c r="L52" t="n">
-        <v>353.95</v>
+        <v>182.18</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>289.76</v>
+        <v>135.99</v>
       </c>
       <c r="K53" t="n">
-        <v>-266.65</v>
+        <v>-125.14</v>
       </c>
       <c r="L53" t="n">
-        <v>393.77</v>
+        <v>184.81</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>140.46</v>
+        <v>64.86</v>
       </c>
       <c r="K54" t="n">
-        <v>297.25</v>
+        <v>137.25</v>
       </c>
       <c r="L54" t="n">
-        <v>328.76</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-418.04</v>
+        <v>-193.59</v>
       </c>
       <c r="K55" t="n">
-        <v>-130.45</v>
+        <v>-60.41</v>
       </c>
       <c r="L55" t="n">
-        <v>437.92</v>
+        <v>202.8</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-1036.7</v>
+        <v>-445.09</v>
       </c>
       <c r="K56" t="n">
-        <v>197.56</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>1055.36</v>
+        <v>453.1</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>745.99</v>
+        <v>336.38</v>
       </c>
       <c r="K57" t="n">
-        <v>334.64</v>
+        <v>150.89</v>
       </c>
       <c r="L57" t="n">
-        <v>817.61</v>
+        <v>368.68</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-997.15</v>
+        <v>-435.78</v>
       </c>
       <c r="K58" t="n">
-        <v>-577.91</v>
+        <v>-252.56</v>
       </c>
       <c r="L58" t="n">
-        <v>1152.51</v>
+        <v>503.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-134.37</v>
+        <v>-85.83</v>
       </c>
       <c r="K59" t="n">
-        <v>141.31</v>
+        <v>90.27</v>
       </c>
       <c r="L59" t="n">
-        <v>195</v>
+        <v>124.57</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-68.92</v>
+        <v>-43.46</v>
       </c>
       <c r="K60" t="n">
-        <v>101.02</v>
+        <v>63.7</v>
       </c>
       <c r="L60" t="n">
-        <v>122.3</v>
+        <v>77.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-168.86</v>
+        <v>-111.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-42.52</v>
+        <v>-28.13</v>
       </c>
       <c r="L61" t="n">
-        <v>174.13</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-226.78</v>
+        <v>-153.46</v>
       </c>
       <c r="K62" t="n">
-        <v>123.61</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>258.28</v>
+        <v>174.78</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-31.11</v>
+        <v>-18.34</v>
       </c>
       <c r="K63" t="n">
-        <v>241.93</v>
+        <v>142.57</v>
       </c>
       <c r="L63" t="n">
-        <v>243.92</v>
+        <v>143.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-156.76</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-54.96</v>
+        <v>-32.43</v>
       </c>
       <c r="L64" t="n">
-        <v>166.12</v>
+        <v>98.01000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>298.31</v>
+        <v>161.23</v>
       </c>
       <c r="K65" t="n">
-        <v>176.93</v>
+        <v>95.62</v>
       </c>
       <c r="L65" t="n">
-        <v>346.83</v>
+        <v>187.45</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>203.32</v>
+        <v>110.44</v>
       </c>
       <c r="K66" t="n">
-        <v>383.63</v>
+        <v>208.38</v>
       </c>
       <c r="L66" t="n">
-        <v>434.18</v>
+        <v>235.83</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>231.91</v>
+        <v>133.49</v>
       </c>
       <c r="K67" t="n">
-        <v>-241.43</v>
+        <v>-138.97</v>
       </c>
       <c r="L67" t="n">
-        <v>334.77</v>
+        <v>192.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-594.35</v>
+        <v>-276.42</v>
       </c>
       <c r="K68" t="n">
-        <v>175.35</v>
+        <v>81.55</v>
       </c>
       <c r="L68" t="n">
-        <v>619.67</v>
+        <v>288.19</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-741.96</v>
+        <v>-336.8</v>
       </c>
       <c r="K69" t="n">
-        <v>-241.49</v>
+        <v>-109.62</v>
       </c>
       <c r="L69" t="n">
-        <v>780.27</v>
+        <v>354.19</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-983.55</v>
+        <v>-443.54</v>
       </c>
       <c r="K70" t="n">
-        <v>-180.14</v>
+        <v>-81.23</v>
       </c>
       <c r="L70" t="n">
-        <v>999.91</v>
+        <v>450.91</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-30.71</v>
+        <v>-12.77</v>
       </c>
       <c r="K71" t="n">
-        <v>-1363.8</v>
+        <v>-566.87</v>
       </c>
       <c r="L71" t="n">
-        <v>1364.14</v>
+        <v>567.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-374.51</v>
+        <v>-157.15</v>
       </c>
       <c r="K72" t="n">
-        <v>633.6799999999999</v>
+        <v>265.9</v>
       </c>
       <c r="L72" t="n">
-        <v>736.0700000000001</v>
+        <v>308.87</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-210.4</v>
+        <v>-88.92</v>
       </c>
       <c r="K73" t="n">
-        <v>-619.14</v>
+        <v>-261.67</v>
       </c>
       <c r="L73" t="n">
-        <v>653.91</v>
+        <v>276.37</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-86.15000000000001</v>
+        <v>-54.88</v>
       </c>
       <c r="K74" t="n">
-        <v>-339.01</v>
+        <v>-215.95</v>
       </c>
       <c r="L74" t="n">
-        <v>349.78</v>
+        <v>222.82</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-314.32</v>
+        <v>-188.47</v>
       </c>
       <c r="K75" t="n">
-        <v>305.52</v>
+        <v>183.2</v>
       </c>
       <c r="L75" t="n">
-        <v>438.34</v>
+        <v>262.84</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>128.9</v>
+        <v>84.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-149.83</v>
+        <v>-98.5</v>
       </c>
       <c r="L76" t="n">
-        <v>197.64</v>
+        <v>129.94</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-180.18</v>
+        <v>-116.88</v>
       </c>
       <c r="K77" t="n">
-        <v>-161.86</v>
+        <v>-105</v>
       </c>
       <c r="L77" t="n">
-        <v>242.2</v>
+        <v>157.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-25.9</v>
+        <v>-15.43</v>
       </c>
       <c r="K78" t="n">
-        <v>-239.04</v>
+        <v>-142.39</v>
       </c>
       <c r="L78" t="n">
-        <v>240.44</v>
+        <v>143.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>28.04</v>
+        <v>17.32</v>
       </c>
       <c r="K79" t="n">
-        <v>215.93</v>
+        <v>133.34</v>
       </c>
       <c r="L79" t="n">
-        <v>217.74</v>
+        <v>134.46</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>315.58</v>
+        <v>161.34</v>
       </c>
       <c r="K80" t="n">
-        <v>-495.21</v>
+        <v>-253.18</v>
       </c>
       <c r="L80" t="n">
-        <v>587.22</v>
+        <v>300.21</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-212.16</v>
+        <v>-107.16</v>
       </c>
       <c r="K81" t="n">
-        <v>463.7</v>
+        <v>234.2</v>
       </c>
       <c r="L81" t="n">
-        <v>509.93</v>
+        <v>257.55</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-417.07</v>
+        <v>-214.08</v>
       </c>
       <c r="K82" t="n">
-        <v>-244.26</v>
+        <v>-125.38</v>
       </c>
       <c r="L82" t="n">
-        <v>483.33</v>
+        <v>248.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-806.42</v>
+        <v>-363.82</v>
       </c>
       <c r="K83" t="n">
-        <v>-320.73</v>
+        <v>-144.7</v>
       </c>
       <c r="L83" t="n">
-        <v>867.86</v>
+        <v>391.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>474.37</v>
+        <v>210.12</v>
       </c>
       <c r="K84" t="n">
-        <v>-624.62</v>
+        <v>-276.67</v>
       </c>
       <c r="L84" t="n">
-        <v>784.33</v>
+        <v>347.41</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-137.16</v>
+        <v>-64.78</v>
       </c>
       <c r="K85" t="n">
-        <v>426.74</v>
+        <v>201.54</v>
       </c>
       <c r="L85" t="n">
-        <v>448.24</v>
+        <v>211.69</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-96.59</v>
+        <v>-39.64</v>
       </c>
       <c r="K86" t="n">
-        <v>-750.15</v>
+        <v>-307.88</v>
       </c>
       <c r="L86" t="n">
-        <v>756.34</v>
+        <v>310.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-783.02</v>
+        <v>-328.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-761.46</v>
+        <v>-319.77</v>
       </c>
       <c r="L87" t="n">
-        <v>1092.22</v>
+        <v>458.67</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>531.88</v>
+        <v>217.91</v>
       </c>
       <c r="K88" t="n">
-        <v>-611.91</v>
+        <v>-250.69</v>
       </c>
       <c r="L88" t="n">
-        <v>810.77</v>
+        <v>332.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>40.76</v>
+        <v>42.25</v>
       </c>
       <c r="K14" t="n">
-        <v>66.97</v>
+        <v>69.42</v>
       </c>
       <c r="L14" t="n">
-        <v>78.40000000000001</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>46.52</v>
+        <v>48.82</v>
       </c>
       <c r="K15" t="n">
-        <v>-127.47</v>
+        <v>-133.77</v>
       </c>
       <c r="L15" t="n">
-        <v>135.7</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-68.06</v>
+        <v>-71.66</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.58</v>
+        <v>-37.46</v>
       </c>
       <c r="L16" t="n">
-        <v>76.8</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-112.05</v>
+        <v>-121.11</v>
       </c>
       <c r="K17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="L17" t="n">
-        <v>112.05</v>
+        <v>121.11</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>85.38</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-93.53</v>
+        <v>-101.62</v>
       </c>
       <c r="L18" t="n">
-        <v>126.64</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-59.49</v>
+        <v>-64.68000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>122.84</v>
+        <v>133.57</v>
       </c>
       <c r="L19" t="n">
-        <v>136.49</v>
+        <v>148.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-204.44</v>
+        <v>-230.39</v>
       </c>
       <c r="K20" t="n">
-        <v>163.27</v>
+        <v>183.99</v>
       </c>
       <c r="L20" t="n">
-        <v>261.64</v>
+        <v>294.84</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>167.64</v>
+        <v>188.2</v>
       </c>
       <c r="K21" t="n">
-        <v>63.87</v>
+        <v>71.7</v>
       </c>
       <c r="L21" t="n">
-        <v>179.39</v>
+        <v>201.39</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>108.64</v>
+        <v>122.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-76.19</v>
+        <v>-85.97</v>
       </c>
       <c r="L22" t="n">
-        <v>132.69</v>
+        <v>149.73</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>195.85</v>
+        <v>224.54</v>
       </c>
       <c r="K23" t="n">
-        <v>-145.81</v>
+        <v>-167.17</v>
       </c>
       <c r="L23" t="n">
-        <v>244.17</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-203.92</v>
+        <v>-233.81</v>
       </c>
       <c r="K24" t="n">
-        <v>217.95</v>
+        <v>249.9</v>
       </c>
       <c r="L24" t="n">
-        <v>298.47</v>
+        <v>342.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>104.68</v>
+        <v>118.94</v>
       </c>
       <c r="K25" t="n">
-        <v>385.37</v>
+        <v>437.86</v>
       </c>
       <c r="L25" t="n">
-        <v>399.34</v>
+        <v>453.73</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>58.72</v>
+        <v>67.91</v>
       </c>
       <c r="K26" t="n">
-        <v>-192.7</v>
+        <v>-222.87</v>
       </c>
       <c r="L26" t="n">
-        <v>201.45</v>
+        <v>232.98</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>118.66</v>
+        <v>137.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-358.08</v>
+        <v>-413.49</v>
       </c>
       <c r="L27" t="n">
-        <v>377.23</v>
+        <v>435.6</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>481.6</v>
+        <v>565.4299999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>64.08</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>485.84</v>
+        <v>570.42</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-16.41</v>
+        <v>-17.32</v>
       </c>
       <c r="K29" t="n">
-        <v>161.45</v>
+        <v>170.39</v>
       </c>
       <c r="L29" t="n">
-        <v>162.29</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-143.34</v>
+        <v>-150.11</v>
       </c>
       <c r="K30" t="n">
-        <v>-79.01000000000001</v>
+        <v>-82.75</v>
       </c>
       <c r="L30" t="n">
-        <v>163.68</v>
+        <v>171.41</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>114.06</v>
+        <v>119.73</v>
       </c>
       <c r="K31" t="n">
-        <v>102.04</v>
+        <v>107.11</v>
       </c>
       <c r="L31" t="n">
-        <v>153.04</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.4</v>
+        <v>-16.75</v>
       </c>
       <c r="K32" t="n">
-        <v>-89.77</v>
+        <v>-97.65000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>91.09</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-116.25</v>
+        <v>-126.88</v>
       </c>
       <c r="K33" t="n">
-        <v>121.13</v>
+        <v>132.21</v>
       </c>
       <c r="L33" t="n">
-        <v>167.89</v>
+        <v>183.24</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>293.04</v>
+        <v>312.18</v>
       </c>
       <c r="K34" t="n">
-        <v>98.26000000000001</v>
+        <v>104.68</v>
       </c>
       <c r="L34" t="n">
-        <v>309.08</v>
+        <v>329.26</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-37.27</v>
+        <v>-41.35</v>
       </c>
       <c r="K35" t="n">
-        <v>-235.24</v>
+        <v>-260.97</v>
       </c>
       <c r="L35" t="n">
-        <v>238.18</v>
+        <v>264.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>218.86</v>
+        <v>244.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-58.43</v>
+        <v>-65.2</v>
       </c>
       <c r="L36" t="n">
-        <v>226.53</v>
+        <v>252.74</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-299.28</v>
+        <v>-338.49</v>
       </c>
       <c r="K37" t="n">
-        <v>-313.14</v>
+        <v>-354.17</v>
       </c>
       <c r="L37" t="n">
-        <v>433.16</v>
+        <v>489.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>217.98</v>
+        <v>250.72</v>
       </c>
       <c r="K38" t="n">
-        <v>331.71</v>
+        <v>381.54</v>
       </c>
       <c r="L38" t="n">
-        <v>396.92</v>
+        <v>456.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>223.85</v>
+        <v>257.17</v>
       </c>
       <c r="K39" t="n">
-        <v>-184.86</v>
+        <v>-212.37</v>
       </c>
       <c r="L39" t="n">
-        <v>290.32</v>
+        <v>333.52</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-134.8</v>
+        <v>-154.61</v>
       </c>
       <c r="K40" t="n">
-        <v>-25.69</v>
+        <v>-29.47</v>
       </c>
       <c r="L40" t="n">
-        <v>137.23</v>
+        <v>157.4</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-156.95</v>
+        <v>-183.31</v>
       </c>
       <c r="K41" t="n">
-        <v>156.45</v>
+        <v>182.73</v>
       </c>
       <c r="L41" t="n">
-        <v>221.6</v>
+        <v>258.83</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>99.81999999999999</v>
+        <v>117.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-232.1</v>
+        <v>-272.79</v>
       </c>
       <c r="L42" t="n">
-        <v>252.65</v>
+        <v>296.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-324.68</v>
+        <v>-380.74</v>
       </c>
       <c r="K43" t="n">
-        <v>-155.22</v>
+        <v>-182.02</v>
       </c>
       <c r="L43" t="n">
-        <v>359.87</v>
+        <v>422.01</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-19.97</v>
+        <v>-20.64</v>
       </c>
       <c r="K44" t="n">
-        <v>-128.88</v>
+        <v>-133.21</v>
       </c>
       <c r="L44" t="n">
-        <v>130.42</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>219.4</v>
+        <v>232.38</v>
       </c>
       <c r="K45" t="n">
-        <v>-207.35</v>
+        <v>-219.62</v>
       </c>
       <c r="L45" t="n">
-        <v>301.88</v>
+        <v>319.74</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-81.93000000000001</v>
+        <v>-87.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-131.57</v>
+        <v>-140.33</v>
       </c>
       <c r="L46" t="n">
-        <v>154.99</v>
+        <v>165.32</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-199.97</v>
+        <v>-213.57</v>
       </c>
       <c r="K47" t="n">
-        <v>119.51</v>
+        <v>127.64</v>
       </c>
       <c r="L47" t="n">
-        <v>232.96</v>
+        <v>248.8</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-75.06</v>
+        <v>-81.66</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.41</v>
+        <v>-41.79</v>
       </c>
       <c r="L48" t="n">
-        <v>84.31999999999999</v>
+        <v>91.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-24.42</v>
+        <v>-26.67</v>
       </c>
       <c r="K49" t="n">
-        <v>-221.49</v>
+        <v>-241.89</v>
       </c>
       <c r="L49" t="n">
-        <v>222.83</v>
+        <v>243.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>90.7</v>
+        <v>100.94</v>
       </c>
       <c r="K50" t="n">
-        <v>-233.21</v>
+        <v>-259.53</v>
       </c>
       <c r="L50" t="n">
-        <v>250.23</v>
+        <v>278.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>26.6</v>
+        <v>30.04</v>
       </c>
       <c r="K51" t="n">
-        <v>217.97</v>
+        <v>246.2</v>
       </c>
       <c r="L51" t="n">
-        <v>219.59</v>
+        <v>248.03</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>139.34</v>
+        <v>156.02</v>
       </c>
       <c r="K52" t="n">
-        <v>-117.36</v>
+        <v>-131.42</v>
       </c>
       <c r="L52" t="n">
-        <v>182.18</v>
+        <v>203.99</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>135.99</v>
+        <v>156.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-125.14</v>
+        <v>-143.7</v>
       </c>
       <c r="L53" t="n">
-        <v>184.81</v>
+        <v>212.21</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>64.86</v>
+        <v>74.41</v>
       </c>
       <c r="K54" t="n">
-        <v>137.25</v>
+        <v>157.45</v>
       </c>
       <c r="L54" t="n">
-        <v>151.8</v>
+        <v>174.15</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-193.59</v>
+        <v>-221.59</v>
       </c>
       <c r="K55" t="n">
-        <v>-60.41</v>
+        <v>-69.15000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>202.8</v>
+        <v>232.13</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-445.09</v>
+        <v>-521.13</v>
       </c>
       <c r="K56" t="n">
-        <v>84.81999999999999</v>
+        <v>99.31</v>
       </c>
       <c r="L56" t="n">
-        <v>453.1</v>
+        <v>530.51</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>336.38</v>
+        <v>388.92</v>
       </c>
       <c r="K57" t="n">
-        <v>150.89</v>
+        <v>174.46</v>
       </c>
       <c r="L57" t="n">
-        <v>368.68</v>
+        <v>426.26</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-435.78</v>
+        <v>-505.45</v>
       </c>
       <c r="K58" t="n">
-        <v>-252.56</v>
+        <v>-292.93</v>
       </c>
       <c r="L58" t="n">
-        <v>503.68</v>
+        <v>584.2</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-85.83</v>
+        <v>-90.20999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>90.27</v>
+        <v>94.87</v>
       </c>
       <c r="L59" t="n">
-        <v>124.57</v>
+        <v>130.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.46</v>
+        <v>-45.63</v>
       </c>
       <c r="K60" t="n">
-        <v>63.7</v>
+        <v>66.87</v>
       </c>
       <c r="L60" t="n">
-        <v>77.11</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-111.7</v>
+        <v>-117.17</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.13</v>
+        <v>-29.51</v>
       </c>
       <c r="L61" t="n">
-        <v>115.19</v>
+        <v>120.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-153.46</v>
+        <v>-164.79</v>
       </c>
       <c r="K62" t="n">
-        <v>83.65000000000001</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>174.78</v>
+        <v>187.68</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-18.34</v>
+        <v>-19.99</v>
       </c>
       <c r="K63" t="n">
-        <v>142.57</v>
+        <v>155.4</v>
       </c>
       <c r="L63" t="n">
-        <v>143.74</v>
+        <v>156.68</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-92.48999999999999</v>
+        <v>-101.08</v>
       </c>
       <c r="K64" t="n">
-        <v>-32.43</v>
+        <v>-35.44</v>
       </c>
       <c r="L64" t="n">
-        <v>98.01000000000001</v>
+        <v>107.11</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>161.23</v>
+        <v>179.3</v>
       </c>
       <c r="K65" t="n">
-        <v>95.62</v>
+        <v>106.34</v>
       </c>
       <c r="L65" t="n">
-        <v>187.45</v>
+        <v>208.46</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>110.44</v>
+        <v>122.12</v>
       </c>
       <c r="K66" t="n">
-        <v>208.38</v>
+        <v>230.42</v>
       </c>
       <c r="L66" t="n">
-        <v>235.83</v>
+        <v>260.78</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>133.49</v>
+        <v>148.33</v>
       </c>
       <c r="K67" t="n">
-        <v>-138.97</v>
+        <v>-154.43</v>
       </c>
       <c r="L67" t="n">
-        <v>192.69</v>
+        <v>214.13</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-276.42</v>
+        <v>-320</v>
       </c>
       <c r="K68" t="n">
-        <v>81.55</v>
+        <v>94.41</v>
       </c>
       <c r="L68" t="n">
-        <v>288.19</v>
+        <v>333.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-336.8</v>
+        <v>-388.85</v>
       </c>
       <c r="K69" t="n">
-        <v>-109.62</v>
+        <v>-126.56</v>
       </c>
       <c r="L69" t="n">
-        <v>354.19</v>
+        <v>408.93</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-443.54</v>
+        <v>-512.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-81.23</v>
+        <v>-93.93000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>450.91</v>
+        <v>521.41</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.77</v>
+        <v>-15</v>
       </c>
       <c r="K71" t="n">
-        <v>-566.87</v>
+        <v>-666.01</v>
       </c>
       <c r="L71" t="n">
-        <v>567.01</v>
+        <v>666.1799999999999</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-157.15</v>
+        <v>-184.7</v>
       </c>
       <c r="K72" t="n">
-        <v>265.9</v>
+        <v>312.51</v>
       </c>
       <c r="L72" t="n">
-        <v>308.87</v>
+        <v>363.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-88.92</v>
+        <v>-104.16</v>
       </c>
       <c r="K73" t="n">
-        <v>-261.67</v>
+        <v>-306.52</v>
       </c>
       <c r="L73" t="n">
-        <v>276.37</v>
+        <v>323.73</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-54.88</v>
+        <v>-57.55</v>
       </c>
       <c r="K74" t="n">
-        <v>-215.95</v>
+        <v>-226.47</v>
       </c>
       <c r="L74" t="n">
-        <v>222.82</v>
+        <v>233.66</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-188.47</v>
+        <v>-202.42</v>
       </c>
       <c r="K75" t="n">
-        <v>183.2</v>
+        <v>196.76</v>
       </c>
       <c r="L75" t="n">
-        <v>262.84</v>
+        <v>282.29</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>84.75</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-98.5</v>
+        <v>-103.24</v>
       </c>
       <c r="L76" t="n">
-        <v>129.94</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-116.88</v>
+        <v>-127.28</v>
       </c>
       <c r="K77" t="n">
-        <v>-105</v>
+        <v>-114.34</v>
       </c>
       <c r="L77" t="n">
-        <v>157.12</v>
+        <v>171.1</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-15.43</v>
+        <v>-16.71</v>
       </c>
       <c r="K78" t="n">
-        <v>-142.39</v>
+        <v>-154.18</v>
       </c>
       <c r="L78" t="n">
-        <v>143.23</v>
+        <v>155.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>17.32</v>
+        <v>18.36</v>
       </c>
       <c r="K79" t="n">
-        <v>133.34</v>
+        <v>141.41</v>
       </c>
       <c r="L79" t="n">
-        <v>134.46</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>161.34</v>
+        <v>182.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-253.18</v>
+        <v>-285.69</v>
       </c>
       <c r="L80" t="n">
-        <v>300.21</v>
+        <v>338.77</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-107.16</v>
+        <v>-121.54</v>
       </c>
       <c r="K81" t="n">
-        <v>234.2</v>
+        <v>265.64</v>
       </c>
       <c r="L81" t="n">
-        <v>257.55</v>
+        <v>292.13</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-214.08</v>
+        <v>-242.06</v>
       </c>
       <c r="K82" t="n">
-        <v>-125.38</v>
+        <v>-141.77</v>
       </c>
       <c r="L82" t="n">
-        <v>248.09</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-363.82</v>
+        <v>-420.1</v>
       </c>
       <c r="K83" t="n">
-        <v>-144.7</v>
+        <v>-167.08</v>
       </c>
       <c r="L83" t="n">
-        <v>391.54</v>
+        <v>452.1</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>210.12</v>
+        <v>244.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-276.67</v>
+        <v>-321.42</v>
       </c>
       <c r="L84" t="n">
-        <v>347.41</v>
+        <v>403.6</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-64.78</v>
+        <v>-74.43000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>201.54</v>
+        <v>231.56</v>
       </c>
       <c r="L85" t="n">
-        <v>211.69</v>
+        <v>243.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-39.64</v>
+        <v>-46.44</v>
       </c>
       <c r="K86" t="n">
-        <v>-307.88</v>
+        <v>-360.63</v>
       </c>
       <c r="L86" t="n">
-        <v>310.42</v>
+        <v>363.6</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-328.82</v>
+        <v>-386.77</v>
       </c>
       <c r="K87" t="n">
-        <v>-319.77</v>
+        <v>-376.12</v>
       </c>
       <c r="L87" t="n">
-        <v>458.67</v>
+        <v>539.5</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>217.91</v>
+        <v>259.2</v>
       </c>
       <c r="K88" t="n">
-        <v>-250.69</v>
+        <v>-298.2</v>
       </c>
       <c r="L88" t="n">
-        <v>332.16</v>
+        <v>395.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>42.25</v>
+        <v>26.5</v>
       </c>
       <c r="K14" t="n">
-        <v>69.42</v>
+        <v>43.54</v>
       </c>
       <c r="L14" t="n">
-        <v>81.27</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>48.82</v>
+        <v>28.34</v>
       </c>
       <c r="K15" t="n">
-        <v>-133.77</v>
+        <v>-77.66</v>
       </c>
       <c r="L15" t="n">
-        <v>142.4</v>
+        <v>82.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-71.66</v>
+        <v>-44.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-37.46</v>
+        <v>-23.04</v>
       </c>
       <c r="L16" t="n">
-        <v>80.86</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-121.11</v>
+        <v>-62.52</v>
       </c>
       <c r="K17" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="L17" t="n">
-        <v>121.11</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>92.76000000000001</v>
+        <v>53.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-101.62</v>
+        <v>-58.43</v>
       </c>
       <c r="L18" t="n">
-        <v>137.6</v>
+        <v>79.12</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-64.68000000000001</v>
+        <v>-33.11</v>
       </c>
       <c r="K19" t="n">
-        <v>133.57</v>
+        <v>68.36</v>
       </c>
       <c r="L19" t="n">
-        <v>148.41</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-230.39</v>
+        <v>-118.63</v>
       </c>
       <c r="K20" t="n">
-        <v>183.99</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>294.84</v>
+        <v>151.82</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>188.2</v>
+        <v>99.16</v>
       </c>
       <c r="K21" t="n">
-        <v>71.7</v>
+        <v>37.78</v>
       </c>
       <c r="L21" t="n">
-        <v>201.39</v>
+        <v>106.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>122.59</v>
+        <v>69.84</v>
       </c>
       <c r="K22" t="n">
-        <v>-85.97</v>
+        <v>-48.98</v>
       </c>
       <c r="L22" t="n">
-        <v>149.73</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>224.54</v>
+        <v>106.41</v>
       </c>
       <c r="K23" t="n">
-        <v>-167.17</v>
+        <v>-79.22</v>
       </c>
       <c r="L23" t="n">
-        <v>279.94</v>
+        <v>132.66</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-233.81</v>
+        <v>-130.97</v>
       </c>
       <c r="K24" t="n">
-        <v>249.9</v>
+        <v>139.98</v>
       </c>
       <c r="L24" t="n">
-        <v>342.23</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>118.94</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>437.86</v>
+        <v>242.01</v>
       </c>
       <c r="L25" t="n">
-        <v>453.73</v>
+        <v>250.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>67.91</v>
+        <v>42.17</v>
       </c>
       <c r="K26" t="n">
-        <v>-222.87</v>
+        <v>-138.4</v>
       </c>
       <c r="L26" t="n">
-        <v>232.98</v>
+        <v>144.68</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>137.03</v>
+        <v>78.87</v>
       </c>
       <c r="K27" t="n">
-        <v>-413.49</v>
+        <v>-237.98</v>
       </c>
       <c r="L27" t="n">
-        <v>435.6</v>
+        <v>250.71</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>565.4299999999999</v>
+        <v>310.25</v>
       </c>
       <c r="K28" t="n">
-        <v>75.23999999999999</v>
+        <v>41.28</v>
       </c>
       <c r="L28" t="n">
-        <v>570.42</v>
+        <v>312.99</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-17.32</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>170.39</v>
+        <v>87.41</v>
       </c>
       <c r="L29" t="n">
-        <v>171.27</v>
+        <v>87.86</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-150.11</v>
+        <v>-79.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-82.75</v>
+        <v>-43.8</v>
       </c>
       <c r="L30" t="n">
-        <v>171.41</v>
+        <v>90.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>119.73</v>
+        <v>61.89</v>
       </c>
       <c r="K31" t="n">
-        <v>107.11</v>
+        <v>55.37</v>
       </c>
       <c r="L31" t="n">
-        <v>160.65</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-16.75</v>
+        <v>-9.17</v>
       </c>
       <c r="K32" t="n">
-        <v>-97.65000000000001</v>
+        <v>-53.45</v>
       </c>
       <c r="L32" t="n">
-        <v>99.08</v>
+        <v>54.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-126.88</v>
+        <v>-66.36</v>
       </c>
       <c r="K33" t="n">
-        <v>132.21</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>183.24</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>312.18</v>
+        <v>130.23</v>
       </c>
       <c r="K34" t="n">
-        <v>104.68</v>
+        <v>43.67</v>
       </c>
       <c r="L34" t="n">
-        <v>329.26</v>
+        <v>137.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-41.35</v>
+        <v>-21.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-260.97</v>
+        <v>-135.61</v>
       </c>
       <c r="L35" t="n">
-        <v>264.22</v>
+        <v>137.3</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>244.19</v>
+        <v>129.72</v>
       </c>
       <c r="K36" t="n">
-        <v>-65.2</v>
+        <v>-34.63</v>
       </c>
       <c r="L36" t="n">
-        <v>252.74</v>
+        <v>134.26</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-338.49</v>
+        <v>-165.24</v>
       </c>
       <c r="K37" t="n">
-        <v>-354.17</v>
+        <v>-172.9</v>
       </c>
       <c r="L37" t="n">
-        <v>489.91</v>
+        <v>239.16</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>250.72</v>
+        <v>132.48</v>
       </c>
       <c r="K38" t="n">
-        <v>381.54</v>
+        <v>201.6</v>
       </c>
       <c r="L38" t="n">
-        <v>456.54</v>
+        <v>241.23</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>257.17</v>
+        <v>154.78</v>
       </c>
       <c r="K39" t="n">
-        <v>-212.37</v>
+        <v>-127.81</v>
       </c>
       <c r="L39" t="n">
-        <v>333.52</v>
+        <v>200.73</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-154.61</v>
+        <v>-99.68000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-29.47</v>
+        <v>-19</v>
       </c>
       <c r="L40" t="n">
-        <v>157.4</v>
+        <v>101.48</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-183.31</v>
+        <v>-100.99</v>
       </c>
       <c r="K41" t="n">
-        <v>182.73</v>
+        <v>100.67</v>
       </c>
       <c r="L41" t="n">
-        <v>258.83</v>
+        <v>142.59</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>117.32</v>
+        <v>64.47</v>
       </c>
       <c r="K42" t="n">
-        <v>-272.79</v>
+        <v>-149.9</v>
       </c>
       <c r="L42" t="n">
-        <v>296.95</v>
+        <v>163.18</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-380.74</v>
+        <v>-207.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-182.02</v>
+        <v>-99.44</v>
       </c>
       <c r="L43" t="n">
-        <v>422.01</v>
+        <v>230.54</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-20.64</v>
+        <v>-11.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-133.21</v>
+        <v>-75.69</v>
       </c>
       <c r="L44" t="n">
-        <v>134.8</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>232.38</v>
+        <v>104.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-219.62</v>
+        <v>-98.78</v>
       </c>
       <c r="L45" t="n">
-        <v>319.74</v>
+        <v>143.81</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-87.39</v>
+        <v>-40.21</v>
       </c>
       <c r="K46" t="n">
-        <v>-140.33</v>
+        <v>-64.56999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>165.32</v>
+        <v>76.06999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-213.57</v>
+        <v>-99.5</v>
       </c>
       <c r="K47" t="n">
-        <v>127.64</v>
+        <v>59.47</v>
       </c>
       <c r="L47" t="n">
-        <v>248.8</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-81.66</v>
+        <v>-47.05</v>
       </c>
       <c r="K48" t="n">
-        <v>-41.79</v>
+        <v>-24.08</v>
       </c>
       <c r="L48" t="n">
-        <v>91.73</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.67</v>
+        <v>-14.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-241.89</v>
+        <v>-134.75</v>
       </c>
       <c r="L49" t="n">
-        <v>243.36</v>
+        <v>135.57</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>100.94</v>
+        <v>53.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-259.53</v>
+        <v>-136.75</v>
       </c>
       <c r="L50" t="n">
-        <v>278.47</v>
+        <v>146.73</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>30.04</v>
+        <v>16.09</v>
       </c>
       <c r="K51" t="n">
-        <v>246.2</v>
+        <v>131.87</v>
       </c>
       <c r="L51" t="n">
-        <v>248.03</v>
+        <v>132.85</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>156.02</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-131.42</v>
+        <v>-65.78</v>
       </c>
       <c r="L52" t="n">
-        <v>203.99</v>
+        <v>102.11</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>156.15</v>
+        <v>90.95</v>
       </c>
       <c r="K53" t="n">
-        <v>-143.7</v>
+        <v>-83.7</v>
       </c>
       <c r="L53" t="n">
-        <v>212.21</v>
+        <v>123.61</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>74.41</v>
+        <v>39.07</v>
       </c>
       <c r="K54" t="n">
-        <v>157.45</v>
+        <v>82.67</v>
       </c>
       <c r="L54" t="n">
-        <v>174.15</v>
+        <v>91.44</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-221.59</v>
+        <v>-123.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-69.15000000000001</v>
+        <v>-38.56</v>
       </c>
       <c r="L55" t="n">
-        <v>232.13</v>
+        <v>129.45</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-521.13</v>
+        <v>-288.89</v>
       </c>
       <c r="K56" t="n">
-        <v>99.31</v>
+        <v>55.05</v>
       </c>
       <c r="L56" t="n">
-        <v>530.51</v>
+        <v>294.09</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>388.92</v>
+        <v>215.48</v>
       </c>
       <c r="K57" t="n">
-        <v>174.46</v>
+        <v>96.66</v>
       </c>
       <c r="L57" t="n">
-        <v>426.26</v>
+        <v>236.17</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-505.45</v>
+        <v>-277.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-292.93</v>
+        <v>-160.97</v>
       </c>
       <c r="L58" t="n">
-        <v>584.2</v>
+        <v>321.03</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-90.20999999999999</v>
+        <v>-40.74</v>
       </c>
       <c r="K59" t="n">
-        <v>94.87</v>
+        <v>42.85</v>
       </c>
       <c r="L59" t="n">
-        <v>130.92</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.63</v>
+        <v>-23.05</v>
       </c>
       <c r="K60" t="n">
-        <v>66.87</v>
+        <v>33.78</v>
       </c>
       <c r="L60" t="n">
-        <v>80.95999999999999</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-117.17</v>
+        <v>-55.09</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.51</v>
+        <v>-13.87</v>
       </c>
       <c r="L61" t="n">
-        <v>120.83</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-164.79</v>
+        <v>-95.69</v>
       </c>
       <c r="K62" t="n">
-        <v>89.81999999999999</v>
+        <v>52.16</v>
       </c>
       <c r="L62" t="n">
-        <v>187.68</v>
+        <v>108.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-19.99</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>155.4</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>156.68</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-101.08</v>
+        <v>-49.29</v>
       </c>
       <c r="K64" t="n">
-        <v>-35.44</v>
+        <v>-17.28</v>
       </c>
       <c r="L64" t="n">
-        <v>107.11</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>179.3</v>
+        <v>89.95</v>
       </c>
       <c r="K65" t="n">
-        <v>106.34</v>
+        <v>53.35</v>
       </c>
       <c r="L65" t="n">
-        <v>208.46</v>
+        <v>104.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>122.12</v>
+        <v>59.76</v>
       </c>
       <c r="K66" t="n">
-        <v>230.42</v>
+        <v>112.75</v>
       </c>
       <c r="L66" t="n">
-        <v>260.78</v>
+        <v>127.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>148.33</v>
+        <v>79.45</v>
       </c>
       <c r="K67" t="n">
-        <v>-154.43</v>
+        <v>-82.70999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>214.13</v>
+        <v>114.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-320</v>
+        <v>-181.3</v>
       </c>
       <c r="K68" t="n">
-        <v>94.41</v>
+        <v>53.49</v>
       </c>
       <c r="L68" t="n">
-        <v>333.63</v>
+        <v>189.03</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-388.85</v>
+        <v>-200.5</v>
       </c>
       <c r="K69" t="n">
-        <v>-126.56</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>408.93</v>
+        <v>210.86</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-512.88</v>
+        <v>-257.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-93.93000000000001</v>
+        <v>-47.12</v>
       </c>
       <c r="L70" t="n">
-        <v>521.41</v>
+        <v>261.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-15</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-666.01</v>
+        <v>-364.36</v>
       </c>
       <c r="L71" t="n">
-        <v>666.1799999999999</v>
+        <v>364.46</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-184.7</v>
+        <v>-102.39</v>
       </c>
       <c r="K72" t="n">
-        <v>312.51</v>
+        <v>173.24</v>
       </c>
       <c r="L72" t="n">
-        <v>363.01</v>
+        <v>201.23</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-104.16</v>
+        <v>-58.31</v>
       </c>
       <c r="K73" t="n">
-        <v>-306.52</v>
+        <v>-171.59</v>
       </c>
       <c r="L73" t="n">
-        <v>323.73</v>
+        <v>181.23</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-57.55</v>
+        <v>-25.68</v>
       </c>
       <c r="K74" t="n">
-        <v>-226.47</v>
+        <v>-101.04</v>
       </c>
       <c r="L74" t="n">
-        <v>233.66</v>
+        <v>104.26</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-202.42</v>
+        <v>-85.01000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>196.76</v>
+        <v>82.63</v>
       </c>
       <c r="L75" t="n">
-        <v>282.29</v>
+        <v>118.55</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>88.81999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="K76" t="n">
-        <v>-103.24</v>
+        <v>-47.31</v>
       </c>
       <c r="L76" t="n">
-        <v>136.19</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-127.28</v>
+        <v>-66.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-114.34</v>
+        <v>-59.67</v>
       </c>
       <c r="L77" t="n">
-        <v>171.1</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-16.71</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-154.18</v>
+        <v>-77.45</v>
       </c>
       <c r="L78" t="n">
-        <v>155.08</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>18.36</v>
+        <v>8.18</v>
       </c>
       <c r="K79" t="n">
-        <v>141.41</v>
+        <v>63</v>
       </c>
       <c r="L79" t="n">
-        <v>142.6</v>
+        <v>63.53</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>182.06</v>
+        <v>90.39</v>
       </c>
       <c r="K80" t="n">
-        <v>-285.69</v>
+        <v>-141.84</v>
       </c>
       <c r="L80" t="n">
-        <v>338.77</v>
+        <v>168.2</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-121.54</v>
+        <v>-59.45</v>
       </c>
       <c r="K81" t="n">
-        <v>265.64</v>
+        <v>129.92</v>
       </c>
       <c r="L81" t="n">
-        <v>292.13</v>
+        <v>142.88</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-242.06</v>
+        <v>-120.76</v>
       </c>
       <c r="K82" t="n">
-        <v>-141.77</v>
+        <v>-70.73</v>
       </c>
       <c r="L82" t="n">
-        <v>280.52</v>
+        <v>139.95</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-420.1</v>
+        <v>-211.16</v>
       </c>
       <c r="K83" t="n">
-        <v>-167.08</v>
+        <v>-83.98</v>
       </c>
       <c r="L83" t="n">
-        <v>452.1</v>
+        <v>227.25</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>244.1</v>
+        <v>113.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-321.42</v>
+        <v>-148.92</v>
       </c>
       <c r="L84" t="n">
-        <v>403.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-74.43000000000001</v>
+        <v>-43.89</v>
       </c>
       <c r="K85" t="n">
-        <v>231.56</v>
+        <v>136.56</v>
       </c>
       <c r="L85" t="n">
-        <v>243.22</v>
+        <v>143.44</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-46.44</v>
+        <v>-24.96</v>
       </c>
       <c r="K86" t="n">
-        <v>-360.63</v>
+        <v>-193.81</v>
       </c>
       <c r="L86" t="n">
-        <v>363.6</v>
+        <v>195.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-386.77</v>
+        <v>-214.63</v>
       </c>
       <c r="K87" t="n">
-        <v>-376.12</v>
+        <v>-208.73</v>
       </c>
       <c r="L87" t="n">
-        <v>539.5</v>
+        <v>299.39</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>259.2</v>
+        <v>138.94</v>
       </c>
       <c r="K88" t="n">
-        <v>-298.2</v>
+        <v>-159.85</v>
       </c>
       <c r="L88" t="n">
-        <v>395.1</v>
+        <v>211.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>26.5</v>
+        <v>27.3</v>
       </c>
       <c r="K14" t="n">
-        <v>43.54</v>
+        <v>44.85</v>
       </c>
       <c r="L14" t="n">
-        <v>50.98</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>28.34</v>
+        <v>27.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-77.66</v>
+        <v>-76.31999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>82.67</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-44.06</v>
+        <v>-45.83</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.04</v>
+        <v>-23.96</v>
       </c>
       <c r="L16" t="n">
-        <v>49.72</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-62.52</v>
+        <v>-65.52</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>62.52</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>53.34</v>
+        <v>53.96</v>
       </c>
       <c r="K18" t="n">
-        <v>-58.43</v>
+        <v>-59.11</v>
       </c>
       <c r="L18" t="n">
-        <v>79.12</v>
+        <v>80.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-33.11</v>
+        <v>-33.73</v>
       </c>
       <c r="K19" t="n">
-        <v>68.36</v>
+        <v>69.66</v>
       </c>
       <c r="L19" t="n">
-        <v>75.95999999999999</v>
+        <v>77.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-118.63</v>
+        <v>-116.15</v>
       </c>
       <c r="K20" t="n">
-        <v>94.73999999999999</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>151.82</v>
+        <v>148.64</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>99.16</v>
+        <v>101.21</v>
       </c>
       <c r="K21" t="n">
-        <v>37.78</v>
+        <v>38.56</v>
       </c>
       <c r="L21" t="n">
-        <v>106.12</v>
+        <v>108.31</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>69.84</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-48.98</v>
+        <v>-51.44</v>
       </c>
       <c r="L22" t="n">
-        <v>85.31</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>106.41</v>
+        <v>112.47</v>
       </c>
       <c r="K23" t="n">
-        <v>-79.22</v>
+        <v>-83.73</v>
       </c>
       <c r="L23" t="n">
-        <v>132.66</v>
+        <v>140.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-130.97</v>
+        <v>-130.03</v>
       </c>
       <c r="K24" t="n">
-        <v>139.98</v>
+        <v>138.98</v>
       </c>
       <c r="L24" t="n">
-        <v>191.7</v>
+        <v>190.33</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>65.73999999999999</v>
+        <v>63.49</v>
       </c>
       <c r="K25" t="n">
-        <v>242.01</v>
+        <v>233.73</v>
       </c>
       <c r="L25" t="n">
-        <v>250.78</v>
+        <v>242.2</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>42.17</v>
+        <v>45</v>
       </c>
       <c r="K26" t="n">
-        <v>-138.4</v>
+        <v>-147.68</v>
       </c>
       <c r="L26" t="n">
-        <v>144.68</v>
+        <v>154.39</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>78.87</v>
+        <v>77.98</v>
       </c>
       <c r="K27" t="n">
-        <v>-237.98</v>
+        <v>-235.31</v>
       </c>
       <c r="L27" t="n">
-        <v>250.71</v>
+        <v>247.9</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>310.25</v>
+        <v>313.59</v>
       </c>
       <c r="K28" t="n">
-        <v>41.28</v>
+        <v>41.73</v>
       </c>
       <c r="L28" t="n">
-        <v>312.99</v>
+        <v>316.36</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.69</v>
       </c>
       <c r="K29" t="n">
-        <v>87.41</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>87.86</v>
+        <v>85.93000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-79.45</v>
+        <v>-77.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-43.8</v>
+        <v>-42.79</v>
       </c>
       <c r="L30" t="n">
-        <v>90.72</v>
+        <v>88.63</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>61.89</v>
+        <v>60.83</v>
       </c>
       <c r="K31" t="n">
-        <v>55.37</v>
+        <v>54.42</v>
       </c>
       <c r="L31" t="n">
-        <v>83.05</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.17</v>
+        <v>-9.77</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.45</v>
+        <v>-56.98</v>
       </c>
       <c r="L32" t="n">
-        <v>54.23</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-66.36</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>69.15000000000001</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>95.84</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>130.23</v>
+        <v>117.34</v>
       </c>
       <c r="K34" t="n">
-        <v>43.67</v>
+        <v>39.34</v>
       </c>
       <c r="L34" t="n">
-        <v>137.36</v>
+        <v>123.76</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.49</v>
+        <v>-21.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-135.61</v>
+        <v>-133.51</v>
       </c>
       <c r="L35" t="n">
-        <v>137.3</v>
+        <v>135.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>129.72</v>
+        <v>127.57</v>
       </c>
       <c r="K36" t="n">
-        <v>-34.63</v>
+        <v>-34.06</v>
       </c>
       <c r="L36" t="n">
-        <v>134.26</v>
+        <v>132.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-165.24</v>
+        <v>-155.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-172.9</v>
+        <v>-162.41</v>
       </c>
       <c r="L37" t="n">
-        <v>239.16</v>
+        <v>224.65</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>132.48</v>
+        <v>128.58</v>
       </c>
       <c r="K38" t="n">
-        <v>201.6</v>
+        <v>195.67</v>
       </c>
       <c r="L38" t="n">
-        <v>241.23</v>
+        <v>234.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>154.78</v>
+        <v>151.39</v>
       </c>
       <c r="K39" t="n">
-        <v>-127.81</v>
+        <v>-125.01</v>
       </c>
       <c r="L39" t="n">
-        <v>200.73</v>
+        <v>196.33</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-99.68000000000001</v>
+        <v>-105.91</v>
       </c>
       <c r="K40" t="n">
-        <v>-19</v>
+        <v>-20.18</v>
       </c>
       <c r="L40" t="n">
-        <v>101.48</v>
+        <v>107.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-100.99</v>
+        <v>-113.23</v>
       </c>
       <c r="K41" t="n">
-        <v>100.67</v>
+        <v>112.87</v>
       </c>
       <c r="L41" t="n">
-        <v>142.59</v>
+        <v>159.88</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>64.47</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-149.9</v>
+        <v>-164.74</v>
       </c>
       <c r="L42" t="n">
-        <v>163.18</v>
+        <v>179.33</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-207.99</v>
+        <v>-218.47</v>
       </c>
       <c r="K43" t="n">
-        <v>-99.44</v>
+        <v>-104.45</v>
       </c>
       <c r="L43" t="n">
-        <v>230.54</v>
+        <v>242.16</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.73</v>
+        <v>-11.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-75.69</v>
+        <v>-74.72</v>
       </c>
       <c r="L44" t="n">
-        <v>76.59</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>104.52</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-98.78</v>
+        <v>-91.19</v>
       </c>
       <c r="L45" t="n">
-        <v>143.81</v>
+        <v>132.76</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-40.21</v>
+        <v>-39.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-64.56999999999999</v>
+        <v>-63.74</v>
       </c>
       <c r="L46" t="n">
-        <v>76.06999999999999</v>
+        <v>75.09</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.5</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>59.47</v>
+        <v>56.61</v>
       </c>
       <c r="L47" t="n">
-        <v>115.92</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-47.05</v>
+        <v>-50.65</v>
       </c>
       <c r="K48" t="n">
-        <v>-24.08</v>
+        <v>-25.92</v>
       </c>
       <c r="L48" t="n">
-        <v>52.85</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.86</v>
+        <v>-14.22</v>
       </c>
       <c r="K49" t="n">
-        <v>-134.75</v>
+        <v>-128.93</v>
       </c>
       <c r="L49" t="n">
-        <v>135.57</v>
+        <v>129.72</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>53.19</v>
+        <v>52.07</v>
       </c>
       <c r="K50" t="n">
-        <v>-136.75</v>
+        <v>-133.9</v>
       </c>
       <c r="L50" t="n">
-        <v>146.73</v>
+        <v>143.67</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>16.09</v>
+        <v>15.94</v>
       </c>
       <c r="K51" t="n">
-        <v>131.87</v>
+        <v>130.62</v>
       </c>
       <c r="L51" t="n">
-        <v>132.85</v>
+        <v>131.59</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>78.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-65.78</v>
+        <v>-67.97</v>
       </c>
       <c r="L52" t="n">
-        <v>102.11</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>90.95</v>
+        <v>95.55</v>
       </c>
       <c r="K53" t="n">
-        <v>-83.7</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>123.61</v>
+        <v>129.85</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>39.07</v>
+        <v>38.18</v>
       </c>
       <c r="K54" t="n">
-        <v>82.67</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>91.44</v>
+        <v>89.34999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-123.57</v>
+        <v>-129.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-38.56</v>
+        <v>-40.35</v>
       </c>
       <c r="L55" t="n">
-        <v>129.45</v>
+        <v>135.46</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-288.89</v>
+        <v>-289.31</v>
       </c>
       <c r="K56" t="n">
-        <v>55.05</v>
+        <v>55.13</v>
       </c>
       <c r="L56" t="n">
-        <v>294.09</v>
+        <v>294.51</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>215.48</v>
+        <v>220.36</v>
       </c>
       <c r="K57" t="n">
-        <v>96.66</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>236.17</v>
+        <v>241.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-277.75</v>
+        <v>-278.15</v>
       </c>
       <c r="K58" t="n">
-        <v>-160.97</v>
+        <v>-161.2</v>
       </c>
       <c r="L58" t="n">
-        <v>321.03</v>
+        <v>321.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-40.74</v>
+        <v>-41.28</v>
       </c>
       <c r="K59" t="n">
-        <v>42.85</v>
+        <v>43.41</v>
       </c>
       <c r="L59" t="n">
-        <v>59.12</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.05</v>
+        <v>-22.34</v>
       </c>
       <c r="K60" t="n">
-        <v>33.78</v>
+        <v>32.74</v>
       </c>
       <c r="L60" t="n">
-        <v>40.9</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-55.09</v>
+        <v>-56.26</v>
       </c>
       <c r="K61" t="n">
-        <v>-13.87</v>
+        <v>-14.17</v>
       </c>
       <c r="L61" t="n">
-        <v>56.81</v>
+        <v>58.01</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.69</v>
+        <v>-92.55</v>
       </c>
       <c r="K62" t="n">
-        <v>52.16</v>
+        <v>50.44</v>
       </c>
       <c r="L62" t="n">
-        <v>108.98</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.82</v>
       </c>
       <c r="K63" t="n">
-        <v>75.48999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="L63" t="n">
-        <v>76.12</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-49.29</v>
+        <v>-53.25</v>
       </c>
       <c r="K64" t="n">
-        <v>-17.28</v>
+        <v>-18.67</v>
       </c>
       <c r="L64" t="n">
-        <v>52.23</v>
+        <v>56.43</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>89.95</v>
+        <v>91.89</v>
       </c>
       <c r="K65" t="n">
-        <v>53.35</v>
+        <v>54.5</v>
       </c>
       <c r="L65" t="n">
-        <v>104.58</v>
+        <v>106.84</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>59.76</v>
+        <v>59.58</v>
       </c>
       <c r="K66" t="n">
-        <v>112.75</v>
+        <v>112.42</v>
       </c>
       <c r="L66" t="n">
-        <v>127.61</v>
+        <v>127.23</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>79.45</v>
+        <v>79.41</v>
       </c>
       <c r="K67" t="n">
-        <v>-82.70999999999999</v>
+        <v>-82.67</v>
       </c>
       <c r="L67" t="n">
-        <v>114.69</v>
+        <v>114.63</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-181.3</v>
+        <v>-179.88</v>
       </c>
       <c r="K68" t="n">
-        <v>53.49</v>
+        <v>53.07</v>
       </c>
       <c r="L68" t="n">
-        <v>189.03</v>
+        <v>187.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-200.5</v>
+        <v>-197.74</v>
       </c>
       <c r="K69" t="n">
-        <v>-65.26000000000001</v>
+        <v>-64.36</v>
       </c>
       <c r="L69" t="n">
-        <v>210.86</v>
+        <v>207.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-257.3</v>
+        <v>-248.98</v>
       </c>
       <c r="K70" t="n">
-        <v>-47.12</v>
+        <v>-45.6</v>
       </c>
       <c r="L70" t="n">
-        <v>261.58</v>
+        <v>253.13</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.19</v>
       </c>
       <c r="K71" t="n">
-        <v>-364.36</v>
+        <v>-363.51</v>
       </c>
       <c r="L71" t="n">
-        <v>364.46</v>
+        <v>363.6</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-102.39</v>
+        <v>-107.51</v>
       </c>
       <c r="K72" t="n">
-        <v>173.24</v>
+        <v>181.91</v>
       </c>
       <c r="L72" t="n">
-        <v>201.23</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-58.31</v>
+        <v>-61.33</v>
       </c>
       <c r="K73" t="n">
-        <v>-171.59</v>
+        <v>-180.48</v>
       </c>
       <c r="L73" t="n">
-        <v>181.23</v>
+        <v>190.61</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-25.68</v>
+        <v>-24.14</v>
       </c>
       <c r="K74" t="n">
-        <v>-101.04</v>
+        <v>-94.98</v>
       </c>
       <c r="L74" t="n">
-        <v>104.26</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-85.01000000000001</v>
+        <v>-78.75</v>
       </c>
       <c r="K75" t="n">
-        <v>82.63</v>
+        <v>76.55</v>
       </c>
       <c r="L75" t="n">
-        <v>118.55</v>
+        <v>109.82</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>40.7</v>
+        <v>40.63</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.31</v>
+        <v>-47.23</v>
       </c>
       <c r="L76" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.42</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-59.67</v>
+        <v>-58.85</v>
       </c>
       <c r="L77" t="n">
-        <v>89.29000000000001</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.43</v>
       </c>
       <c r="K78" t="n">
-        <v>-77.45</v>
+        <v>-77.79000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>77.90000000000001</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>8.18</v>
+        <v>8.32</v>
       </c>
       <c r="K79" t="n">
-        <v>63</v>
+        <v>64.06</v>
       </c>
       <c r="L79" t="n">
-        <v>63.53</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>90.39</v>
+        <v>87.36</v>
       </c>
       <c r="K80" t="n">
-        <v>-141.84</v>
+        <v>-137.08</v>
       </c>
       <c r="L80" t="n">
-        <v>168.2</v>
+        <v>162.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-59.45</v>
+        <v>-58.65</v>
       </c>
       <c r="K81" t="n">
-        <v>129.92</v>
+        <v>128.18</v>
       </c>
       <c r="L81" t="n">
-        <v>142.88</v>
+        <v>140.96</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-120.76</v>
+        <v>-118.98</v>
       </c>
       <c r="K82" t="n">
-        <v>-70.73</v>
+        <v>-69.68000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>139.95</v>
+        <v>137.88</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-211.16</v>
+        <v>-206.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-83.98</v>
+        <v>-82.02</v>
       </c>
       <c r="L83" t="n">
-        <v>227.25</v>
+        <v>221.93</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>113.1</v>
+        <v>113.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-148.92</v>
+        <v>-149.57</v>
       </c>
       <c r="L84" t="n">
-        <v>187</v>
+        <v>187.81</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-43.89</v>
+        <v>-44.63</v>
       </c>
       <c r="K85" t="n">
-        <v>136.56</v>
+        <v>138.86</v>
       </c>
       <c r="L85" t="n">
-        <v>143.44</v>
+        <v>145.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-24.96</v>
+        <v>-27.34</v>
       </c>
       <c r="K86" t="n">
-        <v>-193.81</v>
+        <v>-212.32</v>
       </c>
       <c r="L86" t="n">
-        <v>195.41</v>
+        <v>214.07</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-214.63</v>
+        <v>-213.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-208.73</v>
+        <v>-207.63</v>
       </c>
       <c r="L87" t="n">
-        <v>299.39</v>
+        <v>297.82</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>138.94</v>
+        <v>152.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-159.85</v>
+        <v>-174.89</v>
       </c>
       <c r="L88" t="n">
-        <v>211.8</v>
+        <v>231.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
       <c r="K14" t="n">
-        <v>44.85</v>
+        <v>46.34</v>
       </c>
       <c r="L14" t="n">
-        <v>52.5</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>27.85</v>
+        <v>27.29</v>
       </c>
       <c r="K15" t="n">
-        <v>-76.31999999999999</v>
+        <v>-74.78</v>
       </c>
       <c r="L15" t="n">
-        <v>81.23999999999999</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.83</v>
+        <v>-47.86</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.96</v>
+        <v>-25.02</v>
       </c>
       <c r="L16" t="n">
-        <v>51.72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-65.52</v>
+        <v>-69.37</v>
       </c>
       <c r="K17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>65.52</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>53.96</v>
+        <v>54.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-59.11</v>
+        <v>-59.89</v>
       </c>
       <c r="L18" t="n">
-        <v>80.04000000000001</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-33.73</v>
+        <v>-34.72</v>
       </c>
       <c r="K19" t="n">
-        <v>69.66</v>
+        <v>71.7</v>
       </c>
       <c r="L19" t="n">
-        <v>77.39</v>
+        <v>79.66</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-116.15</v>
+        <v>-113.34</v>
       </c>
       <c r="K20" t="n">
-        <v>92.76000000000001</v>
+        <v>90.52</v>
       </c>
       <c r="L20" t="n">
-        <v>148.64</v>
+        <v>145.05</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>101.21</v>
+        <v>103.56</v>
       </c>
       <c r="K21" t="n">
-        <v>38.56</v>
+        <v>39.46</v>
       </c>
       <c r="L21" t="n">
-        <v>108.31</v>
+        <v>110.82</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>73.34999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="K22" t="n">
-        <v>-51.44</v>
+        <v>-54.25</v>
       </c>
       <c r="L22" t="n">
-        <v>89.59</v>
+        <v>94.48999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>112.47</v>
+        <v>118.57</v>
       </c>
       <c r="K23" t="n">
-        <v>-83.73</v>
+        <v>-88.27</v>
       </c>
       <c r="L23" t="n">
-        <v>140.22</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-130.03</v>
+        <v>-128.81</v>
       </c>
       <c r="K24" t="n">
-        <v>138.98</v>
+        <v>137.67</v>
       </c>
       <c r="L24" t="n">
-        <v>190.33</v>
+        <v>188.53</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>63.49</v>
+        <v>60.81</v>
       </c>
       <c r="K25" t="n">
-        <v>233.73</v>
+        <v>223.86</v>
       </c>
       <c r="L25" t="n">
-        <v>242.2</v>
+        <v>231.98</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>45</v>
+        <v>48.23</v>
       </c>
       <c r="K26" t="n">
-        <v>-147.68</v>
+        <v>-158.29</v>
       </c>
       <c r="L26" t="n">
-        <v>154.39</v>
+        <v>165.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>77.98</v>
+        <v>76.97</v>
       </c>
       <c r="K27" t="n">
-        <v>-235.31</v>
+        <v>-232.26</v>
       </c>
       <c r="L27" t="n">
-        <v>247.9</v>
+        <v>244.68</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>313.59</v>
+        <v>306.64</v>
       </c>
       <c r="K28" t="n">
-        <v>41.73</v>
+        <v>40.8</v>
       </c>
       <c r="L28" t="n">
-        <v>316.36</v>
+        <v>309.34</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.69</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>85.48999999999999</v>
+        <v>83.97</v>
       </c>
       <c r="L29" t="n">
-        <v>85.93000000000001</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-77.62</v>
+        <v>-75.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-42.79</v>
+        <v>-41.8</v>
       </c>
       <c r="L30" t="n">
-        <v>88.63</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>60.83</v>
+        <v>60.04</v>
       </c>
       <c r="K31" t="n">
-        <v>54.42</v>
+        <v>53.71</v>
       </c>
       <c r="L31" t="n">
-        <v>81.62</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.77</v>
+        <v>-10.47</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.98</v>
+        <v>-61.01</v>
       </c>
       <c r="L32" t="n">
-        <v>57.81</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-65.51000000000001</v>
+        <v>-64.86</v>
       </c>
       <c r="K33" t="n">
-        <v>68.26000000000001</v>
+        <v>67.58</v>
       </c>
       <c r="L33" t="n">
-        <v>94.61</v>
+        <v>93.67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>117.34</v>
+        <v>112.23</v>
       </c>
       <c r="K34" t="n">
-        <v>39.34</v>
+        <v>37.63</v>
       </c>
       <c r="L34" t="n">
-        <v>123.76</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.15</v>
+        <v>-20.77</v>
       </c>
       <c r="K35" t="n">
-        <v>-133.51</v>
+        <v>-131.1</v>
       </c>
       <c r="L35" t="n">
-        <v>135.17</v>
+        <v>132.74</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>127.57</v>
+        <v>125.12</v>
       </c>
       <c r="K36" t="n">
-        <v>-34.06</v>
+        <v>-33.4</v>
       </c>
       <c r="L36" t="n">
-        <v>132.04</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-155.22</v>
+        <v>-145.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-162.41</v>
+        <v>-152.35</v>
       </c>
       <c r="L37" t="n">
-        <v>224.65</v>
+        <v>210.74</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>128.58</v>
+        <v>123.68</v>
       </c>
       <c r="K38" t="n">
-        <v>195.67</v>
+        <v>188.21</v>
       </c>
       <c r="L38" t="n">
-        <v>234.14</v>
+        <v>225.21</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>151.39</v>
+        <v>147.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-125.01</v>
+        <v>-121.81</v>
       </c>
       <c r="L39" t="n">
-        <v>196.33</v>
+        <v>191.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-105.91</v>
+        <v>-113.02</v>
       </c>
       <c r="K40" t="n">
-        <v>-20.18</v>
+        <v>-21.54</v>
       </c>
       <c r="L40" t="n">
-        <v>107.81</v>
+        <v>115.05</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-113.23</v>
+        <v>-124.22</v>
       </c>
       <c r="K41" t="n">
-        <v>112.87</v>
+        <v>123.83</v>
       </c>
       <c r="L41" t="n">
-        <v>159.88</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>70.84999999999999</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-164.74</v>
+        <v>-176.82</v>
       </c>
       <c r="L42" t="n">
-        <v>179.33</v>
+        <v>192.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-218.47</v>
+        <v>-222.31</v>
       </c>
       <c r="K43" t="n">
-        <v>-104.45</v>
+        <v>-106.28</v>
       </c>
       <c r="L43" t="n">
-        <v>242.16</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.58</v>
+        <v>-11.41</v>
       </c>
       <c r="K44" t="n">
-        <v>-74.72</v>
+        <v>-73.61</v>
       </c>
       <c r="L44" t="n">
-        <v>75.61</v>
+        <v>74.48999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>96.48999999999999</v>
+        <v>90.09</v>
       </c>
       <c r="K45" t="n">
-        <v>-91.19</v>
+        <v>-85.14</v>
       </c>
       <c r="L45" t="n">
-        <v>132.76</v>
+        <v>123.96</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-39.69</v>
+        <v>-40.03</v>
       </c>
       <c r="K46" t="n">
-        <v>-63.74</v>
+        <v>-64.27</v>
       </c>
       <c r="L46" t="n">
-        <v>75.09</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-94.70999999999999</v>
+        <v>-91.64</v>
       </c>
       <c r="K47" t="n">
-        <v>56.61</v>
+        <v>54.77</v>
       </c>
       <c r="L47" t="n">
-        <v>110.34</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-50.65</v>
+        <v>-54.78</v>
       </c>
       <c r="K48" t="n">
-        <v>-25.92</v>
+        <v>-28.03</v>
       </c>
       <c r="L48" t="n">
-        <v>56.9</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.22</v>
+        <v>-13.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-128.93</v>
+        <v>-122.28</v>
       </c>
       <c r="L49" t="n">
-        <v>129.72</v>
+        <v>123.02</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>52.07</v>
+        <v>50.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-133.9</v>
+        <v>-130.63</v>
       </c>
       <c r="L50" t="n">
-        <v>143.67</v>
+        <v>140.16</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>15.94</v>
+        <v>15.76</v>
       </c>
       <c r="K51" t="n">
-        <v>130.62</v>
+        <v>129.2</v>
       </c>
       <c r="L51" t="n">
-        <v>131.59</v>
+        <v>130.15</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>80.7</v>
+        <v>84.12</v>
       </c>
       <c r="K52" t="n">
-        <v>-67.97</v>
+        <v>-70.84999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>105.51</v>
+        <v>109.98</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>95.55</v>
+        <v>100.8</v>
       </c>
       <c r="K53" t="n">
-        <v>-87.93000000000001</v>
+        <v>-92.76000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>129.85</v>
+        <v>136.99</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>38.18</v>
+        <v>41.95</v>
       </c>
       <c r="K54" t="n">
-        <v>80.79000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="L54" t="n">
-        <v>89.34999999999999</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-129.31</v>
+        <v>-135.71</v>
       </c>
       <c r="K55" t="n">
-        <v>-40.35</v>
+        <v>-42.35</v>
       </c>
       <c r="L55" t="n">
-        <v>135.46</v>
+        <v>142.17</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-289.31</v>
+        <v>-282.91</v>
       </c>
       <c r="K56" t="n">
-        <v>55.13</v>
+        <v>53.91</v>
       </c>
       <c r="L56" t="n">
-        <v>294.51</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>220.36</v>
+        <v>220.7</v>
       </c>
       <c r="K57" t="n">
-        <v>98.84999999999999</v>
+        <v>99</v>
       </c>
       <c r="L57" t="n">
-        <v>241.51</v>
+        <v>241.89</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-278.15</v>
+        <v>-269.39</v>
       </c>
       <c r="K58" t="n">
-        <v>-161.2</v>
+        <v>-156.13</v>
       </c>
       <c r="L58" t="n">
-        <v>321.48</v>
+        <v>311.36</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-41.28</v>
+        <v>-42.94</v>
       </c>
       <c r="K59" t="n">
-        <v>43.41</v>
+        <v>45.16</v>
       </c>
       <c r="L59" t="n">
-        <v>59.91</v>
+        <v>62.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-22.34</v>
+        <v>-24.54</v>
       </c>
       <c r="K60" t="n">
-        <v>32.74</v>
+        <v>35.96</v>
       </c>
       <c r="L60" t="n">
-        <v>39.63</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-56.26</v>
+        <v>-58.67</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.17</v>
+        <v>-14.77</v>
       </c>
       <c r="L61" t="n">
-        <v>58.01</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-92.55</v>
+        <v>-88.95</v>
       </c>
       <c r="K62" t="n">
-        <v>50.44</v>
+        <v>48.49</v>
       </c>
       <c r="L62" t="n">
-        <v>105.4</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-9.82</v>
+        <v>-10.11</v>
       </c>
       <c r="K63" t="n">
-        <v>76.38</v>
+        <v>78.64</v>
       </c>
       <c r="L63" t="n">
-        <v>77</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-53.25</v>
+        <v>-58.56</v>
       </c>
       <c r="K64" t="n">
-        <v>-18.67</v>
+        <v>-20.53</v>
       </c>
       <c r="L64" t="n">
-        <v>56.43</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="K65" t="n">
-        <v>54.5</v>
+        <v>56.1</v>
       </c>
       <c r="L65" t="n">
-        <v>106.84</v>
+        <v>109.98</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>59.58</v>
+        <v>60.01</v>
       </c>
       <c r="K66" t="n">
-        <v>112.42</v>
+        <v>113.23</v>
       </c>
       <c r="L66" t="n">
-        <v>127.23</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>79.41</v>
+        <v>79.36</v>
       </c>
       <c r="K67" t="n">
-        <v>-82.67</v>
+        <v>-82.62</v>
       </c>
       <c r="L67" t="n">
-        <v>114.63</v>
+        <v>114.56</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-179.88</v>
+        <v>-178.11</v>
       </c>
       <c r="K68" t="n">
-        <v>53.07</v>
+        <v>52.55</v>
       </c>
       <c r="L68" t="n">
-        <v>187.54</v>
+        <v>185.7</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-197.74</v>
+        <v>-193.69</v>
       </c>
       <c r="K69" t="n">
-        <v>-64.36</v>
+        <v>-63.04</v>
       </c>
       <c r="L69" t="n">
-        <v>207.95</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-248.98</v>
+        <v>-238.05</v>
       </c>
       <c r="K70" t="n">
-        <v>-45.6</v>
+        <v>-43.6</v>
       </c>
       <c r="L70" t="n">
-        <v>253.13</v>
+        <v>242.01</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.19</v>
+        <v>-7.85</v>
       </c>
       <c r="K71" t="n">
-        <v>-363.51</v>
+        <v>-348.69</v>
       </c>
       <c r="L71" t="n">
-        <v>363.6</v>
+        <v>348.78</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-107.51</v>
+        <v>-110.96</v>
       </c>
       <c r="K72" t="n">
-        <v>181.91</v>
+        <v>187.75</v>
       </c>
       <c r="L72" t="n">
-        <v>211.31</v>
+        <v>218.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-61.33</v>
+        <v>-64.01000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-180.48</v>
+        <v>-188.35</v>
       </c>
       <c r="L73" t="n">
-        <v>190.61</v>
+        <v>198.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-24.14</v>
+        <v>-23.09</v>
       </c>
       <c r="K74" t="n">
-        <v>-94.98</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>98</v>
+        <v>93.73999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.75</v>
+        <v>-74.78</v>
       </c>
       <c r="K75" t="n">
-        <v>76.55</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>109.82</v>
+        <v>104.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>40.63</v>
+        <v>41.51</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.23</v>
+        <v>-48.25</v>
       </c>
       <c r="L76" t="n">
-        <v>62.3</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.51000000000001</v>
+        <v>-64.8</v>
       </c>
       <c r="K77" t="n">
-        <v>-58.85</v>
+        <v>-58.22</v>
       </c>
       <c r="L77" t="n">
-        <v>88.06</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.43</v>
+        <v>-8.57</v>
       </c>
       <c r="K78" t="n">
-        <v>-77.79000000000001</v>
+        <v>-79.05</v>
       </c>
       <c r="L78" t="n">
-        <v>78.25</v>
+        <v>79.52</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>8.32</v>
+        <v>8.74</v>
       </c>
       <c r="K79" t="n">
-        <v>64.06</v>
+        <v>67.27</v>
       </c>
       <c r="L79" t="n">
-        <v>64.59999999999999</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>87.36</v>
+        <v>84.58</v>
       </c>
       <c r="K80" t="n">
-        <v>-137.08</v>
+        <v>-132.73</v>
       </c>
       <c r="L80" t="n">
-        <v>162.55</v>
+        <v>157.39</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-58.65</v>
+        <v>-58.37</v>
       </c>
       <c r="K81" t="n">
-        <v>128.18</v>
+        <v>127.57</v>
       </c>
       <c r="L81" t="n">
-        <v>140.96</v>
+        <v>140.29</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-118.98</v>
+        <v>-117.74</v>
       </c>
       <c r="K82" t="n">
-        <v>-69.68000000000001</v>
+        <v>-68.95999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>137.88</v>
+        <v>136.45</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-206.22</v>
+        <v>-199.42</v>
       </c>
       <c r="K83" t="n">
-        <v>-82.02</v>
+        <v>-79.31</v>
       </c>
       <c r="L83" t="n">
-        <v>221.93</v>
+        <v>214.61</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>113.59</v>
+        <v>113.14</v>
       </c>
       <c r="K84" t="n">
-        <v>-149.57</v>
+        <v>-148.97</v>
       </c>
       <c r="L84" t="n">
-        <v>187.81</v>
+        <v>187.06</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-44.63</v>
+        <v>-45.48</v>
       </c>
       <c r="K85" t="n">
-        <v>138.86</v>
+        <v>141.49</v>
       </c>
       <c r="L85" t="n">
-        <v>145.86</v>
+        <v>148.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-27.34</v>
+        <v>-28.69</v>
       </c>
       <c r="K86" t="n">
-        <v>-212.32</v>
+        <v>-222.77</v>
       </c>
       <c r="L86" t="n">
-        <v>214.07</v>
+        <v>224.61</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-213.51</v>
+        <v>-207.35</v>
       </c>
       <c r="K87" t="n">
-        <v>-207.63</v>
+        <v>-201.64</v>
       </c>
       <c r="L87" t="n">
-        <v>297.82</v>
+        <v>289.22</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>152.02</v>
+        <v>158.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-174.89</v>
+        <v>-182.37</v>
       </c>
       <c r="L88" t="n">
-        <v>231.72</v>
+        <v>241.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -628,25 +628,25 @@
         <v>2.45</v>
       </c>
       <c r="F14" t="n">
-        <v>11.48</v>
+        <v>4.33</v>
       </c>
       <c r="G14" t="n">
-        <v>313.4</v>
+        <v>306.8</v>
       </c>
       <c r="H14" t="n">
-        <v>61.4</v>
+        <v>68.8</v>
       </c>
       <c r="I14" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>28.2</v>
+        <v>29.01</v>
       </c>
       <c r="K14" t="n">
-        <v>46.34</v>
+        <v>49.5</v>
       </c>
       <c r="L14" t="n">
-        <v>54.25</v>
+        <v>57.38</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>2.84</v>
       </c>
       <c r="F15" t="n">
-        <v>11.99</v>
+        <v>6.74</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H15" t="n">
-        <v>70.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>27.29</v>
+        <v>28.89</v>
       </c>
       <c r="K15" t="n">
-        <v>-74.78</v>
+        <v>-80.33</v>
       </c>
       <c r="L15" t="n">
-        <v>79.59999999999999</v>
+        <v>85.37</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>2.54</v>
       </c>
       <c r="F16" t="n">
-        <v>11.71</v>
+        <v>10.28</v>
       </c>
       <c r="G16" t="n">
-        <v>301.3</v>
+        <v>311.3</v>
       </c>
       <c r="H16" t="n">
-        <v>72.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-47.86</v>
+        <v>-58.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.02</v>
+        <v>-28.99</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.45</v>
       </c>
       <c r="F17" t="n">
-        <v>11.54</v>
+        <v>10.73</v>
       </c>
       <c r="G17" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H17" t="n">
-        <v>63.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-69.37</v>
+        <v>-81.88</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="L17" t="n">
-        <v>69.37</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.9</v>
       </c>
       <c r="F18" t="n">
-        <v>10.92</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>303.7</v>
+        <v>295.6</v>
       </c>
       <c r="H18" t="n">
-        <v>66.2</v>
+        <v>64</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>54.67</v>
+        <v>59.22</v>
       </c>
       <c r="K18" t="n">
-        <v>-59.89</v>
+        <v>-67.27</v>
       </c>
       <c r="L18" t="n">
-        <v>81.09</v>
+        <v>89.62</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.49</v>
       </c>
       <c r="F19" t="n">
-        <v>11.96</v>
+        <v>10.06</v>
       </c>
       <c r="G19" t="n">
-        <v>309</v>
+        <v>316.4</v>
       </c>
       <c r="H19" t="n">
-        <v>65.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.72</v>
+        <v>-41.68</v>
       </c>
       <c r="K19" t="n">
-        <v>71.7</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>79.66</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>3.27</v>
       </c>
       <c r="F20" t="n">
-        <v>12.12</v>
+        <v>10.49</v>
       </c>
       <c r="G20" t="n">
-        <v>319.1</v>
+        <v>319.6</v>
       </c>
       <c r="H20" t="n">
-        <v>68.7</v>
+        <v>71.7</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-113.34</v>
+        <v>-126.9</v>
       </c>
       <c r="K20" t="n">
-        <v>90.52</v>
+        <v>104.08</v>
       </c>
       <c r="L20" t="n">
-        <v>145.05</v>
+        <v>164.12</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.14</v>
       </c>
       <c r="F21" t="n">
-        <v>12.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>308.7</v>
+        <v>317.3</v>
       </c>
       <c r="H21" t="n">
-        <v>65.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>103.56</v>
+        <v>103.78</v>
       </c>
       <c r="K21" t="n">
-        <v>39.46</v>
+        <v>55.1</v>
       </c>
       <c r="L21" t="n">
-        <v>110.82</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>2.78</v>
       </c>
       <c r="F22" t="n">
-        <v>11.85</v>
+        <v>9.51</v>
       </c>
       <c r="G22" t="n">
-        <v>311.5</v>
+        <v>314.2</v>
       </c>
       <c r="H22" t="n">
-        <v>69.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>77.36</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-54.25</v>
+        <v>-59.61</v>
       </c>
       <c r="L22" t="n">
-        <v>94.48999999999999</v>
+        <v>109.84</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>4.23</v>
       </c>
       <c r="F23" t="n">
-        <v>12.03</v>
+        <v>13.45</v>
       </c>
       <c r="G23" t="n">
-        <v>321.4</v>
+        <v>317.8</v>
       </c>
       <c r="H23" t="n">
-        <v>63.9</v>
+        <v>72.8</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>118.57</v>
+        <v>143.46</v>
       </c>
       <c r="K23" t="n">
-        <v>-88.27</v>
+        <v>-86.52</v>
       </c>
       <c r="L23" t="n">
-        <v>147.82</v>
+        <v>167.53</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.39</v>
       </c>
       <c r="F24" t="n">
-        <v>11.84</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>307.7</v>
+        <v>313.9</v>
       </c>
       <c r="H24" t="n">
-        <v>66.3</v>
+        <v>66</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-128.81</v>
+        <v>-152.3</v>
       </c>
       <c r="K24" t="n">
-        <v>137.67</v>
+        <v>163.07</v>
       </c>
       <c r="L24" t="n">
-        <v>188.53</v>
+        <v>223.13</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>3.45</v>
       </c>
       <c r="F25" t="n">
-        <v>11.98</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>318.5</v>
+        <v>316.7</v>
       </c>
       <c r="H25" t="n">
-        <v>59.2</v>
+        <v>71.3</v>
       </c>
       <c r="I25" t="n">
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>60.81</v>
+        <v>45.93</v>
       </c>
       <c r="K25" t="n">
-        <v>223.86</v>
+        <v>256.13</v>
       </c>
       <c r="L25" t="n">
-        <v>231.98</v>
+        <v>260.22</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.73</v>
       </c>
       <c r="F26" t="n">
-        <v>11.66</v>
+        <v>5.4</v>
       </c>
       <c r="G26" t="n">
-        <v>318.8</v>
+        <v>310.4</v>
       </c>
       <c r="H26" t="n">
-        <v>61.5</v>
+        <v>71.5</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>48.23</v>
+        <v>-42.25</v>
       </c>
       <c r="K26" t="n">
-        <v>-158.29</v>
+        <v>-162.94</v>
       </c>
       <c r="L26" t="n">
-        <v>165.48</v>
+        <v>168.33</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.16</v>
       </c>
       <c r="F27" t="n">
-        <v>11.74</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>309.9</v>
+        <v>311.9</v>
       </c>
       <c r="H27" t="n">
-        <v>65.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>76.97</v>
+        <v>59.04</v>
       </c>
       <c r="K27" t="n">
-        <v>-232.26</v>
+        <v>-254.86</v>
       </c>
       <c r="L27" t="n">
-        <v>244.68</v>
+        <v>261.61</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.85</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5</v>
+        <v>11.32</v>
       </c>
       <c r="G28" t="n">
-        <v>304</v>
+        <v>327.1</v>
       </c>
       <c r="H28" t="n">
-        <v>66.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>306.64</v>
+        <v>321.82</v>
       </c>
       <c r="K28" t="n">
-        <v>40.8</v>
+        <v>89.25</v>
       </c>
       <c r="L28" t="n">
-        <v>309.34</v>
+        <v>333.97</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.48</v>
       </c>
       <c r="F29" t="n">
-        <v>12.47</v>
+        <v>10.42</v>
       </c>
       <c r="G29" t="n">
-        <v>313</v>
+        <v>326.6</v>
       </c>
       <c r="H29" t="n">
-        <v>69.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.529999999999999</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>83.97</v>
+        <v>95.81</v>
       </c>
       <c r="L29" t="n">
-        <v>84.41</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>3.36</v>
       </c>
       <c r="F30" t="n">
-        <v>11.39</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>312.4</v>
+        <v>304.9</v>
       </c>
       <c r="H30" t="n">
-        <v>66.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="I30" t="n">
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-75.81999999999999</v>
+        <v>-86.56</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.8</v>
+        <v>-46.7</v>
       </c>
       <c r="L30" t="n">
-        <v>86.58</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.45</v>
       </c>
       <c r="F31" t="n">
-        <v>11.36</v>
+        <v>12.61</v>
       </c>
       <c r="G31" t="n">
-        <v>299</v>
+        <v>304.3</v>
       </c>
       <c r="H31" t="n">
-        <v>69.40000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>60.04</v>
+        <v>72</v>
       </c>
       <c r="K31" t="n">
-        <v>53.71</v>
+        <v>66.12</v>
       </c>
       <c r="L31" t="n">
-        <v>80.56</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>3.17</v>
       </c>
       <c r="F32" t="n">
-        <v>11.25</v>
+        <v>12.82</v>
       </c>
       <c r="G32" t="n">
-        <v>305.3</v>
+        <v>302.2</v>
       </c>
       <c r="H32" t="n">
-        <v>73.5</v>
+        <v>64.8</v>
       </c>
       <c r="I32" t="n">
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-10.47</v>
+        <v>-19.71</v>
       </c>
       <c r="K32" t="n">
-        <v>-61.01</v>
+        <v>-77.06999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>61.9</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>3.39</v>
       </c>
       <c r="F33" t="n">
-        <v>12.08</v>
+        <v>9.68</v>
       </c>
       <c r="G33" t="n">
-        <v>294.9</v>
+        <v>318.8</v>
       </c>
       <c r="H33" t="n">
-        <v>67.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="I33" t="n">
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-64.86</v>
+        <v>-72.34999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>67.58</v>
+        <v>77.38</v>
       </c>
       <c r="L33" t="n">
-        <v>93.67</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.89</v>
       </c>
       <c r="F34" t="n">
-        <v>11.64</v>
+        <v>13.45</v>
       </c>
       <c r="G34" t="n">
-        <v>309.5</v>
+        <v>310.1</v>
       </c>
       <c r="H34" t="n">
-        <v>65.3</v>
+        <v>66.8</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>112.23</v>
+        <v>123.51</v>
       </c>
       <c r="K34" t="n">
-        <v>37.63</v>
+        <v>45.07</v>
       </c>
       <c r="L34" t="n">
-        <v>118.37</v>
+        <v>131.47</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.21</v>
       </c>
       <c r="F35" t="n">
-        <v>10.75</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>301.2</v>
+        <v>292.2</v>
       </c>
       <c r="H35" t="n">
-        <v>57.2</v>
+        <v>62.7</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-20.77</v>
+        <v>-34.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-131.1</v>
+        <v>-144.98</v>
       </c>
       <c r="L35" t="n">
-        <v>132.74</v>
+        <v>149.02</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.1</v>
       </c>
       <c r="F36" t="n">
-        <v>12.1</v>
+        <v>9.57</v>
       </c>
       <c r="G36" t="n">
-        <v>304.4</v>
+        <v>319.3</v>
       </c>
       <c r="H36" t="n">
-        <v>67.2</v>
+        <v>64.3</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>125.12</v>
+        <v>146.31</v>
       </c>
       <c r="K36" t="n">
-        <v>-33.4</v>
+        <v>-30.65</v>
       </c>
       <c r="L36" t="n">
-        <v>129.5</v>
+        <v>149.48</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>4.22</v>
       </c>
       <c r="F37" t="n">
-        <v>11.48</v>
+        <v>12.34</v>
       </c>
       <c r="G37" t="n">
-        <v>296.6</v>
+        <v>306.8</v>
       </c>
       <c r="H37" t="n">
-        <v>77.3</v>
+        <v>60.4</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-145.6</v>
+        <v>-171.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-152.35</v>
+        <v>-159.77</v>
       </c>
       <c r="L37" t="n">
-        <v>210.74</v>
+        <v>234.05</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.66</v>
       </c>
       <c r="F38" t="n">
-        <v>11.89</v>
+        <v>11.13</v>
       </c>
       <c r="G38" t="n">
-        <v>318.3</v>
+        <v>314.9</v>
       </c>
       <c r="H38" t="n">
-        <v>66.7</v>
+        <v>71.3</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>123.68</v>
+        <v>113.98</v>
       </c>
       <c r="K38" t="n">
-        <v>188.21</v>
+        <v>226.94</v>
       </c>
       <c r="L38" t="n">
-        <v>225.21</v>
+        <v>253.95</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>2.97</v>
       </c>
       <c r="F39" t="n">
-        <v>11.49</v>
+        <v>8.92</v>
       </c>
       <c r="G39" t="n">
-        <v>299.1</v>
+        <v>306.9</v>
       </c>
       <c r="H39" t="n">
-        <v>67.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>147.51</v>
+        <v>149.36</v>
       </c>
       <c r="K39" t="n">
-        <v>-121.81</v>
+        <v>-122.43</v>
       </c>
       <c r="L39" t="n">
-        <v>191.31</v>
+        <v>193.13</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.55</v>
       </c>
       <c r="F40" t="n">
-        <v>11.96</v>
+        <v>5.66</v>
       </c>
       <c r="G40" t="n">
-        <v>310.1</v>
+        <v>316.5</v>
       </c>
       <c r="H40" t="n">
-        <v>62.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-113.02</v>
+        <v>-126.82</v>
       </c>
       <c r="K40" t="n">
-        <v>-21.54</v>
+        <v>7.49</v>
       </c>
       <c r="L40" t="n">
-        <v>115.05</v>
+        <v>127.04</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>3.77</v>
       </c>
       <c r="F41" t="n">
-        <v>11.08</v>
+        <v>13.45</v>
       </c>
       <c r="G41" t="n">
-        <v>316</v>
+        <v>298.9</v>
       </c>
       <c r="H41" t="n">
-        <v>63.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-124.22</v>
+        <v>-205.64</v>
       </c>
       <c r="K41" t="n">
-        <v>123.83</v>
+        <v>131.86</v>
       </c>
       <c r="L41" t="n">
-        <v>175.4</v>
+        <v>244.29</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.82</v>
       </c>
       <c r="F42" t="n">
-        <v>11.58</v>
+        <v>12.16</v>
       </c>
       <c r="G42" t="n">
-        <v>313.6</v>
+        <v>308.8</v>
       </c>
       <c r="H42" t="n">
-        <v>67.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>76.04000000000001</v>
+        <v>11.87</v>
       </c>
       <c r="K42" t="n">
-        <v>-176.82</v>
+        <v>-216.04</v>
       </c>
       <c r="L42" t="n">
-        <v>192.47</v>
+        <v>216.36</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>3.94</v>
       </c>
       <c r="F43" t="n">
-        <v>11.88</v>
+        <v>10.96</v>
       </c>
       <c r="G43" t="n">
-        <v>309.4</v>
+        <v>314.8</v>
       </c>
       <c r="H43" t="n">
-        <v>64.3</v>
+        <v>66.8</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-222.31</v>
+        <v>-272.64</v>
       </c>
       <c r="K43" t="n">
-        <v>-106.28</v>
+        <v>-74.33</v>
       </c>
       <c r="L43" t="n">
-        <v>246.4</v>
+        <v>282.59</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.97</v>
       </c>
       <c r="F44" t="n">
-        <v>11.54</v>
+        <v>9.84</v>
       </c>
       <c r="G44" t="n">
-        <v>307.3</v>
+        <v>307.9</v>
       </c>
       <c r="H44" t="n">
-        <v>68.2</v>
+        <v>65.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.41</v>
+        <v>-14.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.61</v>
+        <v>-90.2</v>
       </c>
       <c r="L44" t="n">
-        <v>74.48999999999999</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.06</v>
       </c>
       <c r="F45" t="n">
-        <v>11.94</v>
+        <v>12.17</v>
       </c>
       <c r="G45" t="n">
-        <v>318</v>
+        <v>315.9</v>
       </c>
       <c r="H45" t="n">
-        <v>63.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>90.09</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-85.14</v>
+        <v>-94.31999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>123.96</v>
+        <v>137.31</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>3.95</v>
       </c>
       <c r="F46" t="n">
-        <v>11.99</v>
+        <v>13.45</v>
       </c>
       <c r="G46" t="n">
-        <v>317.4</v>
+        <v>317.1</v>
       </c>
       <c r="H46" t="n">
-        <v>69.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-40.03</v>
+        <v>-48.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-64.27</v>
+        <v>-74.73999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>75.72</v>
+        <v>89.13</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>3.98</v>
       </c>
       <c r="F47" t="n">
-        <v>11.62</v>
+        <v>13.45</v>
       </c>
       <c r="G47" t="n">
-        <v>308.2</v>
+        <v>309.7</v>
       </c>
       <c r="H47" t="n">
-        <v>64.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="I47" t="n">
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-91.64</v>
+        <v>-108</v>
       </c>
       <c r="K47" t="n">
-        <v>54.77</v>
+        <v>65.25</v>
       </c>
       <c r="L47" t="n">
-        <v>106.76</v>
+        <v>126.18</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>2.89</v>
       </c>
       <c r="F48" t="n">
-        <v>11.87</v>
+        <v>9.19</v>
       </c>
       <c r="G48" t="n">
-        <v>303</v>
+        <v>314.6</v>
       </c>
       <c r="H48" t="n">
-        <v>67.3</v>
+        <v>63.6</v>
       </c>
       <c r="I48" t="n">
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-54.78</v>
+        <v>-69.66</v>
       </c>
       <c r="K48" t="n">
-        <v>-28.03</v>
+        <v>-27.98</v>
       </c>
       <c r="L48" t="n">
-        <v>61.53</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>3.07</v>
       </c>
       <c r="F49" t="n">
-        <v>11.39</v>
+        <v>12.96</v>
       </c>
       <c r="G49" t="n">
-        <v>314.4</v>
+        <v>304.9</v>
       </c>
       <c r="H49" t="n">
-        <v>68.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I49" t="n">
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.48</v>
+        <v>-18.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-122.28</v>
+        <v>-149.75</v>
       </c>
       <c r="L49" t="n">
-        <v>123.02</v>
+        <v>150.94</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>3.14</v>
       </c>
       <c r="F50" t="n">
-        <v>11.65</v>
+        <v>6.22</v>
       </c>
       <c r="G50" t="n">
-        <v>316.4</v>
+        <v>310.2</v>
       </c>
       <c r="H50" t="n">
-        <v>59.5</v>
+        <v>70.3</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>50.8</v>
+        <v>44.98</v>
       </c>
       <c r="K50" t="n">
-        <v>-130.63</v>
+        <v>-130.58</v>
       </c>
       <c r="L50" t="n">
-        <v>140.16</v>
+        <v>138.11</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>3.06</v>
       </c>
       <c r="F51" t="n">
-        <v>11.47</v>
+        <v>13.45</v>
       </c>
       <c r="G51" t="n">
-        <v>315</v>
+        <v>306.5</v>
       </c>
       <c r="H51" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>15.76</v>
+        <v>8.32</v>
       </c>
       <c r="K51" t="n">
-        <v>129.2</v>
+        <v>162.8</v>
       </c>
       <c r="L51" t="n">
-        <v>130.15</v>
+        <v>163.02</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>3.73</v>
       </c>
       <c r="F52" t="n">
-        <v>11.43</v>
+        <v>10.36</v>
       </c>
       <c r="G52" t="n">
-        <v>316.1</v>
+        <v>305.8</v>
       </c>
       <c r="H52" t="n">
-        <v>64</v>
+        <v>70.2</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>84.12</v>
+        <v>89.73</v>
       </c>
       <c r="K52" t="n">
-        <v>-70.84999999999999</v>
+        <v>-82.90000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>109.98</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>3.2</v>
       </c>
       <c r="F53" t="n">
-        <v>12.22</v>
+        <v>10.2</v>
       </c>
       <c r="G53" t="n">
-        <v>316.5</v>
+        <v>321.7</v>
       </c>
       <c r="H53" t="n">
-        <v>68.2</v>
+        <v>70.3</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>100.8</v>
+        <v>121.37</v>
       </c>
       <c r="K53" t="n">
-        <v>-92.76000000000001</v>
+        <v>-89.05</v>
       </c>
       <c r="L53" t="n">
-        <v>136.99</v>
+        <v>150.53</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>3.46</v>
       </c>
       <c r="F54" t="n">
-        <v>11.37</v>
+        <v>10.61</v>
       </c>
       <c r="G54" t="n">
-        <v>314.8</v>
+        <v>304.7</v>
       </c>
       <c r="H54" t="n">
-        <v>66.2</v>
+        <v>69.5</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>41.95</v>
+        <v>-44.77</v>
       </c>
       <c r="K54" t="n">
-        <v>88.77</v>
+        <v>145.09</v>
       </c>
       <c r="L54" t="n">
-        <v>98.18000000000001</v>
+        <v>151.84</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>3.41</v>
       </c>
       <c r="F55" t="n">
-        <v>11.8</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>318</v>
+        <v>313.1</v>
       </c>
       <c r="H55" t="n">
-        <v>64.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-135.71</v>
+        <v>-165.49</v>
       </c>
       <c r="K55" t="n">
-        <v>-42.35</v>
+        <v>-9.84</v>
       </c>
       <c r="L55" t="n">
-        <v>142.17</v>
+        <v>165.78</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>3.65</v>
       </c>
       <c r="F56" t="n">
-        <v>11.53</v>
+        <v>13.18</v>
       </c>
       <c r="G56" t="n">
-        <v>319.4</v>
+        <v>307.7</v>
       </c>
       <c r="H56" t="n">
-        <v>70.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-282.91</v>
+        <v>-348.35</v>
       </c>
       <c r="K56" t="n">
-        <v>53.91</v>
+        <v>79.44</v>
       </c>
       <c r="L56" t="n">
-        <v>288</v>
+        <v>357.3</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>3.66</v>
       </c>
       <c r="F57" t="n">
-        <v>11.38</v>
+        <v>13.45</v>
       </c>
       <c r="G57" t="n">
-        <v>304.7</v>
+        <v>304.9</v>
       </c>
       <c r="H57" t="n">
-        <v>66.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>220.7</v>
+        <v>250.76</v>
       </c>
       <c r="K57" t="n">
-        <v>99</v>
+        <v>165.79</v>
       </c>
       <c r="L57" t="n">
-        <v>241.89</v>
+        <v>300.61</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>3.82</v>
       </c>
       <c r="F58" t="n">
-        <v>11.91</v>
+        <v>10.63</v>
       </c>
       <c r="G58" t="n">
-        <v>305.5</v>
+        <v>315.4</v>
       </c>
       <c r="H58" t="n">
-        <v>63.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-269.39</v>
+        <v>-323.05</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.13</v>
+        <v>-142.6</v>
       </c>
       <c r="L58" t="n">
-        <v>311.36</v>
+        <v>353.12</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>4.04</v>
       </c>
       <c r="F59" t="n">
-        <v>11.59</v>
+        <v>13.45</v>
       </c>
       <c r="G59" t="n">
-        <v>314.2</v>
+        <v>309</v>
       </c>
       <c r="H59" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.94</v>
+        <v>-55.21</v>
       </c>
       <c r="K59" t="n">
-        <v>45.16</v>
+        <v>57.2</v>
       </c>
       <c r="L59" t="n">
-        <v>62.31</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>3.45</v>
       </c>
       <c r="F60" t="n">
-        <v>11.81</v>
+        <v>10.89</v>
       </c>
       <c r="G60" t="n">
-        <v>311.4</v>
+        <v>313.4</v>
       </c>
       <c r="H60" t="n">
-        <v>66.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.54</v>
+        <v>-34.38</v>
       </c>
       <c r="K60" t="n">
-        <v>35.96</v>
+        <v>49.11</v>
       </c>
       <c r="L60" t="n">
-        <v>43.53</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.85</v>
       </c>
       <c r="F61" t="n">
-        <v>11.17</v>
+        <v>11.02</v>
       </c>
       <c r="G61" t="n">
-        <v>316.6</v>
+        <v>300.5</v>
       </c>
       <c r="H61" t="n">
-        <v>68</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-58.67</v>
+        <v>-73.22</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.77</v>
+        <v>-17.37</v>
       </c>
       <c r="L61" t="n">
-        <v>60.5</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>2.85</v>
       </c>
       <c r="F62" t="n">
-        <v>11.25</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>292.4</v>
+        <v>302.3</v>
       </c>
       <c r="H62" t="n">
-        <v>67</v>
+        <v>58.3</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-88.95</v>
+        <v>-106.4</v>
       </c>
       <c r="K62" t="n">
-        <v>48.49</v>
+        <v>58.55</v>
       </c>
       <c r="L62" t="n">
-        <v>101.31</v>
+        <v>121.44</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.75</v>
       </c>
       <c r="F63" t="n">
-        <v>11.62</v>
+        <v>10.46</v>
       </c>
       <c r="G63" t="n">
-        <v>305.9</v>
+        <v>309.7</v>
       </c>
       <c r="H63" t="n">
-        <v>69.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-10.11</v>
+        <v>-14.84</v>
       </c>
       <c r="K63" t="n">
-        <v>78.64</v>
+        <v>90.63</v>
       </c>
       <c r="L63" t="n">
-        <v>79.29000000000001</v>
+        <v>91.84</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>3.73</v>
       </c>
       <c r="F64" t="n">
-        <v>11.74</v>
+        <v>13.45</v>
       </c>
       <c r="G64" t="n">
-        <v>319.6</v>
+        <v>311.9</v>
       </c>
       <c r="H64" t="n">
-        <v>71.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I64" t="n">
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-58.56</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-20.53</v>
+        <v>-16.97</v>
       </c>
       <c r="L64" t="n">
-        <v>62.06</v>
+        <v>80.55</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>3.69</v>
       </c>
       <c r="F65" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
       <c r="G65" t="n">
-        <v>303.2</v>
+        <v>312.1</v>
       </c>
       <c r="H65" t="n">
-        <v>64.8</v>
+        <v>63.7</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>94.59</v>
+        <v>103.08</v>
       </c>
       <c r="K65" t="n">
-        <v>56.1</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>109.98</v>
+        <v>134.41</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>4.17</v>
       </c>
       <c r="F66" t="n">
-        <v>11.68</v>
+        <v>11.99</v>
       </c>
       <c r="G66" t="n">
-        <v>308.4</v>
+        <v>310.7</v>
       </c>
       <c r="H66" t="n">
-        <v>63.7</v>
+        <v>66.3</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>60.01</v>
+        <v>55.46</v>
       </c>
       <c r="K66" t="n">
-        <v>113.23</v>
+        <v>147.21</v>
       </c>
       <c r="L66" t="n">
-        <v>128.15</v>
+        <v>157.31</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>3.06</v>
       </c>
       <c r="F67" t="n">
-        <v>12.41</v>
+        <v>4.54</v>
       </c>
       <c r="G67" t="n">
-        <v>310.4</v>
+        <v>325.4</v>
       </c>
       <c r="H67" t="n">
         <v>67.3</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>79.36</v>
+        <v>83.66</v>
       </c>
       <c r="K67" t="n">
-        <v>-82.62</v>
+        <v>-81.56</v>
       </c>
       <c r="L67" t="n">
-        <v>114.56</v>
+        <v>116.84</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>3.34</v>
       </c>
       <c r="F68" t="n">
-        <v>11.55</v>
+        <v>13.45</v>
       </c>
       <c r="G68" t="n">
-        <v>303.9</v>
+        <v>308.1</v>
       </c>
       <c r="H68" t="n">
-        <v>73.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I68" t="n">
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-178.11</v>
+        <v>-227.45</v>
       </c>
       <c r="K68" t="n">
-        <v>52.55</v>
+        <v>81.27</v>
       </c>
       <c r="L68" t="n">
-        <v>185.7</v>
+        <v>241.54</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>3.78</v>
       </c>
       <c r="F69" t="n">
-        <v>11.54</v>
+        <v>10.13</v>
       </c>
       <c r="G69" t="n">
-        <v>310.6</v>
+        <v>308</v>
       </c>
       <c r="H69" t="n">
-        <v>68.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-193.69</v>
+        <v>-229.23</v>
       </c>
       <c r="K69" t="n">
-        <v>-63.04</v>
+        <v>-46.07</v>
       </c>
       <c r="L69" t="n">
-        <v>203.7</v>
+        <v>233.82</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>3.92</v>
       </c>
       <c r="F70" t="n">
-        <v>11.37</v>
+        <v>13.45</v>
       </c>
       <c r="G70" t="n">
-        <v>302</v>
+        <v>304.6</v>
       </c>
       <c r="H70" t="n">
-        <v>69</v>
+        <v>63.1</v>
       </c>
       <c r="I70" t="n">
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-238.05</v>
+        <v>-288.26</v>
       </c>
       <c r="K70" t="n">
-        <v>-43.6</v>
+        <v>-30.06</v>
       </c>
       <c r="L70" t="n">
-        <v>242.01</v>
+        <v>289.83</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>3.91</v>
       </c>
       <c r="F71" t="n">
-        <v>11.84</v>
+        <v>13.45</v>
       </c>
       <c r="G71" t="n">
-        <v>294.2</v>
+        <v>314</v>
       </c>
       <c r="H71" t="n">
-        <v>66.09999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.85</v>
+        <v>-30.23</v>
       </c>
       <c r="K71" t="n">
-        <v>-348.69</v>
+        <v>-374.99</v>
       </c>
       <c r="L71" t="n">
-        <v>348.78</v>
+        <v>376.21</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.65</v>
       </c>
       <c r="F72" t="n">
-        <v>11.68</v>
+        <v>13.45</v>
       </c>
       <c r="G72" t="n">
-        <v>309.2</v>
+        <v>310.8</v>
       </c>
       <c r="H72" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="I72" t="n">
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-110.96</v>
+        <v>-161.67</v>
       </c>
       <c r="K72" t="n">
-        <v>187.75</v>
+        <v>238.87</v>
       </c>
       <c r="L72" t="n">
-        <v>218.09</v>
+        <v>288.44</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.47</v>
       </c>
       <c r="F73" t="n">
-        <v>11.19</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>308.6</v>
+        <v>301.1</v>
       </c>
       <c r="H73" t="n">
-        <v>70.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-64.01000000000001</v>
+        <v>-131.98</v>
       </c>
       <c r="K73" t="n">
-        <v>-188.35</v>
+        <v>-175.61</v>
       </c>
       <c r="L73" t="n">
-        <v>198.93</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>4.1</v>
       </c>
       <c r="F74" t="n">
-        <v>11.34</v>
+        <v>10.72</v>
       </c>
       <c r="G74" t="n">
-        <v>318.4</v>
+        <v>304</v>
       </c>
       <c r="H74" t="n">
-        <v>61.2</v>
+        <v>71.3</v>
       </c>
       <c r="I74" t="n">
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-23.09</v>
+        <v>-26.48</v>
       </c>
       <c r="K74" t="n">
-        <v>-90.84999999999999</v>
+        <v>-99.34</v>
       </c>
       <c r="L74" t="n">
-        <v>93.73999999999999</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>4.42</v>
       </c>
       <c r="F75" t="n">
-        <v>10.81</v>
+        <v>13.45</v>
       </c>
       <c r="G75" t="n">
-        <v>299.9</v>
+        <v>293.4</v>
       </c>
       <c r="H75" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I75" t="n">
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-74.78</v>
+        <v>-83.68000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>72.68000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>104.28</v>
+        <v>116.11</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>3.97</v>
       </c>
       <c r="F76" t="n">
-        <v>11.4</v>
+        <v>12.46</v>
       </c>
       <c r="G76" t="n">
-        <v>329.2</v>
+        <v>305.2</v>
       </c>
       <c r="H76" t="n">
-        <v>65.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>41.51</v>
+        <v>50.95</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.25</v>
+        <v>-61.59</v>
       </c>
       <c r="L76" t="n">
-        <v>63.65</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>3.4</v>
       </c>
       <c r="F77" t="n">
-        <v>10.96</v>
+        <v>12.81</v>
       </c>
       <c r="G77" t="n">
-        <v>327.4</v>
+        <v>296.5</v>
       </c>
       <c r="H77" t="n">
-        <v>75</v>
+        <v>75.8</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-64.8</v>
+        <v>-86.22</v>
       </c>
       <c r="K77" t="n">
-        <v>-58.22</v>
+        <v>-73.52</v>
       </c>
       <c r="L77" t="n">
-        <v>87.12</v>
+        <v>113.31</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>3.58</v>
       </c>
       <c r="F78" t="n">
-        <v>12.26</v>
+        <v>9.99</v>
       </c>
       <c r="G78" t="n">
-        <v>292.2</v>
+        <v>322.4</v>
       </c>
       <c r="H78" t="n">
-        <v>63.2</v>
+        <v>58.2</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.57</v>
+        <v>-10.76</v>
       </c>
       <c r="K78" t="n">
-        <v>-79.05</v>
+        <v>-83.34</v>
       </c>
       <c r="L78" t="n">
-        <v>79.52</v>
+        <v>84.03</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>4.25</v>
       </c>
       <c r="F79" t="n">
-        <v>11.55</v>
+        <v>13.25</v>
       </c>
       <c r="G79" t="n">
-        <v>315.1</v>
+        <v>308.1</v>
       </c>
       <c r="H79" t="n">
-        <v>60.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>8.74</v>
+        <v>4.5</v>
       </c>
       <c r="K79" t="n">
-        <v>67.27</v>
+        <v>85.89</v>
       </c>
       <c r="L79" t="n">
-        <v>67.83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>3.88</v>
       </c>
       <c r="F80" t="n">
-        <v>12.3</v>
+        <v>13.45</v>
       </c>
       <c r="G80" t="n">
-        <v>318.4</v>
+        <v>323.2</v>
       </c>
       <c r="H80" t="n">
-        <v>69.7</v>
+        <v>71.3</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>84.58</v>
+        <v>90.63</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.73</v>
+        <v>-142.73</v>
       </c>
       <c r="L80" t="n">
-        <v>157.39</v>
+        <v>169.07</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>4.18</v>
       </c>
       <c r="F81" t="n">
-        <v>11.68</v>
+        <v>13.45</v>
       </c>
       <c r="G81" t="n">
-        <v>312.6</v>
+        <v>310.8</v>
       </c>
       <c r="H81" t="n">
-        <v>73.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I81" t="n">
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-58.37</v>
+        <v>-77.58</v>
       </c>
       <c r="K81" t="n">
-        <v>127.57</v>
+        <v>150.72</v>
       </c>
       <c r="L81" t="n">
-        <v>140.29</v>
+        <v>169.51</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.79</v>
       </c>
       <c r="F82" t="n">
-        <v>11.72</v>
+        <v>13.45</v>
       </c>
       <c r="G82" t="n">
-        <v>317.9</v>
+        <v>311.5</v>
       </c>
       <c r="H82" t="n">
-        <v>71.2</v>
+        <v>71</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-117.74</v>
+        <v>-147.56</v>
       </c>
       <c r="K82" t="n">
-        <v>-68.95999999999999</v>
+        <v>-69.73</v>
       </c>
       <c r="L82" t="n">
-        <v>136.45</v>
+        <v>163.21</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>3.91</v>
       </c>
       <c r="F83" t="n">
-        <v>11.98</v>
+        <v>13.45</v>
       </c>
       <c r="G83" t="n">
-        <v>321.5</v>
+        <v>316.8</v>
       </c>
       <c r="H83" t="n">
-        <v>68</v>
+        <v>72.8</v>
       </c>
       <c r="I83" t="n">
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-199.42</v>
+        <v>-250.76</v>
       </c>
       <c r="K83" t="n">
-        <v>-79.31</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>214.61</v>
+        <v>259.71</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>4.36</v>
       </c>
       <c r="F84" t="n">
-        <v>11.89</v>
+        <v>13.45</v>
       </c>
       <c r="G84" t="n">
-        <v>306.2</v>
+        <v>315.1</v>
       </c>
       <c r="H84" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>113.14</v>
+        <v>119.63</v>
       </c>
       <c r="K84" t="n">
-        <v>-148.97</v>
+        <v>-159.8</v>
       </c>
       <c r="L84" t="n">
-        <v>187.06</v>
+        <v>199.62</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>3.11</v>
       </c>
       <c r="F85" t="n">
-        <v>11.95</v>
+        <v>10.93</v>
       </c>
       <c r="G85" t="n">
-        <v>296.2</v>
+        <v>316.2</v>
       </c>
       <c r="H85" t="n">
-        <v>68.09999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-45.48</v>
+        <v>-66.18000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>141.49</v>
+        <v>175.54</v>
       </c>
       <c r="L85" t="n">
-        <v>148.62</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>4.3</v>
       </c>
       <c r="F86" t="n">
-        <v>12.37</v>
+        <v>10.54</v>
       </c>
       <c r="G86" t="n">
-        <v>302</v>
+        <v>324.7</v>
       </c>
       <c r="H86" t="n">
-        <v>59</v>
+        <v>63.1</v>
       </c>
       <c r="I86" t="n">
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-28.69</v>
+        <v>-64.79000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-222.77</v>
+        <v>-226.88</v>
       </c>
       <c r="L86" t="n">
-        <v>224.61</v>
+        <v>235.95</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>3.63</v>
       </c>
       <c r="F87" t="n">
-        <v>11.95</v>
+        <v>13.45</v>
       </c>
       <c r="G87" t="n">
-        <v>315.6</v>
+        <v>316.2</v>
       </c>
       <c r="H87" t="n">
-        <v>70.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-207.35</v>
+        <v>-265.73</v>
       </c>
       <c r="K87" t="n">
-        <v>-201.64</v>
+        <v>-203.01</v>
       </c>
       <c r="L87" t="n">
-        <v>289.22</v>
+        <v>334.4</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>4.36</v>
       </c>
       <c r="F88" t="n">
-        <v>11.8</v>
+        <v>13.45</v>
       </c>
       <c r="G88" t="n">
-        <v>312.9</v>
+        <v>313.3</v>
       </c>
       <c r="H88" t="n">
-        <v>69.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>158.52</v>
+        <v>161.19</v>
       </c>
       <c r="K88" t="n">
-        <v>-182.37</v>
+        <v>-195.68</v>
       </c>
       <c r="L88" t="n">
-        <v>241.64</v>
+        <v>253.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>29.01</v>
+        <v>33.01</v>
       </c>
       <c r="K14" t="n">
-        <v>49.5</v>
+        <v>56.33</v>
       </c>
       <c r="L14" t="n">
-        <v>57.38</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>28.89</v>
+        <v>32.88</v>
       </c>
       <c r="K15" t="n">
-        <v>-80.33</v>
+        <v>-91.41</v>
       </c>
       <c r="L15" t="n">
-        <v>85.37</v>
+        <v>97.14</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-58.29</v>
+        <v>-63.59</v>
       </c>
       <c r="K16" t="n">
-        <v>-28.99</v>
+        <v>-31.62</v>
       </c>
       <c r="L16" t="n">
-        <v>65.09999999999999</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-81.88</v>
+        <v>-89.23</v>
       </c>
       <c r="K17" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="L17" t="n">
-        <v>81.95</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>59.22</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-67.27</v>
+        <v>-75.53</v>
       </c>
       <c r="L18" t="n">
-        <v>89.62</v>
+        <v>100.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.68</v>
+        <v>-47.37</v>
       </c>
       <c r="K19" t="n">
-        <v>84.06999999999999</v>
+        <v>95.55</v>
       </c>
       <c r="L19" t="n">
-        <v>93.83</v>
+        <v>106.65</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-126.9</v>
+        <v>-138.43</v>
       </c>
       <c r="K20" t="n">
-        <v>104.08</v>
+        <v>113.54</v>
       </c>
       <c r="L20" t="n">
-        <v>164.12</v>
+        <v>179.04</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>103.78</v>
+        <v>113.22</v>
       </c>
       <c r="K21" t="n">
-        <v>55.1</v>
+        <v>60.11</v>
       </c>
       <c r="L21" t="n">
-        <v>117.5</v>
+        <v>128.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>92.26000000000001</v>
+        <v>103.58</v>
       </c>
       <c r="K22" t="n">
-        <v>-59.61</v>
+        <v>-66.93000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>109.84</v>
+        <v>123.32</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>143.46</v>
+        <v>163.43</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.52</v>
+        <v>-98.56</v>
       </c>
       <c r="L23" t="n">
-        <v>167.53</v>
+        <v>190.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-152.3</v>
+        <v>-171.03</v>
       </c>
       <c r="K24" t="n">
-        <v>163.07</v>
+        <v>183.13</v>
       </c>
       <c r="L24" t="n">
-        <v>223.13</v>
+        <v>250.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>45.93</v>
+        <v>52.28</v>
       </c>
       <c r="K25" t="n">
-        <v>256.13</v>
+        <v>291.53</v>
       </c>
       <c r="L25" t="n">
-        <v>260.22</v>
+        <v>296.18</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-42.25</v>
+        <v>-47.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-162.94</v>
+        <v>-182.95</v>
       </c>
       <c r="L26" t="n">
-        <v>168.33</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>59.04</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-254.86</v>
+        <v>-290.01</v>
       </c>
       <c r="L27" t="n">
-        <v>261.61</v>
+        <v>297.69</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>321.82</v>
+        <v>358.01</v>
       </c>
       <c r="K28" t="n">
-        <v>89.25</v>
+        <v>99.28</v>
       </c>
       <c r="L28" t="n">
-        <v>333.97</v>
+        <v>371.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.970000000000001</v>
+        <v>-11.33</v>
       </c>
       <c r="K29" t="n">
-        <v>95.81</v>
+        <v>108.91</v>
       </c>
       <c r="L29" t="n">
-        <v>96.33</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-86.56</v>
+        <v>-98.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-46.7</v>
+        <v>-53.11</v>
       </c>
       <c r="L30" t="n">
-        <v>98.34999999999999</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>72</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>66.12</v>
+        <v>75.17</v>
       </c>
       <c r="L31" t="n">
-        <v>97.76000000000001</v>
+        <v>111.13</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-19.71</v>
+        <v>-21.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-77.06999999999999</v>
+        <v>-84.06999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>79.55</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-72.34999999999999</v>
+        <v>-82.27</v>
       </c>
       <c r="K33" t="n">
-        <v>77.38</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>105.93</v>
+        <v>120.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>123.51</v>
+        <v>135.72</v>
       </c>
       <c r="K34" t="n">
-        <v>45.07</v>
+        <v>49.52</v>
       </c>
       <c r="L34" t="n">
-        <v>131.47</v>
+        <v>144.47</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-34.49</v>
+        <v>-39.25</v>
       </c>
       <c r="K35" t="n">
-        <v>-144.98</v>
+        <v>-164.97</v>
       </c>
       <c r="L35" t="n">
-        <v>149.02</v>
+        <v>169.58</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>146.31</v>
+        <v>166.49</v>
       </c>
       <c r="K36" t="n">
-        <v>-30.65</v>
+        <v>-34.88</v>
       </c>
       <c r="L36" t="n">
-        <v>149.48</v>
+        <v>170.1</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-171.03</v>
+        <v>-194.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-159.77</v>
+        <v>-181.52</v>
       </c>
       <c r="L37" t="n">
-        <v>234.05</v>
+        <v>265.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>113.98</v>
+        <v>128.04</v>
       </c>
       <c r="K38" t="n">
-        <v>226.94</v>
+        <v>254.94</v>
       </c>
       <c r="L38" t="n">
-        <v>253.95</v>
+        <v>285.28</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>149.36</v>
+        <v>162.94</v>
       </c>
       <c r="K39" t="n">
-        <v>-122.43</v>
+        <v>-133.56</v>
       </c>
       <c r="L39" t="n">
-        <v>193.13</v>
+        <v>210.68</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-126.82</v>
+        <v>-138.35</v>
       </c>
       <c r="K40" t="n">
-        <v>7.49</v>
+        <v>8.17</v>
       </c>
       <c r="L40" t="n">
-        <v>127.04</v>
+        <v>138.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-205.64</v>
+        <v>-235</v>
       </c>
       <c r="K41" t="n">
-        <v>131.86</v>
+        <v>150.68</v>
       </c>
       <c r="L41" t="n">
-        <v>244.29</v>
+        <v>279.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>11.87</v>
+        <v>13.38</v>
       </c>
       <c r="K42" t="n">
-        <v>-216.04</v>
+        <v>-243.68</v>
       </c>
       <c r="L42" t="n">
-        <v>216.36</v>
+        <v>244.05</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-272.64</v>
+        <v>-307.78</v>
       </c>
       <c r="K43" t="n">
-        <v>-74.33</v>
+        <v>-83.91</v>
       </c>
       <c r="L43" t="n">
-        <v>282.59</v>
+        <v>319.01</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-14.84</v>
+        <v>-16.89</v>
       </c>
       <c r="K44" t="n">
-        <v>-90.2</v>
+        <v>-102.64</v>
       </c>
       <c r="L44" t="n">
-        <v>91.41</v>
+        <v>104.02</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>99.79000000000001</v>
+        <v>113.11</v>
       </c>
       <c r="K45" t="n">
-        <v>-94.31999999999999</v>
+        <v>-106.91</v>
       </c>
       <c r="L45" t="n">
-        <v>137.31</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-48.56</v>
+        <v>-54.34</v>
       </c>
       <c r="K46" t="n">
-        <v>-74.73999999999999</v>
+        <v>-83.64</v>
       </c>
       <c r="L46" t="n">
-        <v>89.13</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-108</v>
+        <v>-117.4</v>
       </c>
       <c r="K47" t="n">
-        <v>65.25</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>126.18</v>
+        <v>137.17</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.66</v>
+        <v>-79.27</v>
       </c>
       <c r="K48" t="n">
-        <v>-27.98</v>
+        <v>-31.84</v>
       </c>
       <c r="L48" t="n">
-        <v>75.06999999999999</v>
+        <v>85.42</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-18.86</v>
+        <v>-21.46</v>
       </c>
       <c r="K49" t="n">
-        <v>-149.75</v>
+        <v>-170.41</v>
       </c>
       <c r="L49" t="n">
-        <v>150.94</v>
+        <v>171.76</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>44.98</v>
+        <v>49.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-130.58</v>
+        <v>-144.58</v>
       </c>
       <c r="L50" t="n">
-        <v>138.11</v>
+        <v>152.91</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>8.32</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>162.8</v>
+        <v>180.25</v>
       </c>
       <c r="L51" t="n">
-        <v>163.02</v>
+        <v>180.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>89.73</v>
+        <v>102.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-82.90000000000001</v>
+        <v>-94.25</v>
       </c>
       <c r="L52" t="n">
-        <v>122.16</v>
+        <v>138.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>121.37</v>
+        <v>136.27</v>
       </c>
       <c r="K53" t="n">
-        <v>-89.05</v>
+        <v>-99.98</v>
       </c>
       <c r="L53" t="n">
-        <v>150.53</v>
+        <v>169.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-44.77</v>
+        <v>-50.96</v>
       </c>
       <c r="K54" t="n">
-        <v>145.09</v>
+        <v>165.14</v>
       </c>
       <c r="L54" t="n">
-        <v>151.84</v>
+        <v>172.83</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-165.49</v>
+        <v>-183.26</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.84</v>
+        <v>-10.89</v>
       </c>
       <c r="L55" t="n">
-        <v>165.78</v>
+        <v>183.58</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-348.35</v>
+        <v>-386.96</v>
       </c>
       <c r="K56" t="n">
-        <v>79.44</v>
+        <v>88.25</v>
       </c>
       <c r="L56" t="n">
-        <v>357.3</v>
+        <v>396.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>250.76</v>
+        <v>286.32</v>
       </c>
       <c r="K57" t="n">
-        <v>165.79</v>
+        <v>189.3</v>
       </c>
       <c r="L57" t="n">
-        <v>300.61</v>
+        <v>343.24</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-323.05</v>
+        <v>-364.38</v>
       </c>
       <c r="K58" t="n">
-        <v>-142.6</v>
+        <v>-160.85</v>
       </c>
       <c r="L58" t="n">
-        <v>353.12</v>
+        <v>398.3</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.21</v>
+        <v>-62.58</v>
       </c>
       <c r="K59" t="n">
-        <v>57.2</v>
+        <v>64.84</v>
       </c>
       <c r="L59" t="n">
-        <v>79.5</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.38</v>
+        <v>-39.08</v>
       </c>
       <c r="K60" t="n">
-        <v>49.11</v>
+        <v>55.83</v>
       </c>
       <c r="L60" t="n">
-        <v>59.95</v>
+        <v>68.15000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-73.22</v>
+        <v>-83.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.37</v>
+        <v>-19.71</v>
       </c>
       <c r="L61" t="n">
-        <v>75.26000000000001</v>
+        <v>85.39</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-106.4</v>
+        <v>-121.07</v>
       </c>
       <c r="K62" t="n">
-        <v>58.55</v>
+        <v>66.62</v>
       </c>
       <c r="L62" t="n">
-        <v>121.44</v>
+        <v>138.19</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.84</v>
+        <v>-16.85</v>
       </c>
       <c r="K63" t="n">
-        <v>90.63</v>
+        <v>102.88</v>
       </c>
       <c r="L63" t="n">
-        <v>91.84</v>
+        <v>104.25</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-78.73999999999999</v>
+        <v>-89.39</v>
       </c>
       <c r="K64" t="n">
-        <v>-16.97</v>
+        <v>-19.26</v>
       </c>
       <c r="L64" t="n">
-        <v>80.55</v>
+        <v>91.44</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>103.08</v>
+        <v>117.21</v>
       </c>
       <c r="K65" t="n">
-        <v>86.26000000000001</v>
+        <v>98.08</v>
       </c>
       <c r="L65" t="n">
-        <v>134.41</v>
+        <v>152.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>55.46</v>
+        <v>63.02</v>
       </c>
       <c r="K66" t="n">
-        <v>147.21</v>
+        <v>167.26</v>
       </c>
       <c r="L66" t="n">
-        <v>157.31</v>
+        <v>178.74</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>83.66</v>
+        <v>95.2</v>
       </c>
       <c r="K67" t="n">
-        <v>-81.56</v>
+        <v>-92.81</v>
       </c>
       <c r="L67" t="n">
-        <v>116.84</v>
+        <v>132.95</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-227.45</v>
+        <v>-258.85</v>
       </c>
       <c r="K68" t="n">
-        <v>81.27</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>241.54</v>
+        <v>274.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-229.23</v>
+        <v>-261.01</v>
       </c>
       <c r="K69" t="n">
-        <v>-46.07</v>
+        <v>-52.45</v>
       </c>
       <c r="L69" t="n">
-        <v>233.82</v>
+        <v>266.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-288.26</v>
+        <v>-328.28</v>
       </c>
       <c r="K70" t="n">
-        <v>-30.06</v>
+        <v>-34.23</v>
       </c>
       <c r="L70" t="n">
-        <v>289.83</v>
+        <v>330.06</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-30.23</v>
+        <v>-34.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-374.99</v>
+        <v>-423.24</v>
       </c>
       <c r="L71" t="n">
-        <v>376.21</v>
+        <v>424.61</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-161.67</v>
+        <v>-184.58</v>
       </c>
       <c r="K72" t="n">
-        <v>238.87</v>
+        <v>272.72</v>
       </c>
       <c r="L72" t="n">
-        <v>288.44</v>
+        <v>329.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-131.98</v>
+        <v>-148.47</v>
       </c>
       <c r="K73" t="n">
-        <v>-175.61</v>
+        <v>-197.55</v>
       </c>
       <c r="L73" t="n">
-        <v>219.68</v>
+        <v>247.13</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-26.48</v>
+        <v>-29.2</v>
       </c>
       <c r="K74" t="n">
-        <v>-99.34</v>
+        <v>-109.53</v>
       </c>
       <c r="L74" t="n">
-        <v>102.81</v>
+        <v>113.35</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.68000000000001</v>
+        <v>-94.7</v>
       </c>
       <c r="K75" t="n">
-        <v>80.48999999999999</v>
+        <v>91.09</v>
       </c>
       <c r="L75" t="n">
-        <v>116.11</v>
+        <v>131.39</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>50.95</v>
+        <v>57.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-61.59</v>
+        <v>-69.84</v>
       </c>
       <c r="L76" t="n">
-        <v>79.93000000000001</v>
+        <v>90.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-86.22</v>
+        <v>-98.03</v>
       </c>
       <c r="K77" t="n">
-        <v>-73.52</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>113.31</v>
+        <v>128.84</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-10.76</v>
+        <v>-11.72</v>
       </c>
       <c r="K78" t="n">
-        <v>-83.34</v>
+        <v>-90.77</v>
       </c>
       <c r="L78" t="n">
-        <v>84.03</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>4.5</v>
+        <v>5.03</v>
       </c>
       <c r="K79" t="n">
-        <v>85.89</v>
+        <v>95.98</v>
       </c>
       <c r="L79" t="n">
-        <v>86</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>90.63</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-142.73</v>
+        <v>-155.53</v>
       </c>
       <c r="L80" t="n">
-        <v>169.07</v>
+        <v>184.24</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-77.58</v>
+        <v>-88.15000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>150.72</v>
+        <v>171.24</v>
       </c>
       <c r="L81" t="n">
-        <v>169.51</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-147.56</v>
+        <v>-165.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-69.73</v>
+        <v>-78.22</v>
       </c>
       <c r="L82" t="n">
-        <v>163.21</v>
+        <v>183.08</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-250.76</v>
+        <v>-285.57</v>
       </c>
       <c r="K83" t="n">
-        <v>-67.59999999999999</v>
+        <v>-76.98</v>
       </c>
       <c r="L83" t="n">
-        <v>259.71</v>
+        <v>295.76</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>119.63</v>
+        <v>136.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-159.8</v>
+        <v>-182.07</v>
       </c>
       <c r="L84" t="n">
-        <v>199.62</v>
+        <v>227.44</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-66.18000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="K85" t="n">
-        <v>175.54</v>
+        <v>197.1</v>
       </c>
       <c r="L85" t="n">
-        <v>187.6</v>
+        <v>210.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-64.79000000000001</v>
+        <v>-74.70999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-226.88</v>
+        <v>-261.63</v>
       </c>
       <c r="L86" t="n">
-        <v>235.95</v>
+        <v>272.08</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-265.73</v>
+        <v>-295.13</v>
       </c>
       <c r="K87" t="n">
-        <v>-203.01</v>
+        <v>-225.48</v>
       </c>
       <c r="L87" t="n">
-        <v>334.4</v>
+        <v>371.41</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>161.19</v>
+        <v>178.28</v>
       </c>
       <c r="K88" t="n">
-        <v>-195.68</v>
+        <v>-216.43</v>
       </c>
       <c r="L88" t="n">
-        <v>253.52</v>
+        <v>280.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="F14" t="n">
-        <v>4.33</v>
+        <v>4.06</v>
       </c>
       <c r="G14" t="n">
-        <v>306.8</v>
+        <v>316.1</v>
       </c>
       <c r="H14" t="n">
-        <v>68.8</v>
+        <v>58</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>33.01</v>
+        <v>-58.13</v>
       </c>
       <c r="K14" t="n">
-        <v>56.33</v>
+        <v>-36.19</v>
       </c>
       <c r="L14" t="n">
-        <v>65.29000000000001</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:29:04</t>
+          <t>05:29:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.84</v>
+        <v>3.23</v>
       </c>
       <c r="F15" t="n">
-        <v>6.74</v>
+        <v>8.9</v>
       </c>
       <c r="G15" t="n">
-        <v>317</v>
+        <v>305.3</v>
       </c>
       <c r="H15" t="n">
-        <v>72.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>32.88</v>
+        <v>-65.76000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-91.41</v>
+        <v>-8.16</v>
       </c>
       <c r="L15" t="n">
-        <v>97.14</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:30:49</t>
+          <t>05:31:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="F16" t="n">
-        <v>10.28</v>
+        <v>11.59</v>
       </c>
       <c r="G16" t="n">
-        <v>311.3</v>
+        <v>325.4</v>
       </c>
       <c r="H16" t="n">
-        <v>62.8</v>
+        <v>62.7</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-63.59</v>
+        <v>15.75</v>
       </c>
       <c r="K16" t="n">
-        <v>-31.62</v>
+        <v>-50.35</v>
       </c>
       <c r="L16" t="n">
-        <v>71.02</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:36:13</t>
+          <t>05:36:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="F17" t="n">
-        <v>10.73</v>
+        <v>7.26</v>
       </c>
       <c r="G17" t="n">
-        <v>308</v>
+        <v>290.6</v>
       </c>
       <c r="H17" t="n">
-        <v>67.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-89.23</v>
+        <v>25.82</v>
       </c>
       <c r="K17" t="n">
-        <v>3.78</v>
+        <v>-86.20999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>89.31</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:37:27</t>
+          <t>05:37:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="F18" t="n">
-        <v>8.130000000000001</v>
+        <v>11.26</v>
       </c>
       <c r="G18" t="n">
-        <v>295.6</v>
+        <v>310.4</v>
       </c>
       <c r="H18" t="n">
-        <v>64</v>
+        <v>32.2</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>66.48999999999999</v>
+        <v>16.82</v>
       </c>
       <c r="K18" t="n">
-        <v>-75.53</v>
+        <v>-90.53</v>
       </c>
       <c r="L18" t="n">
-        <v>100.63</v>
+        <v>92.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:39:47</t>
+          <t>05:39:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="F19" t="n">
-        <v>10.06</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>316.4</v>
+        <v>314.4</v>
       </c>
       <c r="H19" t="n">
-        <v>66.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>-47.37</v>
+        <v>94.75</v>
       </c>
       <c r="K19" t="n">
-        <v>95.55</v>
+        <v>37.13</v>
       </c>
       <c r="L19" t="n">
-        <v>106.65</v>
+        <v>101.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:43:46</t>
+          <t>05:43:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.27</v>
+        <v>4.32</v>
       </c>
       <c r="F20" t="n">
-        <v>10.49</v>
+        <v>10.3</v>
       </c>
       <c r="G20" t="n">
-        <v>319.6</v>
+        <v>302.9</v>
       </c>
       <c r="H20" t="n">
-        <v>71.7</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>-138.43</v>
+        <v>2.96</v>
       </c>
       <c r="K20" t="n">
-        <v>113.54</v>
+        <v>149.3</v>
       </c>
       <c r="L20" t="n">
-        <v>179.04</v>
+        <v>149.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:45:24</t>
+          <t>05:45:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.14</v>
+        <v>3.31</v>
       </c>
       <c r="F21" t="n">
-        <v>8.199999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="G21" t="n">
-        <v>317.3</v>
+        <v>314.5</v>
       </c>
       <c r="H21" t="n">
-        <v>66.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>113.22</v>
+        <v>80.87</v>
       </c>
       <c r="K21" t="n">
-        <v>60.11</v>
+        <v>21.77</v>
       </c>
       <c r="L21" t="n">
-        <v>128.19</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:47:44</t>
+          <t>05:47:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="F22" t="n">
-        <v>9.51</v>
+        <v>10.6</v>
       </c>
       <c r="G22" t="n">
-        <v>314.2</v>
+        <v>305.7</v>
       </c>
       <c r="H22" t="n">
-        <v>67.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>103.58</v>
+        <v>-181.81</v>
       </c>
       <c r="K22" t="n">
-        <v>-66.93000000000001</v>
+        <v>35.54</v>
       </c>
       <c r="L22" t="n">
-        <v>123.32</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:52:20</t>
+          <t>05:51:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.23</v>
+        <v>3.32</v>
       </c>
       <c r="F23" t="n">
-        <v>13.45</v>
+        <v>9.1</v>
       </c>
       <c r="G23" t="n">
-        <v>317.8</v>
+        <v>324.9</v>
       </c>
       <c r="H23" t="n">
-        <v>72.8</v>
+        <v>56</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>163.43</v>
+        <v>-141.7</v>
       </c>
       <c r="K23" t="n">
-        <v>-98.56</v>
+        <v>-71.76000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>190.85</v>
+        <v>158.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:54:47</t>
+          <t>05:53:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="F24" t="n">
-        <v>9.779999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="G24" t="n">
-        <v>313.9</v>
+        <v>307.5</v>
       </c>
       <c r="H24" t="n">
-        <v>66</v>
+        <v>27.5</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J24" t="n">
-        <v>-171.03</v>
+        <v>173.06</v>
       </c>
       <c r="K24" t="n">
-        <v>183.13</v>
+        <v>7.47</v>
       </c>
       <c r="L24" t="n">
-        <v>250.58</v>
+        <v>173.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:56:30</t>
+          <t>05:56:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.45</v>
+        <v>2.81</v>
       </c>
       <c r="F25" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G25" t="n">
-        <v>316.7</v>
+        <v>317</v>
       </c>
       <c r="H25" t="n">
-        <v>71.3</v>
+        <v>58.9</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>52.28</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>291.53</v>
+        <v>-69.59</v>
       </c>
       <c r="L25" t="n">
-        <v>296.18</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:01:25</t>
+          <t>05:59:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="F26" t="n">
-        <v>5.4</v>
+        <v>13.45</v>
       </c>
       <c r="G26" t="n">
-        <v>310.4</v>
+        <v>300.4</v>
       </c>
       <c r="H26" t="n">
-        <v>71.5</v>
+        <v>45.2</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>-47.44</v>
+        <v>-132.03</v>
       </c>
       <c r="K26" t="n">
-        <v>-182.95</v>
+        <v>174.73</v>
       </c>
       <c r="L26" t="n">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:03:24</t>
+          <t>06:01:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="F27" t="n">
-        <v>8.619999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>311.9</v>
+        <v>313.5</v>
       </c>
       <c r="H27" t="n">
-        <v>67.09999999999999</v>
+        <v>58.9</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>67.18000000000001</v>
+        <v>-8.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-290.01</v>
+        <v>228.2</v>
       </c>
       <c r="L27" t="n">
-        <v>297.69</v>
+        <v>228.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:05:37</t>
+          <t>06:03:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.85</v>
+        <v>4.85</v>
       </c>
       <c r="F28" t="n">
-        <v>11.32</v>
+        <v>12.4</v>
       </c>
       <c r="G28" t="n">
-        <v>327.1</v>
+        <v>311.3</v>
       </c>
       <c r="H28" t="n">
-        <v>64.09999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>358.01</v>
+        <v>-362.9</v>
       </c>
       <c r="K28" t="n">
-        <v>99.28</v>
+        <v>262.56</v>
       </c>
       <c r="L28" t="n">
-        <v>371.52</v>
+        <v>447.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:15:20</t>
+          <t>06:13:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.48</v>
+        <v>3.63</v>
       </c>
       <c r="F29" t="n">
-        <v>10.42</v>
+        <v>12.49</v>
       </c>
       <c r="G29" t="n">
-        <v>326.6</v>
+        <v>310.8</v>
       </c>
       <c r="H29" t="n">
-        <v>68.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.33</v>
+        <v>46.03</v>
       </c>
       <c r="K29" t="n">
-        <v>108.91</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>109.49</v>
+        <v>84.65000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:17:21</t>
+          <t>06:14:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="F30" t="n">
-        <v>9.970000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="G30" t="n">
-        <v>304.9</v>
+        <v>315.2</v>
       </c>
       <c r="H30" t="n">
-        <v>68.3</v>
+        <v>62.6</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>-98.45</v>
+        <v>-26.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-53.11</v>
+        <v>-42.44</v>
       </c>
       <c r="L30" t="n">
-        <v>111.86</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:18:24</t>
+          <t>06:16:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="F31" t="n">
-        <v>12.61</v>
+        <v>11.44</v>
       </c>
       <c r="G31" t="n">
-        <v>304.3</v>
+        <v>315.3</v>
       </c>
       <c r="H31" t="n">
-        <v>61.6</v>
+        <v>58.9</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>81.84999999999999</v>
+        <v>42.19</v>
       </c>
       <c r="K31" t="n">
-        <v>75.17</v>
+        <v>-78.15000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>111.13</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:24:00</t>
+          <t>06:20:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="F32" t="n">
-        <v>12.82</v>
+        <v>8.18</v>
       </c>
       <c r="G32" t="n">
-        <v>302.2</v>
+        <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>64.8</v>
+        <v>55.6</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>-21.5</v>
+        <v>-38.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-84.06999999999999</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>86.78</v>
+        <v>95.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:25:42</t>
+          <t>06:21:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="F33" t="n">
-        <v>9.68</v>
+        <v>7.98</v>
       </c>
       <c r="G33" t="n">
-        <v>318.8</v>
+        <v>309.1</v>
       </c>
       <c r="H33" t="n">
-        <v>59.6</v>
+        <v>57.8</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-82.27</v>
+        <v>-82.7</v>
       </c>
       <c r="K33" t="n">
-        <v>87.98999999999999</v>
+        <v>42.4</v>
       </c>
       <c r="L33" t="n">
-        <v>120.46</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:27:48</t>
+          <t>06:24:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.89</v>
+        <v>2.75</v>
       </c>
       <c r="F34" t="n">
-        <v>13.45</v>
+        <v>11.98</v>
       </c>
       <c r="G34" t="n">
-        <v>310.1</v>
+        <v>314.8</v>
       </c>
       <c r="H34" t="n">
-        <v>66.8</v>
+        <v>42.2</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>135.72</v>
+        <v>14.68</v>
       </c>
       <c r="K34" t="n">
-        <v>49.52</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>144.47</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:31:47</t>
+          <t>06:28:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>13.45</v>
       </c>
       <c r="G35" t="n">
-        <v>292.2</v>
+        <v>323.1</v>
       </c>
       <c r="H35" t="n">
-        <v>62.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-39.25</v>
+        <v>-105.8</v>
       </c>
       <c r="K35" t="n">
-        <v>-164.97</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>169.58</v>
+        <v>138.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:33:35</t>
+          <t>06:30:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="F36" t="n">
-        <v>9.57</v>
+        <v>12.74</v>
       </c>
       <c r="G36" t="n">
-        <v>319.3</v>
+        <v>304.1</v>
       </c>
       <c r="H36" t="n">
-        <v>64.3</v>
+        <v>50.9</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J36" t="n">
-        <v>166.49</v>
+        <v>-66.52</v>
       </c>
       <c r="K36" t="n">
-        <v>-34.88</v>
+        <v>-22.67</v>
       </c>
       <c r="L36" t="n">
-        <v>170.1</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:34:22</t>
+          <t>06:32:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.22</v>
+        <v>3.39</v>
       </c>
       <c r="F37" t="n">
-        <v>12.34</v>
+        <v>9.66</v>
       </c>
       <c r="G37" t="n">
-        <v>306.8</v>
+        <v>320.9</v>
       </c>
       <c r="H37" t="n">
-        <v>60.4</v>
+        <v>32.1</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-194.31</v>
+        <v>-126.26</v>
       </c>
       <c r="K37" t="n">
-        <v>-181.52</v>
+        <v>34.17</v>
       </c>
       <c r="L37" t="n">
-        <v>265.9</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:38:57</t>
+          <t>06:36:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.66</v>
+        <v>3.05</v>
       </c>
       <c r="F38" t="n">
-        <v>11.13</v>
+        <v>8.99</v>
       </c>
       <c r="G38" t="n">
-        <v>314.9</v>
+        <v>315.7</v>
       </c>
       <c r="H38" t="n">
-        <v>71.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>128.04</v>
+        <v>68.3</v>
       </c>
       <c r="K38" t="n">
-        <v>254.94</v>
+        <v>-190.44</v>
       </c>
       <c r="L38" t="n">
-        <v>285.28</v>
+        <v>202.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:41:00</t>
+          <t>06:37:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="F39" t="n">
-        <v>8.92</v>
+        <v>13.41</v>
       </c>
       <c r="G39" t="n">
-        <v>306.9</v>
+        <v>328.5</v>
       </c>
       <c r="H39" t="n">
-        <v>61.7</v>
+        <v>37.8</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>162.94</v>
+        <v>174.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-133.56</v>
+        <v>26.19</v>
       </c>
       <c r="L39" t="n">
-        <v>210.68</v>
+        <v>176.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:43:23</t>
+          <t>06:39:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.55</v>
+        <v>3.22</v>
       </c>
       <c r="F40" t="n">
-        <v>5.66</v>
+        <v>9.74</v>
       </c>
       <c r="G40" t="n">
-        <v>316.5</v>
+        <v>307.6</v>
       </c>
       <c r="H40" t="n">
-        <v>67.09999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>-138.35</v>
+        <v>-323.3</v>
       </c>
       <c r="K40" t="n">
-        <v>8.17</v>
+        <v>-142.83</v>
       </c>
       <c r="L40" t="n">
-        <v>138.59</v>
+        <v>353.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:46:29</t>
+          <t>06:44:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="F41" t="n">
-        <v>13.45</v>
+        <v>12.22</v>
       </c>
       <c r="G41" t="n">
-        <v>298.9</v>
+        <v>324.7</v>
       </c>
       <c r="H41" t="n">
-        <v>70.09999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>-235</v>
+        <v>-110.24</v>
       </c>
       <c r="K41" t="n">
-        <v>150.68</v>
+        <v>283.03</v>
       </c>
       <c r="L41" t="n">
-        <v>279.16</v>
+        <v>303.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:48:00</t>
+          <t>06:45:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="F42" t="n">
-        <v>12.16</v>
+        <v>13.45</v>
       </c>
       <c r="G42" t="n">
-        <v>308.8</v>
+        <v>312.1</v>
       </c>
       <c r="H42" t="n">
-        <v>68.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J42" t="n">
-        <v>13.38</v>
+        <v>-24.41</v>
       </c>
       <c r="K42" t="n">
-        <v>-243.68</v>
+        <v>-326.03</v>
       </c>
       <c r="L42" t="n">
-        <v>244.05</v>
+        <v>326.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:49:40</t>
+          <t>06:47:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.94</v>
+        <v>3.24</v>
       </c>
       <c r="F43" t="n">
-        <v>10.96</v>
+        <v>9.93</v>
       </c>
       <c r="G43" t="n">
-        <v>314.8</v>
+        <v>316.6</v>
       </c>
       <c r="H43" t="n">
-        <v>66.8</v>
+        <v>65.2</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>-307.78</v>
+        <v>-231.35</v>
       </c>
       <c r="K43" t="n">
-        <v>-83.91</v>
+        <v>-158.12</v>
       </c>
       <c r="L43" t="n">
-        <v>319.01</v>
+        <v>280.22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:01:08</t>
+          <t>06:55:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="F44" t="n">
-        <v>9.84</v>
+        <v>10.89</v>
       </c>
       <c r="G44" t="n">
-        <v>307.9</v>
+        <v>306.9</v>
       </c>
       <c r="H44" t="n">
-        <v>65.7</v>
+        <v>50.8</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.89</v>
+        <v>-58</v>
       </c>
       <c r="K44" t="n">
-        <v>-102.64</v>
+        <v>28.84</v>
       </c>
       <c r="L44" t="n">
-        <v>104.02</v>
+        <v>64.78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:02:55</t>
+          <t>06:57:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.06</v>
+        <v>3.79</v>
       </c>
       <c r="F45" t="n">
-        <v>12.17</v>
+        <v>13.45</v>
       </c>
       <c r="G45" t="n">
-        <v>315.9</v>
+        <v>307.2</v>
       </c>
       <c r="H45" t="n">
-        <v>71.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>113.11</v>
+        <v>-55.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-106.91</v>
+        <v>-37.51</v>
       </c>
       <c r="L45" t="n">
-        <v>155.64</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:03:51</t>
+          <t>06:58:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.95</v>
+        <v>3.36</v>
       </c>
       <c r="F46" t="n">
-        <v>13.45</v>
+        <v>11.19</v>
       </c>
       <c r="G46" t="n">
-        <v>317.1</v>
+        <v>310.4</v>
       </c>
       <c r="H46" t="n">
-        <v>70.8</v>
+        <v>15</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.34</v>
+        <v>-54.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-83.64</v>
+        <v>-32.76</v>
       </c>
       <c r="L46" t="n">
-        <v>99.73999999999999</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:09:46</t>
+          <t>07:01:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.98</v>
+        <v>2.7</v>
       </c>
       <c r="F47" t="n">
-        <v>13.45</v>
+        <v>9.19</v>
       </c>
       <c r="G47" t="n">
-        <v>309.7</v>
+        <v>294.5</v>
       </c>
       <c r="H47" t="n">
-        <v>66.2</v>
+        <v>45</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>-117.4</v>
+        <v>-5.91</v>
       </c>
       <c r="K47" t="n">
-        <v>70.93000000000001</v>
+        <v>-64.86</v>
       </c>
       <c r="L47" t="n">
-        <v>137.17</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:11:16</t>
+          <t>07:03:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.89</v>
+        <v>3.92</v>
       </c>
       <c r="F48" t="n">
-        <v>9.19</v>
+        <v>13.45</v>
       </c>
       <c r="G48" t="n">
-        <v>314.6</v>
+        <v>320.5</v>
       </c>
       <c r="H48" t="n">
-        <v>63.6</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-79.27</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-31.84</v>
+        <v>-95.3</v>
       </c>
       <c r="L48" t="n">
-        <v>85.42</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:13:32</t>
+          <t>07:04:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.07</v>
+        <v>3.64</v>
       </c>
       <c r="F49" t="n">
-        <v>12.96</v>
+        <v>12.07</v>
       </c>
       <c r="G49" t="n">
-        <v>304.9</v>
+        <v>316.7</v>
       </c>
       <c r="H49" t="n">
-        <v>69.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-21.46</v>
+        <v>-75.05</v>
       </c>
       <c r="K49" t="n">
-        <v>-170.41</v>
+        <v>44.96</v>
       </c>
       <c r="L49" t="n">
-        <v>171.76</v>
+        <v>87.48999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:16:42</t>
+          <t>07:10:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.14</v>
+        <v>3.51</v>
       </c>
       <c r="F50" t="n">
-        <v>6.22</v>
+        <v>9.51</v>
       </c>
       <c r="G50" t="n">
-        <v>310.2</v>
+        <v>306.3</v>
       </c>
       <c r="H50" t="n">
-        <v>70.3</v>
+        <v>48.8</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>49.8</v>
+        <v>-50.35</v>
       </c>
       <c r="K50" t="n">
-        <v>-144.58</v>
+        <v>-80.78</v>
       </c>
       <c r="L50" t="n">
-        <v>152.91</v>
+        <v>95.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:18:42</t>
+          <t>07:11:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.06</v>
+        <v>3.64</v>
       </c>
       <c r="F51" t="n">
-        <v>13.45</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>306.5</v>
+        <v>310.9</v>
       </c>
       <c r="H51" t="n">
-        <v>69.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>9.210000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="K51" t="n">
-        <v>180.25</v>
+        <v>111.08</v>
       </c>
       <c r="L51" t="n">
-        <v>180.48</v>
+        <v>112.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:20:40</t>
+          <t>07:13:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.73</v>
+        <v>3.36</v>
       </c>
       <c r="F52" t="n">
-        <v>10.36</v>
+        <v>13.16</v>
       </c>
       <c r="G52" t="n">
-        <v>305.8</v>
+        <v>314.1</v>
       </c>
       <c r="H52" t="n">
-        <v>70.2</v>
+        <v>57.8</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>102.01</v>
+        <v>-64.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-94.25</v>
+        <v>125</v>
       </c>
       <c r="L52" t="n">
-        <v>138.89</v>
+        <v>140.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:25:45</t>
+          <t>07:19:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="F53" t="n">
-        <v>10.2</v>
+        <v>13.45</v>
       </c>
       <c r="G53" t="n">
-        <v>321.7</v>
+        <v>301.6</v>
       </c>
       <c r="H53" t="n">
-        <v>70.3</v>
+        <v>61.6</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>136.27</v>
+        <v>119.9</v>
       </c>
       <c r="K53" t="n">
-        <v>-99.98</v>
+        <v>-163.38</v>
       </c>
       <c r="L53" t="n">
-        <v>169.02</v>
+        <v>202.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:27:22</t>
+          <t>07:21:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.46</v>
+        <v>4.17</v>
       </c>
       <c r="F54" t="n">
-        <v>10.61</v>
+        <v>13.45</v>
       </c>
       <c r="G54" t="n">
-        <v>304.7</v>
+        <v>308.1</v>
       </c>
       <c r="H54" t="n">
-        <v>69.5</v>
+        <v>48.8</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.96</v>
+        <v>-0.92</v>
       </c>
       <c r="K54" t="n">
-        <v>165.14</v>
+        <v>306.45</v>
       </c>
       <c r="L54" t="n">
-        <v>172.83</v>
+        <v>306.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:28:54</t>
+          <t>07:22:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.41</v>
+        <v>3.76</v>
       </c>
       <c r="F55" t="n">
-        <v>8.710000000000001</v>
+        <v>12.09</v>
       </c>
       <c r="G55" t="n">
-        <v>313.1</v>
+        <v>307.8</v>
       </c>
       <c r="H55" t="n">
-        <v>71.09999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-183.26</v>
+        <v>-65.75</v>
       </c>
       <c r="K55" t="n">
-        <v>-10.89</v>
+        <v>188.23</v>
       </c>
       <c r="L55" t="n">
-        <v>183.58</v>
+        <v>199.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:34:34</t>
+          <t>07:25:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.65</v>
+        <v>3.93</v>
       </c>
       <c r="F56" t="n">
-        <v>13.18</v>
+        <v>10.45</v>
       </c>
       <c r="G56" t="n">
-        <v>307.7</v>
+        <v>302.3</v>
       </c>
       <c r="H56" t="n">
-        <v>71.8</v>
+        <v>27.8</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J56" t="n">
-        <v>-386.96</v>
+        <v>-177.98</v>
       </c>
       <c r="K56" t="n">
-        <v>88.25</v>
+        <v>305.84</v>
       </c>
       <c r="L56" t="n">
-        <v>396.89</v>
+        <v>353.86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:36:53</t>
+          <t>07:27:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>13.45</v>
+        <v>10.04</v>
       </c>
       <c r="G57" t="n">
-        <v>304.9</v>
+        <v>331.9</v>
       </c>
       <c r="H57" t="n">
-        <v>64.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>286.32</v>
+        <v>160.28</v>
       </c>
       <c r="K57" t="n">
-        <v>189.3</v>
+        <v>-51.48</v>
       </c>
       <c r="L57" t="n">
-        <v>343.24</v>
+        <v>168.34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:38:41</t>
+          <t>07:28:49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.82</v>
+        <v>4.39</v>
       </c>
       <c r="F58" t="n">
-        <v>10.63</v>
+        <v>13.45</v>
       </c>
       <c r="G58" t="n">
-        <v>315.4</v>
+        <v>314</v>
       </c>
       <c r="H58" t="n">
-        <v>64.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-364.38</v>
+        <v>-321.08</v>
       </c>
       <c r="K58" t="n">
-        <v>-160.85</v>
+        <v>-185.3</v>
       </c>
       <c r="L58" t="n">
-        <v>398.3</v>
+        <v>370.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:47:22</t>
+          <t>07:42:03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.04</v>
+        <v>4.39</v>
       </c>
       <c r="F59" t="n">
         <v>13.45</v>
       </c>
       <c r="G59" t="n">
-        <v>309</v>
+        <v>308.3</v>
       </c>
       <c r="H59" t="n">
-        <v>69.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-62.58</v>
+        <v>29.56</v>
       </c>
       <c r="K59" t="n">
-        <v>64.84</v>
+        <v>93.89</v>
       </c>
       <c r="L59" t="n">
-        <v>90.12</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:48:19</t>
+          <t>07:42:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="F60" t="n">
-        <v>10.89</v>
+        <v>13.45</v>
       </c>
       <c r="G60" t="n">
-        <v>313.4</v>
+        <v>304.5</v>
       </c>
       <c r="H60" t="n">
-        <v>67.8</v>
+        <v>63.8</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-39.08</v>
+        <v>-20.03</v>
       </c>
       <c r="K60" t="n">
-        <v>55.83</v>
+        <v>66.27</v>
       </c>
       <c r="L60" t="n">
-        <v>68.15000000000001</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:50:11</t>
+          <t>07:44:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="F61" t="n">
-        <v>11.02</v>
+        <v>13.45</v>
       </c>
       <c r="G61" t="n">
-        <v>300.5</v>
+        <v>310.4</v>
       </c>
       <c r="H61" t="n">
-        <v>70.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-83.08</v>
+        <v>-101.11</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.71</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>85.39</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:56:45</t>
+          <t>07:48:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.85</v>
+        <v>4.13</v>
       </c>
       <c r="F62" t="n">
-        <v>9.119999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="G62" t="n">
-        <v>302.3</v>
+        <v>320.2</v>
       </c>
       <c r="H62" t="n">
-        <v>58.3</v>
+        <v>55.2</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>-121.07</v>
+        <v>143.73</v>
       </c>
       <c r="K62" t="n">
-        <v>66.62</v>
+        <v>-33.61</v>
       </c>
       <c r="L62" t="n">
-        <v>138.19</v>
+        <v>147.61</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:57:58</t>
+          <t>07:51:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="F63" t="n">
-        <v>10.46</v>
+        <v>12.02</v>
       </c>
       <c r="G63" t="n">
-        <v>309.7</v>
+        <v>316.1</v>
       </c>
       <c r="H63" t="n">
-        <v>65.09999999999999</v>
+        <v>34.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>-16.85</v>
+        <v>-59.87</v>
       </c>
       <c r="K63" t="n">
-        <v>102.88</v>
+        <v>56.67</v>
       </c>
       <c r="L63" t="n">
-        <v>104.25</v>
+        <v>82.44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:58:53</t>
+          <t>07:52:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="F64" t="n">
-        <v>13.45</v>
+        <v>8.73</v>
       </c>
       <c r="G64" t="n">
-        <v>311.9</v>
+        <v>325.6</v>
       </c>
       <c r="H64" t="n">
-        <v>71.90000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-89.39</v>
+        <v>3.52</v>
       </c>
       <c r="K64" t="n">
-        <v>-19.26</v>
+        <v>89.25</v>
       </c>
       <c r="L64" t="n">
-        <v>91.44</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:02:51</t>
+          <t>07:56:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.69</v>
+        <v>3.51</v>
       </c>
       <c r="F65" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="G65" t="n">
-        <v>312.1</v>
+        <v>318.6</v>
       </c>
       <c r="H65" t="n">
-        <v>63.7</v>
+        <v>38.9</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>117.21</v>
+        <v>53.98</v>
       </c>
       <c r="K65" t="n">
-        <v>98.08</v>
+        <v>101.75</v>
       </c>
       <c r="L65" t="n">
-        <v>152.83</v>
+        <v>115.18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:05:20</t>
+          <t>07:58:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.17</v>
+        <v>3.17</v>
       </c>
       <c r="F66" t="n">
-        <v>11.99</v>
+        <v>8.98</v>
       </c>
       <c r="G66" t="n">
-        <v>310.7</v>
+        <v>313.6</v>
       </c>
       <c r="H66" t="n">
-        <v>66.3</v>
+        <v>63</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>63.02</v>
+        <v>12.91</v>
       </c>
       <c r="K66" t="n">
-        <v>167.26</v>
+        <v>-119.8</v>
       </c>
       <c r="L66" t="n">
-        <v>178.74</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:06:54</t>
+          <t>07:59:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.06</v>
+        <v>4.01</v>
       </c>
       <c r="F67" t="n">
-        <v>4.54</v>
+        <v>13.45</v>
       </c>
       <c r="G67" t="n">
-        <v>325.4</v>
+        <v>331.4</v>
       </c>
       <c r="H67" t="n">
-        <v>67.3</v>
+        <v>89.7</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>95.2</v>
+        <v>-2.53</v>
       </c>
       <c r="K67" t="n">
-        <v>-92.81</v>
+        <v>-169.8</v>
       </c>
       <c r="L67" t="n">
-        <v>132.95</v>
+        <v>169.81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:12:24</t>
+          <t>08:03:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="F68" t="n">
-        <v>13.45</v>
+        <v>11.97</v>
       </c>
       <c r="G68" t="n">
-        <v>308.1</v>
+        <v>302.8</v>
       </c>
       <c r="H68" t="n">
-        <v>64.09999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-258.85</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>92.48999999999999</v>
+        <v>-167.29</v>
       </c>
       <c r="L68" t="n">
-        <v>274.88</v>
+        <v>190.46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:13:25</t>
+          <t>08:05:44</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="F69" t="n">
-        <v>10.13</v>
+        <v>12.4</v>
       </c>
       <c r="G69" t="n">
-        <v>308</v>
+        <v>308.8</v>
       </c>
       <c r="H69" t="n">
-        <v>67.40000000000001</v>
+        <v>40</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-261.01</v>
+        <v>-195.71</v>
       </c>
       <c r="K69" t="n">
-        <v>-52.45</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>266.23</v>
+        <v>213.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:15:30</t>
+          <t>08:07:34</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="F70" t="n">
-        <v>13.45</v>
+        <v>11.94</v>
       </c>
       <c r="G70" t="n">
-        <v>304.6</v>
+        <v>306</v>
       </c>
       <c r="H70" t="n">
-        <v>63.1</v>
+        <v>59.7</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-328.28</v>
+        <v>-206.72</v>
       </c>
       <c r="K70" t="n">
-        <v>-34.23</v>
+        <v>-74.31</v>
       </c>
       <c r="L70" t="n">
-        <v>330.06</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:21:07</t>
+          <t>08:12:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.91</v>
+        <v>2.95</v>
       </c>
       <c r="F71" t="n">
-        <v>13.45</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>314</v>
+        <v>312.5</v>
       </c>
       <c r="H71" t="n">
-        <v>59.2</v>
+        <v>57.3</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-34.12</v>
+        <v>-67.83</v>
       </c>
       <c r="K71" t="n">
-        <v>-423.24</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>424.61</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:23:50</t>
+          <t>08:13:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="F72" t="n">
-        <v>13.45</v>
+        <v>12.29</v>
       </c>
       <c r="G72" t="n">
-        <v>310.8</v>
+        <v>327.5</v>
       </c>
       <c r="H72" t="n">
-        <v>66.7</v>
+        <v>57.3</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>-184.58</v>
+        <v>-201.86</v>
       </c>
       <c r="K72" t="n">
-        <v>272.72</v>
+        <v>118.85</v>
       </c>
       <c r="L72" t="n">
-        <v>329.32</v>
+        <v>234.25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:25:30</t>
+          <t>08:15:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.47</v>
+        <v>3.17</v>
       </c>
       <c r="F73" t="n">
-        <v>8.609999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="G73" t="n">
-        <v>301.1</v>
+        <v>304.6</v>
       </c>
       <c r="H73" t="n">
-        <v>66.40000000000001</v>
+        <v>32.6</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-148.47</v>
+        <v>-195.84</v>
       </c>
       <c r="K73" t="n">
-        <v>-197.55</v>
+        <v>85.77</v>
       </c>
       <c r="L73" t="n">
-        <v>247.13</v>
+        <v>213.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:35:38</t>
+          <t>08:24:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="F74" t="n">
-        <v>10.72</v>
+        <v>9.98</v>
       </c>
       <c r="G74" t="n">
-        <v>304</v>
+        <v>312.9</v>
       </c>
       <c r="H74" t="n">
-        <v>71.3</v>
+        <v>66.3</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-29.2</v>
+        <v>-38.71</v>
       </c>
       <c r="K74" t="n">
-        <v>-109.53</v>
+        <v>24.99</v>
       </c>
       <c r="L74" t="n">
-        <v>113.35</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:37:44</t>
+          <t>08:25:44</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.42</v>
+        <v>3.79</v>
       </c>
       <c r="F75" t="n">
         <v>13.45</v>
       </c>
       <c r="G75" t="n">
-        <v>293.4</v>
+        <v>320.5</v>
       </c>
       <c r="H75" t="n">
-        <v>62</v>
+        <v>55.8</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-94.7</v>
+        <v>-9.43</v>
       </c>
       <c r="K75" t="n">
-        <v>91.09</v>
+        <v>46.46</v>
       </c>
       <c r="L75" t="n">
-        <v>131.39</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:39:00</t>
+          <t>08:28:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.97</v>
+        <v>4.18</v>
       </c>
       <c r="F76" t="n">
-        <v>12.46</v>
+        <v>11</v>
       </c>
       <c r="G76" t="n">
-        <v>305.2</v>
+        <v>301.7</v>
       </c>
       <c r="H76" t="n">
-        <v>76.7</v>
+        <v>79.8</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>57.78</v>
+        <v>-7.87</v>
       </c>
       <c r="K76" t="n">
-        <v>-69.84</v>
+        <v>115.81</v>
       </c>
       <c r="L76" t="n">
-        <v>90.64</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:42:24</t>
+          <t>08:33:31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="F77" t="n">
-        <v>12.81</v>
+        <v>13.45</v>
       </c>
       <c r="G77" t="n">
-        <v>296.5</v>
+        <v>310.3</v>
       </c>
       <c r="H77" t="n">
-        <v>75.8</v>
+        <v>41.5</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>-98.03</v>
+        <v>73.88</v>
       </c>
       <c r="K77" t="n">
-        <v>-83.59999999999999</v>
+        <v>80.05</v>
       </c>
       <c r="L77" t="n">
-        <v>128.84</v>
+        <v>108.93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:44:14</t>
+          <t>08:35:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="F78" t="n">
-        <v>9.99</v>
+        <v>11.69</v>
       </c>
       <c r="G78" t="n">
-        <v>322.4</v>
+        <v>309.2</v>
       </c>
       <c r="H78" t="n">
-        <v>58.2</v>
+        <v>73</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.72</v>
+        <v>-79.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-90.77</v>
+        <v>16.63</v>
       </c>
       <c r="L78" t="n">
-        <v>91.52</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:46:24</t>
+          <t>08:36:34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.25</v>
+        <v>5.03</v>
       </c>
       <c r="F79" t="n">
-        <v>13.25</v>
+        <v>13.45</v>
       </c>
       <c r="G79" t="n">
-        <v>308.1</v>
+        <v>305.1</v>
       </c>
       <c r="H79" t="n">
-        <v>69.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>5.03</v>
+        <v>28.18</v>
       </c>
       <c r="K79" t="n">
-        <v>95.98</v>
+        <v>-135.32</v>
       </c>
       <c r="L79" t="n">
-        <v>96.11</v>
+        <v>138.22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:49:46</t>
+          <t>08:41:36</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.88</v>
+        <v>4.02</v>
       </c>
       <c r="F80" t="n">
         <v>13.45</v>
       </c>
       <c r="G80" t="n">
-        <v>323.2</v>
+        <v>316.5</v>
       </c>
       <c r="H80" t="n">
-        <v>71.3</v>
+        <v>59</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>98.76000000000001</v>
+        <v>-122.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-155.53</v>
+        <v>-76.34</v>
       </c>
       <c r="L80" t="n">
-        <v>184.24</v>
+        <v>144.19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:51:12</t>
+          <t>08:43:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.18</v>
+        <v>3.84</v>
       </c>
       <c r="F81" t="n">
         <v>13.45</v>
       </c>
       <c r="G81" t="n">
-        <v>310.8</v>
+        <v>307.6</v>
       </c>
       <c r="H81" t="n">
-        <v>68.40000000000001</v>
+        <v>46.5</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>-88.15000000000001</v>
+        <v>-135.9</v>
       </c>
       <c r="K81" t="n">
-        <v>171.24</v>
+        <v>44.94</v>
       </c>
       <c r="L81" t="n">
-        <v>192.6</v>
+        <v>143.14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:53:01</t>
+          <t>08:45:33</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.79</v>
+        <v>3.27</v>
       </c>
       <c r="F82" t="n">
-        <v>13.45</v>
+        <v>12.43</v>
       </c>
       <c r="G82" t="n">
-        <v>311.5</v>
+        <v>305</v>
       </c>
       <c r="H82" t="n">
-        <v>71</v>
+        <v>40.1</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-165.52</v>
+        <v>-93.76000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-78.22</v>
+        <v>50.19</v>
       </c>
       <c r="L82" t="n">
-        <v>183.08</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:58:40</t>
+          <t>08:49:34</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="F83" t="n">
-        <v>13.45</v>
+        <v>12.52</v>
       </c>
       <c r="G83" t="n">
-        <v>316.8</v>
+        <v>318</v>
       </c>
       <c r="H83" t="n">
-        <v>72.8</v>
+        <v>61.6</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>-285.57</v>
+        <v>137.67</v>
       </c>
       <c r="K83" t="n">
-        <v>-76.98</v>
+        <v>144.59</v>
       </c>
       <c r="L83" t="n">
-        <v>295.76</v>
+        <v>199.65</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:00:18</t>
+          <t>08:51:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.36</v>
+        <v>4.03</v>
       </c>
       <c r="F84" t="n">
         <v>13.45</v>
       </c>
       <c r="G84" t="n">
-        <v>315.1</v>
+        <v>321.3</v>
       </c>
       <c r="H84" t="n">
-        <v>65.2</v>
+        <v>38.2</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J84" t="n">
-        <v>136.3</v>
+        <v>-158.53</v>
       </c>
       <c r="K84" t="n">
-        <v>-182.07</v>
+        <v>145.15</v>
       </c>
       <c r="L84" t="n">
-        <v>227.44</v>
+        <v>214.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:02:09</t>
+          <t>08:53:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.11</v>
+        <v>3.76</v>
       </c>
       <c r="F85" t="n">
-        <v>10.93</v>
+        <v>9.69</v>
       </c>
       <c r="G85" t="n">
-        <v>316.2</v>
+        <v>308.5</v>
       </c>
       <c r="H85" t="n">
-        <v>60.2</v>
+        <v>56.3</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J85" t="n">
-        <v>-74.3</v>
+        <v>-166.32</v>
       </c>
       <c r="K85" t="n">
-        <v>197.1</v>
+        <v>-192.67</v>
       </c>
       <c r="L85" t="n">
-        <v>210.64</v>
+        <v>254.53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:07:44</t>
+          <t>08:58:22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.3</v>
+        <v>4.02</v>
       </c>
       <c r="F86" t="n">
-        <v>10.54</v>
+        <v>13.45</v>
       </c>
       <c r="G86" t="n">
-        <v>324.7</v>
+        <v>319</v>
       </c>
       <c r="H86" t="n">
-        <v>63.1</v>
+        <v>69.7</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-74.70999999999999</v>
+        <v>-279.57</v>
       </c>
       <c r="K86" t="n">
-        <v>-261.63</v>
+        <v>-141.91</v>
       </c>
       <c r="L86" t="n">
-        <v>272.08</v>
+        <v>313.53</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:09:18</t>
+          <t>09:00:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.63</v>
+        <v>4.76</v>
       </c>
       <c r="F87" t="n">
         <v>13.45</v>
       </c>
       <c r="G87" t="n">
-        <v>316.2</v>
+        <v>316.7</v>
       </c>
       <c r="H87" t="n">
-        <v>69.90000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-295.13</v>
+        <v>-73.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-225.48</v>
+        <v>-394.71</v>
       </c>
       <c r="L87" t="n">
-        <v>371.41</v>
+        <v>401.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:10:25</t>
+          <t>09:02:37</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.36</v>
+        <v>3.85</v>
       </c>
       <c r="F88" t="n">
-        <v>13.45</v>
+        <v>13.15</v>
       </c>
       <c r="G88" t="n">
-        <v>313.3</v>
+        <v>301.1</v>
       </c>
       <c r="H88" t="n">
-        <v>68.5</v>
+        <v>36.9</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>178.28</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-216.43</v>
+        <v>-266.02</v>
       </c>
       <c r="L88" t="n">
-        <v>280.41</v>
+        <v>275.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="F14" t="n">
-        <v>4.06</v>
+        <v>7.99</v>
       </c>
       <c r="G14" t="n">
-        <v>316.1</v>
+        <v>318.9</v>
       </c>
       <c r="H14" t="n">
-        <v>58</v>
+        <v>24.9</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-58.13</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-36.19</v>
+        <v>34.54</v>
       </c>
       <c r="L14" t="n">
-        <v>68.47</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:29:12</t>
+          <t>05:27:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="F15" t="n">
-        <v>8.9</v>
+        <v>10.92</v>
       </c>
       <c r="G15" t="n">
-        <v>305.3</v>
+        <v>319.7</v>
       </c>
       <c r="H15" t="n">
-        <v>63.4</v>
+        <v>45.2</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-65.76000000000001</v>
+        <v>-44.28</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.16</v>
+        <v>29.22</v>
       </c>
       <c r="L15" t="n">
-        <v>66.27</v>
+        <v>53.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:31:09</t>
+          <t>05:28:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.02</v>
+        <v>2.56</v>
       </c>
       <c r="F16" t="n">
-        <v>11.59</v>
+        <v>9.83</v>
       </c>
       <c r="G16" t="n">
-        <v>325.4</v>
+        <v>317.3</v>
       </c>
       <c r="H16" t="n">
-        <v>62.7</v>
+        <v>58.9</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>15.75</v>
+        <v>45.37</v>
       </c>
       <c r="K16" t="n">
-        <v>-50.35</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>52.75</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:36:08</t>
+          <t>05:32:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.36</v>
+        <v>2.87</v>
       </c>
       <c r="F17" t="n">
-        <v>7.26</v>
+        <v>5.2</v>
       </c>
       <c r="G17" t="n">
-        <v>290.6</v>
+        <v>303.4</v>
       </c>
       <c r="H17" t="n">
-        <v>75</v>
+        <v>60.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>25.82</v>
+        <v>27.63</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.20999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="L17" t="n">
-        <v>90</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:37:23</t>
+          <t>05:34:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.26</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>310.4</v>
+        <v>312.7</v>
       </c>
       <c r="H18" t="n">
-        <v>32.2</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>16.82</v>
+        <v>67.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-90.53</v>
+        <v>-76.62</v>
       </c>
       <c r="L18" t="n">
-        <v>92.08</v>
+        <v>102.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:39:42</t>
+          <t>05:37:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="F19" t="n">
-        <v>9.640000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="G19" t="n">
-        <v>314.4</v>
+        <v>316.4</v>
       </c>
       <c r="H19" t="n">
-        <v>90.90000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>94.75</v>
+        <v>-32.43</v>
       </c>
       <c r="K19" t="n">
-        <v>37.13</v>
+        <v>-52.2</v>
       </c>
       <c r="L19" t="n">
-        <v>101.77</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:43:42</t>
+          <t>05:42:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.32</v>
+        <v>3.55</v>
       </c>
       <c r="F20" t="n">
-        <v>10.3</v>
+        <v>13.45</v>
       </c>
       <c r="G20" t="n">
-        <v>302.9</v>
+        <v>310.2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="I20" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>14.47</v>
       </c>
       <c r="K20" t="n">
-        <v>149.3</v>
+        <v>96.5</v>
       </c>
       <c r="L20" t="n">
-        <v>149.33</v>
+        <v>97.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:45:25</t>
+          <t>05:42:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.31</v>
+        <v>2.91</v>
       </c>
       <c r="F21" t="n">
-        <v>10.25</v>
+        <v>7.68</v>
       </c>
       <c r="G21" t="n">
-        <v>314.5</v>
+        <v>319.3</v>
       </c>
       <c r="H21" t="n">
-        <v>62.9</v>
+        <v>54.2</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>80.87</v>
+        <v>11.74</v>
       </c>
       <c r="K21" t="n">
-        <v>21.77</v>
+        <v>-89.08</v>
       </c>
       <c r="L21" t="n">
-        <v>83.75</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:47:43</t>
+          <t>05:45:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="F22" t="n">
-        <v>10.6</v>
+        <v>12.55</v>
       </c>
       <c r="G22" t="n">
-        <v>305.7</v>
+        <v>300</v>
       </c>
       <c r="H22" t="n">
-        <v>81.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-181.81</v>
+        <v>-50.85</v>
       </c>
       <c r="K22" t="n">
-        <v>35.54</v>
+        <v>-76.06</v>
       </c>
       <c r="L22" t="n">
-        <v>185.25</v>
+        <v>91.48999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:51:27</t>
+          <t>05:50:50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="F23" t="n">
-        <v>9.1</v>
+        <v>10.52</v>
       </c>
       <c r="G23" t="n">
-        <v>324.9</v>
+        <v>303.7</v>
       </c>
       <c r="H23" t="n">
-        <v>56</v>
+        <v>33.6</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-141.7</v>
+        <v>-162.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-71.76000000000001</v>
+        <v>97.69</v>
       </c>
       <c r="L23" t="n">
-        <v>158.83</v>
+        <v>189.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:53:40</t>
+          <t>05:52:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="F24" t="n">
-        <v>10.21</v>
+        <v>11.89</v>
       </c>
       <c r="G24" t="n">
-        <v>307.5</v>
+        <v>317.6</v>
       </c>
       <c r="H24" t="n">
-        <v>27.5</v>
+        <v>43</v>
       </c>
       <c r="I24" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>173.06</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>7.47</v>
+        <v>-123.64</v>
       </c>
       <c r="L24" t="n">
-        <v>173.22</v>
+        <v>155.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:56:02</t>
+          <t>05:54:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8</v>
+        <v>13.45</v>
       </c>
       <c r="G25" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H25" t="n">
-        <v>58.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-83.59999999999999</v>
+        <v>129.37</v>
       </c>
       <c r="K25" t="n">
-        <v>-69.59</v>
+        <v>128.13</v>
       </c>
       <c r="L25" t="n">
-        <v>108.77</v>
+        <v>182.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:59:39</t>
+          <t>05:59:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="F26" t="n">
-        <v>13.45</v>
+        <v>10.96</v>
       </c>
       <c r="G26" t="n">
-        <v>300.4</v>
+        <v>317.1</v>
       </c>
       <c r="H26" t="n">
-        <v>45.2</v>
+        <v>50.6</v>
       </c>
       <c r="I26" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-132.03</v>
+        <v>-189.12</v>
       </c>
       <c r="K26" t="n">
-        <v>174.73</v>
+        <v>-18.1</v>
       </c>
       <c r="L26" t="n">
-        <v>219</v>
+        <v>189.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:01:19</t>
+          <t>06:00:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="F27" t="n">
-        <v>9.470000000000001</v>
+        <v>10.91</v>
       </c>
       <c r="G27" t="n">
-        <v>313.5</v>
+        <v>309.4</v>
       </c>
       <c r="H27" t="n">
-        <v>58.9</v>
+        <v>69.8</v>
       </c>
       <c r="I27" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.51</v>
+        <v>-127.18</v>
       </c>
       <c r="K27" t="n">
-        <v>228.2</v>
+        <v>-91.59</v>
       </c>
       <c r="L27" t="n">
-        <v>228.36</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:03:30</t>
+          <t>06:02:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.85</v>
+        <v>2.92</v>
       </c>
       <c r="F28" t="n">
-        <v>12.4</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>311.3</v>
+        <v>318.9</v>
       </c>
       <c r="H28" t="n">
-        <v>35.6</v>
+        <v>72</v>
       </c>
       <c r="I28" t="n">
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-362.9</v>
+        <v>194.81</v>
       </c>
       <c r="K28" t="n">
-        <v>262.56</v>
+        <v>-47.94</v>
       </c>
       <c r="L28" t="n">
-        <v>447.93</v>
+        <v>200.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:13:05</t>
+          <t>06:10:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.63</v>
+        <v>4.02</v>
       </c>
       <c r="F29" t="n">
-        <v>12.49</v>
+        <v>12.45</v>
       </c>
       <c r="G29" t="n">
-        <v>310.8</v>
+        <v>320.8</v>
       </c>
       <c r="H29" t="n">
-        <v>53.1</v>
+        <v>10.5</v>
       </c>
       <c r="I29" t="n">
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>46.03</v>
+        <v>-15.05</v>
       </c>
       <c r="K29" t="n">
-        <v>71.04000000000001</v>
+        <v>-55.47</v>
       </c>
       <c r="L29" t="n">
-        <v>84.65000000000001</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:14:51</t>
+          <t>06:11:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="F30" t="n">
-        <v>10.07</v>
+        <v>11.72</v>
       </c>
       <c r="G30" t="n">
-        <v>315.2</v>
+        <v>305.5</v>
       </c>
       <c r="H30" t="n">
-        <v>62.6</v>
+        <v>46.2</v>
       </c>
       <c r="I30" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-26.28</v>
+        <v>-23.38</v>
       </c>
       <c r="K30" t="n">
-        <v>-42.44</v>
+        <v>-91.38</v>
       </c>
       <c r="L30" t="n">
-        <v>49.92</v>
+        <v>94.31999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:16:47</t>
+          <t>06:13:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="F31" t="n">
-        <v>11.44</v>
+        <v>13.45</v>
       </c>
       <c r="G31" t="n">
-        <v>315.3</v>
+        <v>300.7</v>
       </c>
       <c r="H31" t="n">
-        <v>58.9</v>
+        <v>42.4</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>42.19</v>
+        <v>-22.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-78.15000000000001</v>
+        <v>-46.31</v>
       </c>
       <c r="L31" t="n">
-        <v>88.8</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:20:32</t>
+          <t>06:17:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="F32" t="n">
-        <v>8.18</v>
+        <v>7.66</v>
       </c>
       <c r="G32" t="n">
-        <v>321</v>
+        <v>315.9</v>
       </c>
       <c r="H32" t="n">
-        <v>55.6</v>
+        <v>27.8</v>
       </c>
       <c r="I32" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-38.31</v>
+        <v>-65.09</v>
       </c>
       <c r="K32" t="n">
-        <v>86.95999999999999</v>
+        <v>-4.94</v>
       </c>
       <c r="L32" t="n">
-        <v>95.03</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:21:23</t>
+          <t>06:19:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="F33" t="n">
-        <v>7.98</v>
+        <v>9.68</v>
       </c>
       <c r="G33" t="n">
-        <v>309.1</v>
+        <v>304.7</v>
       </c>
       <c r="H33" t="n">
-        <v>57.8</v>
+        <v>39</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-82.7</v>
+        <v>22.21</v>
       </c>
       <c r="K33" t="n">
-        <v>42.4</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>92.94</v>
+        <v>86.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:24:05</t>
+          <t>06:20:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.75</v>
+        <v>3.61</v>
       </c>
       <c r="F34" t="n">
-        <v>11.98</v>
+        <v>11.01</v>
       </c>
       <c r="G34" t="n">
-        <v>314.8</v>
+        <v>300.6</v>
       </c>
       <c r="H34" t="n">
-        <v>42.2</v>
+        <v>24.5</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>14.68</v>
+        <v>29.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.73999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="L34" t="n">
-        <v>67.36</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:28:36</t>
+          <t>06:24:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.43</v>
+        <v>3.61</v>
       </c>
       <c r="F35" t="n">
-        <v>13.45</v>
+        <v>10.16</v>
       </c>
       <c r="G35" t="n">
-        <v>323.1</v>
+        <v>299.7</v>
       </c>
       <c r="H35" t="n">
-        <v>66.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-105.8</v>
+        <v>35.06</v>
       </c>
       <c r="K35" t="n">
-        <v>89.01000000000001</v>
+        <v>104.24</v>
       </c>
       <c r="L35" t="n">
-        <v>138.26</v>
+        <v>109.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:30:57</t>
+          <t>06:24:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="F36" t="n">
-        <v>12.74</v>
+        <v>6.28</v>
       </c>
       <c r="G36" t="n">
-        <v>304.1</v>
+        <v>307.1</v>
       </c>
       <c r="H36" t="n">
-        <v>50.9</v>
+        <v>32.6</v>
       </c>
       <c r="I36" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-66.52</v>
+        <v>49.98</v>
       </c>
       <c r="K36" t="n">
-        <v>-22.67</v>
+        <v>-63.52</v>
       </c>
       <c r="L36" t="n">
-        <v>70.28</v>
+        <v>80.81999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:32:41</t>
+          <t>06:26:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.39</v>
+        <v>3.97</v>
       </c>
       <c r="F37" t="n">
-        <v>9.66</v>
+        <v>13.38</v>
       </c>
       <c r="G37" t="n">
-        <v>320.9</v>
+        <v>299.8</v>
       </c>
       <c r="H37" t="n">
-        <v>32.1</v>
+        <v>71.3</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-126.26</v>
+        <v>-46.51</v>
       </c>
       <c r="K37" t="n">
-        <v>34.17</v>
+        <v>-83.40000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>130.8</v>
+        <v>95.48999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:36:13</t>
+          <t>06:30:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="F38" t="n">
-        <v>8.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>315.7</v>
+        <v>304.2</v>
       </c>
       <c r="H38" t="n">
-        <v>67.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>68.3</v>
+        <v>-209.68</v>
       </c>
       <c r="K38" t="n">
-        <v>-190.44</v>
+        <v>88.67</v>
       </c>
       <c r="L38" t="n">
-        <v>202.32</v>
+        <v>227.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:37:50</t>
+          <t>06:32:09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.18</v>
+        <v>3.99</v>
       </c>
       <c r="F39" t="n">
-        <v>13.41</v>
+        <v>10.62</v>
       </c>
       <c r="G39" t="n">
-        <v>328.5</v>
+        <v>315.1</v>
       </c>
       <c r="H39" t="n">
-        <v>37.8</v>
+        <v>60.2</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>174.77</v>
+        <v>-9</v>
       </c>
       <c r="K39" t="n">
-        <v>26.19</v>
+        <v>-250.61</v>
       </c>
       <c r="L39" t="n">
-        <v>176.72</v>
+        <v>250.77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:39:08</t>
+          <t>06:34:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.22</v>
+        <v>3.81</v>
       </c>
       <c r="F40" t="n">
-        <v>9.74</v>
+        <v>11.05</v>
       </c>
       <c r="G40" t="n">
-        <v>307.6</v>
+        <v>304.2</v>
       </c>
       <c r="H40" t="n">
-        <v>56.2</v>
+        <v>69.3</v>
       </c>
       <c r="I40" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-323.3</v>
+        <v>-71</v>
       </c>
       <c r="K40" t="n">
-        <v>-142.83</v>
+        <v>-181.37</v>
       </c>
       <c r="L40" t="n">
-        <v>353.44</v>
+        <v>194.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:44:02</t>
+          <t>06:38:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.76</v>
+        <v>3.93</v>
       </c>
       <c r="F41" t="n">
-        <v>12.22</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>324.7</v>
+        <v>319.3</v>
       </c>
       <c r="H41" t="n">
-        <v>59.9</v>
+        <v>69.5</v>
       </c>
       <c r="I41" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-110.24</v>
+        <v>-41.92</v>
       </c>
       <c r="K41" t="n">
-        <v>283.03</v>
+        <v>250.95</v>
       </c>
       <c r="L41" t="n">
-        <v>303.74</v>
+        <v>254.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:45:54</t>
+          <t>06:41:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.75</v>
+        <v>3.63</v>
       </c>
       <c r="F42" t="n">
-        <v>13.45</v>
+        <v>10.95</v>
       </c>
       <c r="G42" t="n">
-        <v>312.1</v>
+        <v>303.5</v>
       </c>
       <c r="H42" t="n">
-        <v>63.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-24.41</v>
+        <v>-191.65</v>
       </c>
       <c r="K42" t="n">
-        <v>-326.03</v>
+        <v>84.53</v>
       </c>
       <c r="L42" t="n">
-        <v>326.94</v>
+        <v>209.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:47:33</t>
+          <t>06:42:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="F43" t="n">
-        <v>9.93</v>
+        <v>10.01</v>
       </c>
       <c r="G43" t="n">
-        <v>316.6</v>
+        <v>304.8</v>
       </c>
       <c r="H43" t="n">
-        <v>65.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-231.35</v>
+        <v>-137.31</v>
       </c>
       <c r="K43" t="n">
-        <v>-158.12</v>
+        <v>217.98</v>
       </c>
       <c r="L43" t="n">
-        <v>280.22</v>
+        <v>257.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:55:56</t>
+          <t>06:52:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.36</v>
+        <v>4.26</v>
       </c>
       <c r="F44" t="n">
-        <v>10.89</v>
+        <v>13.1</v>
       </c>
       <c r="G44" t="n">
-        <v>306.9</v>
+        <v>294.6</v>
       </c>
       <c r="H44" t="n">
-        <v>50.8</v>
+        <v>62.3</v>
       </c>
       <c r="I44" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-58</v>
+        <v>-27.85</v>
       </c>
       <c r="K44" t="n">
-        <v>28.84</v>
+        <v>63.24</v>
       </c>
       <c r="L44" t="n">
-        <v>64.78</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:57:05</t>
+          <t>06:53:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
       <c r="F45" t="n">
-        <v>13.45</v>
+        <v>8.9</v>
       </c>
       <c r="G45" t="n">
-        <v>307.2</v>
+        <v>314.4</v>
       </c>
       <c r="H45" t="n">
-        <v>62.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-55.7</v>
+        <v>-46.73</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.51</v>
+        <v>44.15</v>
       </c>
       <c r="L45" t="n">
-        <v>67.15000000000001</v>
+        <v>64.29000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:58:00</t>
+          <t>06:54:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.36</v>
+        <v>3.65</v>
       </c>
       <c r="F46" t="n">
-        <v>11.19</v>
+        <v>10.27</v>
       </c>
       <c r="G46" t="n">
-        <v>310.4</v>
+        <v>309</v>
       </c>
       <c r="H46" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.86</v>
+        <v>-43.37</v>
       </c>
       <c r="K46" t="n">
-        <v>-32.76</v>
+        <v>36.34</v>
       </c>
       <c r="L46" t="n">
-        <v>63.9</v>
+        <v>56.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:01:52</t>
+          <t>06:58:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.7</v>
+        <v>3.96</v>
       </c>
       <c r="F47" t="n">
-        <v>9.19</v>
+        <v>13.45</v>
       </c>
       <c r="G47" t="n">
-        <v>294.5</v>
+        <v>307.4</v>
       </c>
       <c r="H47" t="n">
-        <v>45</v>
+        <v>57.1</v>
       </c>
       <c r="I47" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-5.91</v>
+        <v>63.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.86</v>
+        <v>50.23</v>
       </c>
       <c r="L47" t="n">
-        <v>65.12</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:03:27</t>
+          <t>07:01:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="F48" t="n">
-        <v>13.45</v>
+        <v>5.78</v>
       </c>
       <c r="G48" t="n">
-        <v>320.5</v>
+        <v>315.8</v>
       </c>
       <c r="H48" t="n">
-        <v>72.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>66.48999999999999</v>
+        <v>-84.39</v>
       </c>
       <c r="K48" t="n">
-        <v>-95.3</v>
+        <v>-17.77</v>
       </c>
       <c r="L48" t="n">
-        <v>116.2</v>
+        <v>86.23999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:04:33</t>
+          <t>07:03:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="F49" t="n">
-        <v>12.07</v>
+        <v>11.36</v>
       </c>
       <c r="G49" t="n">
-        <v>316.7</v>
+        <v>307.8</v>
       </c>
       <c r="H49" t="n">
-        <v>65.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-75.05</v>
+        <v>-64.47</v>
       </c>
       <c r="K49" t="n">
-        <v>44.96</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>87.48999999999999</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:10:16</t>
+          <t>07:09:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="F50" t="n">
-        <v>9.51</v>
+        <v>12.57</v>
       </c>
       <c r="G50" t="n">
-        <v>306.3</v>
+        <v>322.4</v>
       </c>
       <c r="H50" t="n">
-        <v>48.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-50.35</v>
+        <v>106.66</v>
       </c>
       <c r="K50" t="n">
-        <v>-80.78</v>
+        <v>-39.31</v>
       </c>
       <c r="L50" t="n">
-        <v>95.19</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:11:37</t>
+          <t>07:10:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="F51" t="n">
-        <v>8.369999999999999</v>
+        <v>7.59</v>
       </c>
       <c r="G51" t="n">
-        <v>310.9</v>
+        <v>302.6</v>
       </c>
       <c r="H51" t="n">
-        <v>67.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>19.9</v>
+        <v>40.97</v>
       </c>
       <c r="K51" t="n">
-        <v>111.08</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>112.85</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:13:59</t>
+          <t>07:11:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="F52" t="n">
-        <v>13.16</v>
+        <v>10.92</v>
       </c>
       <c r="G52" t="n">
-        <v>314.1</v>
+        <v>319.4</v>
       </c>
       <c r="H52" t="n">
-        <v>57.8</v>
+        <v>50.6</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-64.53</v>
+        <v>-27.36</v>
       </c>
       <c r="K52" t="n">
-        <v>125</v>
+        <v>-108.59</v>
       </c>
       <c r="L52" t="n">
-        <v>140.67</v>
+        <v>111.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:19:46</t>
+          <t>07:16:54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>13.45</v>
+        <v>11.65</v>
       </c>
       <c r="G53" t="n">
-        <v>301.6</v>
+        <v>297.5</v>
       </c>
       <c r="H53" t="n">
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>119.9</v>
+        <v>230.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-163.38</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>202.65</v>
+        <v>249.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:21:43</t>
+          <t>07:18:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="F54" t="n">
         <v>13.45</v>
       </c>
       <c r="G54" t="n">
-        <v>308.1</v>
+        <v>300.6</v>
       </c>
       <c r="H54" t="n">
-        <v>48.8</v>
+        <v>30.8</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.92</v>
+        <v>-218.24</v>
       </c>
       <c r="K54" t="n">
-        <v>306.45</v>
+        <v>28.72</v>
       </c>
       <c r="L54" t="n">
-        <v>306.45</v>
+        <v>220.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:22:24</t>
+          <t>07:19:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.76</v>
+        <v>3.39</v>
       </c>
       <c r="F55" t="n">
-        <v>12.09</v>
+        <v>12.51</v>
       </c>
       <c r="G55" t="n">
-        <v>307.8</v>
+        <v>319.6</v>
       </c>
       <c r="H55" t="n">
-        <v>35.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-65.75</v>
+        <v>2.76</v>
       </c>
       <c r="K55" t="n">
-        <v>188.23</v>
+        <v>191.04</v>
       </c>
       <c r="L55" t="n">
-        <v>199.39</v>
+        <v>191.06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:25:43</t>
+          <t>07:23:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.93</v>
+        <v>3.84</v>
       </c>
       <c r="F56" t="n">
-        <v>10.45</v>
+        <v>12.65</v>
       </c>
       <c r="G56" t="n">
-        <v>302.3</v>
+        <v>318.8</v>
       </c>
       <c r="H56" t="n">
-        <v>27.8</v>
+        <v>8.5</v>
       </c>
       <c r="I56" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-177.98</v>
+        <v>6.3</v>
       </c>
       <c r="K56" t="n">
-        <v>305.84</v>
+        <v>-246.27</v>
       </c>
       <c r="L56" t="n">
-        <v>353.86</v>
+        <v>246.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:27:35</t>
+          <t>07:25:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="F57" t="n">
-        <v>10.04</v>
+        <v>10.6</v>
       </c>
       <c r="G57" t="n">
-        <v>331.9</v>
+        <v>307</v>
       </c>
       <c r="H57" t="n">
-        <v>51.9</v>
+        <v>32.2</v>
       </c>
       <c r="I57" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>160.28</v>
+        <v>-150.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-51.48</v>
+        <v>-104.33</v>
       </c>
       <c r="L57" t="n">
-        <v>168.34</v>
+        <v>182.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:28:49</t>
+          <t>07:27:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.39</v>
+        <v>3.69</v>
       </c>
       <c r="F58" t="n">
-        <v>13.45</v>
+        <v>12.4</v>
       </c>
       <c r="G58" t="n">
-        <v>314</v>
+        <v>303.1</v>
       </c>
       <c r="H58" t="n">
-        <v>77</v>
+        <v>47.2</v>
       </c>
       <c r="I58" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-321.08</v>
+        <v>-224.71</v>
       </c>
       <c r="K58" t="n">
-        <v>-185.3</v>
+        <v>150.07</v>
       </c>
       <c r="L58" t="n">
-        <v>370.71</v>
+        <v>270.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:42:03</t>
+          <t>07:35:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.39</v>
+        <v>3.26</v>
       </c>
       <c r="F59" t="n">
-        <v>13.45</v>
+        <v>10.78</v>
       </c>
       <c r="G59" t="n">
-        <v>308.3</v>
+        <v>314.3</v>
       </c>
       <c r="H59" t="n">
-        <v>68.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>29.56</v>
+        <v>57.98</v>
       </c>
       <c r="K59" t="n">
-        <v>93.89</v>
+        <v>0.48</v>
       </c>
       <c r="L59" t="n">
-        <v>98.43000000000001</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:42:45</t>
+          <t>07:36:21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="F60" t="n">
-        <v>13.45</v>
+        <v>12.17</v>
       </c>
       <c r="G60" t="n">
-        <v>304.5</v>
+        <v>319.9</v>
       </c>
       <c r="H60" t="n">
-        <v>63.8</v>
+        <v>42.8</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-20.03</v>
+        <v>47.36</v>
       </c>
       <c r="K60" t="n">
-        <v>66.27</v>
+        <v>8.77</v>
       </c>
       <c r="L60" t="n">
-        <v>69.23</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:44:50</t>
+          <t>07:37:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.45</v>
+        <v>3.77</v>
       </c>
       <c r="F61" t="n">
-        <v>13.45</v>
+        <v>11.3</v>
       </c>
       <c r="G61" t="n">
-        <v>310.4</v>
+        <v>324.4</v>
       </c>
       <c r="H61" t="n">
-        <v>58.9</v>
+        <v>44.5</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-101.11</v>
+        <v>38.19</v>
       </c>
       <c r="K61" t="n">
-        <v>64.40000000000001</v>
+        <v>-32.32</v>
       </c>
       <c r="L61" t="n">
-        <v>119.88</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:48:56</t>
+          <t>07:42:23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="F62" t="n">
-        <v>10.94</v>
+        <v>10.45</v>
       </c>
       <c r="G62" t="n">
-        <v>320.2</v>
+        <v>321.6</v>
       </c>
       <c r="H62" t="n">
-        <v>55.2</v>
+        <v>61.7</v>
       </c>
       <c r="I62" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>143.73</v>
+        <v>66.37</v>
       </c>
       <c r="K62" t="n">
-        <v>-33.61</v>
+        <v>-55.31</v>
       </c>
       <c r="L62" t="n">
-        <v>147.61</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:51:27</t>
+          <t>07:43:07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="F63" t="n">
-        <v>12.02</v>
+        <v>12.03</v>
       </c>
       <c r="G63" t="n">
-        <v>316.1</v>
+        <v>311.4</v>
       </c>
       <c r="H63" t="n">
-        <v>34.3</v>
+        <v>61.9</v>
       </c>
       <c r="I63" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.87</v>
+        <v>43.1</v>
       </c>
       <c r="K63" t="n">
-        <v>56.67</v>
+        <v>65.2</v>
       </c>
       <c r="L63" t="n">
-        <v>82.44</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:52:02</t>
+          <t>07:44:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="F64" t="n">
-        <v>8.73</v>
+        <v>13.45</v>
       </c>
       <c r="G64" t="n">
-        <v>325.6</v>
+        <v>312.2</v>
       </c>
       <c r="H64" t="n">
-        <v>39.2</v>
+        <v>33.7</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>3.52</v>
+        <v>-103.66</v>
       </c>
       <c r="K64" t="n">
-        <v>89.25</v>
+        <v>-103.67</v>
       </c>
       <c r="L64" t="n">
-        <v>89.31999999999999</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:56:10</t>
+          <t>07:47:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.51</v>
+        <v>3.71</v>
       </c>
       <c r="F65" t="n">
-        <v>13</v>
+        <v>11.08</v>
       </c>
       <c r="G65" t="n">
-        <v>318.6</v>
+        <v>314.2</v>
       </c>
       <c r="H65" t="n">
-        <v>38.9</v>
+        <v>5.9</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>53.98</v>
+        <v>29.3</v>
       </c>
       <c r="K65" t="n">
-        <v>101.75</v>
+        <v>109.78</v>
       </c>
       <c r="L65" t="n">
-        <v>115.18</v>
+        <v>113.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:58:07</t>
+          <t>07:50:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.17</v>
+        <v>4.83</v>
       </c>
       <c r="F66" t="n">
-        <v>8.98</v>
+        <v>13.45</v>
       </c>
       <c r="G66" t="n">
-        <v>313.6</v>
+        <v>313.5</v>
       </c>
       <c r="H66" t="n">
-        <v>63</v>
+        <v>84.3</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>12.91</v>
+        <v>-103.17</v>
       </c>
       <c r="K66" t="n">
-        <v>-119.8</v>
+        <v>-73.62</v>
       </c>
       <c r="L66" t="n">
-        <v>120.5</v>
+        <v>126.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:59:23</t>
+          <t>07:52:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.01</v>
+        <v>3.35</v>
       </c>
       <c r="F67" t="n">
-        <v>13.45</v>
+        <v>10.77</v>
       </c>
       <c r="G67" t="n">
-        <v>331.4</v>
+        <v>307.4</v>
       </c>
       <c r="H67" t="n">
-        <v>89.7</v>
+        <v>62.2</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.53</v>
+        <v>-129.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-169.8</v>
+        <v>-60.91</v>
       </c>
       <c r="L67" t="n">
-        <v>169.81</v>
+        <v>143.49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:03:45</t>
+          <t>07:56:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="F68" t="n">
-        <v>11.97</v>
+        <v>11.06</v>
       </c>
       <c r="G68" t="n">
-        <v>302.8</v>
+        <v>302.3</v>
       </c>
       <c r="H68" t="n">
-        <v>27.2</v>
+        <v>58.6</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-91.04000000000001</v>
+        <v>155.54</v>
       </c>
       <c r="K68" t="n">
-        <v>-167.29</v>
+        <v>146.72</v>
       </c>
       <c r="L68" t="n">
-        <v>190.46</v>
+        <v>213.82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:05:44</t>
+          <t>07:57:40</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="F69" t="n">
-        <v>12.4</v>
+        <v>9.73</v>
       </c>
       <c r="G69" t="n">
-        <v>308.8</v>
+        <v>316.4</v>
       </c>
       <c r="H69" t="n">
-        <v>40</v>
+        <v>57.6</v>
       </c>
       <c r="I69" t="n">
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-195.71</v>
+        <v>-22.7</v>
       </c>
       <c r="K69" t="n">
-        <v>85.01000000000001</v>
+        <v>134.36</v>
       </c>
       <c r="L69" t="n">
-        <v>213.37</v>
+        <v>136.27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:07:34</t>
+          <t>07:59:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="F70" t="n">
-        <v>11.94</v>
+        <v>11.63</v>
       </c>
       <c r="G70" t="n">
-        <v>306</v>
+        <v>309.5</v>
       </c>
       <c r="H70" t="n">
-        <v>59.7</v>
+        <v>88.2</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-206.72</v>
+        <v>88.55</v>
       </c>
       <c r="K70" t="n">
-        <v>-74.31</v>
+        <v>-135</v>
       </c>
       <c r="L70" t="n">
-        <v>219.68</v>
+        <v>161.45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:12:19</t>
+          <t>08:04:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.95</v>
+        <v>4.17</v>
       </c>
       <c r="F71" t="n">
-        <v>9.710000000000001</v>
+        <v>13.45</v>
       </c>
       <c r="G71" t="n">
-        <v>312.5</v>
+        <v>308.5</v>
       </c>
       <c r="H71" t="n">
-        <v>57.3</v>
+        <v>43.3</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-67.83</v>
+        <v>-209.38</v>
       </c>
       <c r="K71" t="n">
-        <v>99.59999999999999</v>
+        <v>162.98</v>
       </c>
       <c r="L71" t="n">
-        <v>120.5</v>
+        <v>265.34</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:13:10</t>
+          <t>08:05:46</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.74</v>
+        <v>4.08</v>
       </c>
       <c r="F72" t="n">
-        <v>12.29</v>
+        <v>12.76</v>
       </c>
       <c r="G72" t="n">
-        <v>327.5</v>
+        <v>313.6</v>
       </c>
       <c r="H72" t="n">
-        <v>57.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-201.86</v>
+        <v>111.65</v>
       </c>
       <c r="K72" t="n">
-        <v>118.85</v>
+        <v>271.36</v>
       </c>
       <c r="L72" t="n">
-        <v>234.25</v>
+        <v>293.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:15:58</t>
+          <t>08:06:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.17</v>
+        <v>3.74</v>
       </c>
       <c r="F73" t="n">
-        <v>11.01</v>
+        <v>11.43</v>
       </c>
       <c r="G73" t="n">
-        <v>304.6</v>
+        <v>320.8</v>
       </c>
       <c r="H73" t="n">
-        <v>32.6</v>
+        <v>70.3</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-195.84</v>
+        <v>188.66</v>
       </c>
       <c r="K73" t="n">
-        <v>85.77</v>
+        <v>-171.61</v>
       </c>
       <c r="L73" t="n">
-        <v>213.8</v>
+        <v>255.03</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:24:16</t>
+          <t>08:17:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="F74" t="n">
-        <v>9.98</v>
+        <v>13.45</v>
       </c>
       <c r="G74" t="n">
-        <v>312.9</v>
+        <v>307.3</v>
       </c>
       <c r="H74" t="n">
-        <v>66.3</v>
+        <v>42.5</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-38.71</v>
+        <v>72.77</v>
       </c>
       <c r="K74" t="n">
-        <v>24.99</v>
+        <v>6.44</v>
       </c>
       <c r="L74" t="n">
-        <v>46.07</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:25:44</t>
+          <t>08:19:09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.79</v>
+        <v>4.11</v>
       </c>
       <c r="F75" t="n">
-        <v>13.45</v>
+        <v>12.65</v>
       </c>
       <c r="G75" t="n">
-        <v>320.5</v>
+        <v>311.5</v>
       </c>
       <c r="H75" t="n">
-        <v>55.8</v>
+        <v>47.8</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.43</v>
+        <v>-61.25</v>
       </c>
       <c r="K75" t="n">
-        <v>46.46</v>
+        <v>12.09</v>
       </c>
       <c r="L75" t="n">
-        <v>47.4</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:28:04</t>
+          <t>08:21:27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="F76" t="n">
-        <v>11</v>
+        <v>13.45</v>
       </c>
       <c r="G76" t="n">
-        <v>301.7</v>
+        <v>309.7</v>
       </c>
       <c r="H76" t="n">
-        <v>79.8</v>
+        <v>70.2</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.87</v>
+        <v>63.68</v>
       </c>
       <c r="K76" t="n">
-        <v>115.81</v>
+        <v>36.56</v>
       </c>
       <c r="L76" t="n">
-        <v>116.08</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:33:31</t>
+          <t>08:25:28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="F77" t="n">
-        <v>13.45</v>
+        <v>11.73</v>
       </c>
       <c r="G77" t="n">
-        <v>310.3</v>
+        <v>309.8</v>
       </c>
       <c r="H77" t="n">
-        <v>41.5</v>
+        <v>47</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>73.88</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>80.05</v>
+        <v>29.76</v>
       </c>
       <c r="L77" t="n">
-        <v>108.93</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:35:27</t>
+          <t>08:27:35</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="F78" t="n">
-        <v>11.69</v>
+        <v>12.98</v>
       </c>
       <c r="G78" t="n">
-        <v>309.2</v>
+        <v>320.8</v>
       </c>
       <c r="H78" t="n">
-        <v>73</v>
+        <v>11.3</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-79.23</v>
+        <v>61.8</v>
       </c>
       <c r="K78" t="n">
-        <v>16.63</v>
+        <v>41.22</v>
       </c>
       <c r="L78" t="n">
-        <v>80.95999999999999</v>
+        <v>74.29000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:36:34</t>
+          <t>08:30:09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.03</v>
+        <v>3.51</v>
       </c>
       <c r="F79" t="n">
-        <v>13.45</v>
+        <v>12.15</v>
       </c>
       <c r="G79" t="n">
-        <v>305.1</v>
+        <v>317.8</v>
       </c>
       <c r="H79" t="n">
-        <v>61.1</v>
+        <v>76.2</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>28.18</v>
+        <v>24.72</v>
       </c>
       <c r="K79" t="n">
-        <v>-135.32</v>
+        <v>87.38</v>
       </c>
       <c r="L79" t="n">
-        <v>138.22</v>
+        <v>90.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:41:36</t>
+          <t>08:35:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.02</v>
+        <v>3.41</v>
       </c>
       <c r="F80" t="n">
-        <v>13.45</v>
+        <v>10.37</v>
       </c>
       <c r="G80" t="n">
-        <v>316.5</v>
+        <v>313.3</v>
       </c>
       <c r="H80" t="n">
-        <v>59</v>
+        <v>61.2</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-122.33</v>
+        <v>-43.86</v>
       </c>
       <c r="K80" t="n">
-        <v>-76.34</v>
+        <v>-97.7</v>
       </c>
       <c r="L80" t="n">
-        <v>144.19</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:43:30</t>
+          <t>08:36:11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="F81" t="n">
-        <v>13.45</v>
+        <v>13.17</v>
       </c>
       <c r="G81" t="n">
-        <v>307.6</v>
+        <v>310.7</v>
       </c>
       <c r="H81" t="n">
-        <v>46.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-135.9</v>
+        <v>-43.56</v>
       </c>
       <c r="K81" t="n">
-        <v>44.94</v>
+        <v>-44.21</v>
       </c>
       <c r="L81" t="n">
-        <v>143.14</v>
+        <v>62.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:45:33</t>
+          <t>08:38:18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.27</v>
+        <v>3.94</v>
       </c>
       <c r="F82" t="n">
-        <v>12.43</v>
+        <v>10.03</v>
       </c>
       <c r="G82" t="n">
-        <v>305</v>
+        <v>315.7</v>
       </c>
       <c r="H82" t="n">
-        <v>40.1</v>
+        <v>41.9</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-93.76000000000001</v>
+        <v>-97.23999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>50.19</v>
+        <v>-56.77</v>
       </c>
       <c r="L82" t="n">
-        <v>106.35</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:49:34</t>
+          <t>08:43:05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="F83" t="n">
-        <v>12.52</v>
+        <v>12.49</v>
       </c>
       <c r="G83" t="n">
-        <v>318</v>
+        <v>310.4</v>
       </c>
       <c r="H83" t="n">
-        <v>61.6</v>
+        <v>80.5</v>
       </c>
       <c r="I83" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>137.67</v>
+        <v>215.88</v>
       </c>
       <c r="K83" t="n">
-        <v>144.59</v>
+        <v>-13.88</v>
       </c>
       <c r="L83" t="n">
-        <v>199.65</v>
+        <v>216.32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:51:22</t>
+          <t>08:44:02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="F84" t="n">
         <v>13.45</v>
       </c>
       <c r="G84" t="n">
-        <v>321.3</v>
+        <v>313.8</v>
       </c>
       <c r="H84" t="n">
-        <v>38.2</v>
+        <v>60.8</v>
       </c>
       <c r="I84" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-158.53</v>
+        <v>-99.56</v>
       </c>
       <c r="K84" t="n">
-        <v>145.15</v>
+        <v>-188.93</v>
       </c>
       <c r="L84" t="n">
-        <v>214.94</v>
+        <v>213.56</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:53:13</t>
+          <t>08:45:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.76</v>
+        <v>3.36</v>
       </c>
       <c r="F85" t="n">
-        <v>9.69</v>
+        <v>12.66</v>
       </c>
       <c r="G85" t="n">
-        <v>308.5</v>
+        <v>300.2</v>
       </c>
       <c r="H85" t="n">
-        <v>56.3</v>
+        <v>34.9</v>
       </c>
       <c r="I85" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-166.32</v>
+        <v>-98.84999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-192.67</v>
+        <v>136.44</v>
       </c>
       <c r="L85" t="n">
-        <v>254.53</v>
+        <v>168.48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:58:22</t>
+          <t>08:51:56</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.02</v>
+        <v>3.72</v>
       </c>
       <c r="F86" t="n">
         <v>13.45</v>
       </c>
       <c r="G86" t="n">
-        <v>319</v>
+        <v>324.6</v>
       </c>
       <c r="H86" t="n">
-        <v>69.7</v>
+        <v>23.8</v>
       </c>
       <c r="I86" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-279.57</v>
+        <v>-205.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-141.91</v>
+        <v>103.39</v>
       </c>
       <c r="L86" t="n">
-        <v>313.53</v>
+        <v>229.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:00:21</t>
+          <t>08:53:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.76</v>
+        <v>3.5</v>
       </c>
       <c r="F87" t="n">
-        <v>13.45</v>
+        <v>11.13</v>
       </c>
       <c r="G87" t="n">
-        <v>316.7</v>
+        <v>307.3</v>
       </c>
       <c r="H87" t="n">
-        <v>38.4</v>
+        <v>51.2</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-73.28</v>
+        <v>-174.98</v>
       </c>
       <c r="K87" t="n">
-        <v>-394.71</v>
+        <v>-97.78</v>
       </c>
       <c r="L87" t="n">
-        <v>401.46</v>
+        <v>200.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:02:37</t>
+          <t>08:54:20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.85</v>
+        <v>3.33</v>
       </c>
       <c r="F88" t="n">
-        <v>13.15</v>
+        <v>11.33</v>
       </c>
       <c r="G88" t="n">
-        <v>301.1</v>
+        <v>322.8</v>
       </c>
       <c r="H88" t="n">
-        <v>36.9</v>
+        <v>78</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>69.73999999999999</v>
+        <v>126.26</v>
       </c>
       <c r="K88" t="n">
-        <v>-266.02</v>
+        <v>174.58</v>
       </c>
       <c r="L88" t="n">
-        <v>275.01</v>
+        <v>215.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>28.2</v>
+        <v>31.13</v>
       </c>
       <c r="K14" t="n">
-        <v>46.34</v>
+        <v>51.14</v>
       </c>
       <c r="L14" t="n">
-        <v>54.25</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>27.29</v>
+        <v>29.05</v>
       </c>
       <c r="K15" t="n">
-        <v>-74.78</v>
+        <v>-79.62</v>
       </c>
       <c r="L15" t="n">
-        <v>79.59999999999999</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-47.86</v>
+        <v>-54.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.02</v>
+        <v>-28.45</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-69.37</v>
+        <v>-82.91</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L17" t="n">
-        <v>69.37</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>54.67</v>
+        <v>61.71</v>
       </c>
       <c r="K18" t="n">
-        <v>-59.89</v>
+        <v>-67.61</v>
       </c>
       <c r="L18" t="n">
-        <v>81.09</v>
+        <v>91.54000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.72</v>
+        <v>-40.35</v>
       </c>
       <c r="K19" t="n">
-        <v>71.7</v>
+        <v>83.33</v>
       </c>
       <c r="L19" t="n">
-        <v>79.66</v>
+        <v>92.59</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-113.34</v>
+        <v>-128.38</v>
       </c>
       <c r="K20" t="n">
-        <v>90.52</v>
+        <v>102.52</v>
       </c>
       <c r="L20" t="n">
-        <v>145.05</v>
+        <v>164.29</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>103.56</v>
+        <v>123.78</v>
       </c>
       <c r="K21" t="n">
-        <v>39.46</v>
+        <v>47.16</v>
       </c>
       <c r="L21" t="n">
-        <v>110.82</v>
+        <v>132.46</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>77.36</v>
+        <v>95.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-54.25</v>
+        <v>-67.04000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>94.48999999999999</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>118.57</v>
+        <v>154.44</v>
       </c>
       <c r="K23" t="n">
-        <v>-88.27</v>
+        <v>-114.98</v>
       </c>
       <c r="L23" t="n">
-        <v>147.82</v>
+        <v>192.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-128.81</v>
+        <v>-154.31</v>
       </c>
       <c r="K24" t="n">
-        <v>137.67</v>
+        <v>164.93</v>
       </c>
       <c r="L24" t="n">
-        <v>188.53</v>
+        <v>225.86</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>60.81</v>
+        <v>69.17</v>
       </c>
       <c r="K25" t="n">
-        <v>223.86</v>
+        <v>254.63</v>
       </c>
       <c r="L25" t="n">
-        <v>231.98</v>
+        <v>263.86</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>48.23</v>
+        <v>64.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-158.29</v>
+        <v>-211.14</v>
       </c>
       <c r="L26" t="n">
-        <v>165.48</v>
+        <v>220.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>76.97</v>
+        <v>94.16</v>
       </c>
       <c r="K27" t="n">
-        <v>-232.26</v>
+        <v>-284.12</v>
       </c>
       <c r="L27" t="n">
-        <v>244.68</v>
+        <v>299.32</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>306.64</v>
+        <v>378.81</v>
       </c>
       <c r="K28" t="n">
-        <v>40.8</v>
+        <v>50.4</v>
       </c>
       <c r="L28" t="n">
-        <v>309.34</v>
+        <v>382.14</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.529999999999999</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>83.97</v>
+        <v>91.37</v>
       </c>
       <c r="L29" t="n">
-        <v>84.41</v>
+        <v>91.84</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-75.81999999999999</v>
+        <v>-81.48</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.8</v>
+        <v>-44.92</v>
       </c>
       <c r="L30" t="n">
-        <v>86.58</v>
+        <v>93.04000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>60.04</v>
+        <v>65.58</v>
       </c>
       <c r="K31" t="n">
-        <v>53.71</v>
+        <v>58.67</v>
       </c>
       <c r="L31" t="n">
-        <v>80.56</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-10.47</v>
+        <v>-12.7</v>
       </c>
       <c r="K32" t="n">
-        <v>-61.01</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>61.9</v>
+        <v>75.12</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-64.86</v>
+        <v>-71.93000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>67.58</v>
+        <v>74.95</v>
       </c>
       <c r="L33" t="n">
-        <v>93.67</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>112.23</v>
+        <v>120.74</v>
       </c>
       <c r="K34" t="n">
-        <v>37.63</v>
+        <v>40.49</v>
       </c>
       <c r="L34" t="n">
-        <v>118.37</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-20.77</v>
+        <v>-23.38</v>
       </c>
       <c r="K35" t="n">
-        <v>-131.1</v>
+        <v>-147.57</v>
       </c>
       <c r="L35" t="n">
-        <v>132.74</v>
+        <v>149.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>125.12</v>
+        <v>141.56</v>
       </c>
       <c r="K36" t="n">
-        <v>-33.4</v>
+        <v>-37.79</v>
       </c>
       <c r="L36" t="n">
-        <v>129.5</v>
+        <v>146.51</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-145.6</v>
+        <v>-160.87</v>
       </c>
       <c r="K37" t="n">
-        <v>-152.35</v>
+        <v>-168.32</v>
       </c>
       <c r="L37" t="n">
-        <v>210.74</v>
+        <v>232.84</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>123.68</v>
+        <v>143.22</v>
       </c>
       <c r="K38" t="n">
-        <v>188.21</v>
+        <v>217.94</v>
       </c>
       <c r="L38" t="n">
-        <v>225.21</v>
+        <v>260.79</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>147.51</v>
+        <v>171.25</v>
       </c>
       <c r="K39" t="n">
-        <v>-121.81</v>
+        <v>-141.42</v>
       </c>
       <c r="L39" t="n">
-        <v>191.31</v>
+        <v>222.1</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-113.02</v>
+        <v>-143.57</v>
       </c>
       <c r="K40" t="n">
-        <v>-21.54</v>
+        <v>-27.36</v>
       </c>
       <c r="L40" t="n">
-        <v>115.05</v>
+        <v>146.15</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-124.22</v>
+        <v>-174.61</v>
       </c>
       <c r="K41" t="n">
-        <v>123.83</v>
+        <v>174.05</v>
       </c>
       <c r="L41" t="n">
-        <v>175.4</v>
+        <v>246.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>76.04000000000001</v>
+        <v>105.07</v>
       </c>
       <c r="K42" t="n">
-        <v>-176.82</v>
+        <v>-244.31</v>
       </c>
       <c r="L42" t="n">
-        <v>192.47</v>
+        <v>265.94</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-222.31</v>
+        <v>-288.86</v>
       </c>
       <c r="K43" t="n">
-        <v>-106.28</v>
+        <v>-138.1</v>
       </c>
       <c r="L43" t="n">
-        <v>246.4</v>
+        <v>320.18</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.41</v>
+        <v>-12.21</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.61</v>
+        <v>-78.81</v>
       </c>
       <c r="L44" t="n">
-        <v>74.48999999999999</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>90.09</v>
+        <v>91.37</v>
       </c>
       <c r="K45" t="n">
-        <v>-85.14</v>
+        <v>-86.34999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>123.96</v>
+        <v>125.72</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-40.03</v>
+        <v>-45.27</v>
       </c>
       <c r="K46" t="n">
-        <v>-64.27</v>
+        <v>-72.69</v>
       </c>
       <c r="L46" t="n">
-        <v>75.72</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-91.64</v>
+        <v>-98.73999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>54.77</v>
+        <v>59.01</v>
       </c>
       <c r="L47" t="n">
-        <v>106.76</v>
+        <v>115.03</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-54.78</v>
+        <v>-66.64</v>
       </c>
       <c r="K48" t="n">
-        <v>-28.03</v>
+        <v>-34.1</v>
       </c>
       <c r="L48" t="n">
-        <v>61.53</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.48</v>
+        <v>-14.04</v>
       </c>
       <c r="K49" t="n">
-        <v>-122.28</v>
+        <v>-127.36</v>
       </c>
       <c r="L49" t="n">
-        <v>123.02</v>
+        <v>128.13</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>50.8</v>
+        <v>56.79</v>
       </c>
       <c r="K50" t="n">
-        <v>-130.63</v>
+        <v>-146.01</v>
       </c>
       <c r="L50" t="n">
-        <v>140.16</v>
+        <v>156.67</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>15.76</v>
+        <v>18.14</v>
       </c>
       <c r="K51" t="n">
-        <v>129.2</v>
+        <v>148.67</v>
       </c>
       <c r="L51" t="n">
-        <v>130.15</v>
+        <v>149.77</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>84.12</v>
+        <v>104.02</v>
       </c>
       <c r="K52" t="n">
-        <v>-70.84999999999999</v>
+        <v>-87.62</v>
       </c>
       <c r="L52" t="n">
-        <v>109.98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>100.8</v>
+        <v>129.96</v>
       </c>
       <c r="K53" t="n">
-        <v>-92.76000000000001</v>
+        <v>-119.6</v>
       </c>
       <c r="L53" t="n">
-        <v>136.99</v>
+        <v>176.62</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>41.95</v>
+        <v>56.64</v>
       </c>
       <c r="K54" t="n">
-        <v>88.77</v>
+        <v>119.85</v>
       </c>
       <c r="L54" t="n">
-        <v>98.18000000000001</v>
+        <v>132.56</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-135.71</v>
+        <v>-174.03</v>
       </c>
       <c r="K55" t="n">
-        <v>-42.35</v>
+        <v>-54.31</v>
       </c>
       <c r="L55" t="n">
-        <v>142.17</v>
+        <v>182.31</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-282.91</v>
+        <v>-348.46</v>
       </c>
       <c r="K56" t="n">
-        <v>53.91</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>288</v>
+        <v>354.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>220.7</v>
+        <v>278.47</v>
       </c>
       <c r="K57" t="n">
-        <v>99</v>
+        <v>124.92</v>
       </c>
       <c r="L57" t="n">
-        <v>241.89</v>
+        <v>305.21</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-269.39</v>
+        <v>-326.26</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.13</v>
+        <v>-189.09</v>
       </c>
       <c r="L58" t="n">
-        <v>311.36</v>
+        <v>377.1</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.94</v>
+        <v>-49.91</v>
       </c>
       <c r="K59" t="n">
-        <v>45.16</v>
+        <v>52.49</v>
       </c>
       <c r="L59" t="n">
-        <v>62.31</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.54</v>
+        <v>-30.24</v>
       </c>
       <c r="K60" t="n">
-        <v>35.96</v>
+        <v>44.33</v>
       </c>
       <c r="L60" t="n">
-        <v>43.53</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-58.67</v>
+        <v>-68.5</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.77</v>
+        <v>-17.25</v>
       </c>
       <c r="L61" t="n">
-        <v>60.5</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-88.95</v>
+        <v>-93.38</v>
       </c>
       <c r="K62" t="n">
-        <v>48.49</v>
+        <v>50.9</v>
       </c>
       <c r="L62" t="n">
-        <v>101.31</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-10.11</v>
+        <v>-11.86</v>
       </c>
       <c r="K63" t="n">
-        <v>78.64</v>
+        <v>92.2</v>
       </c>
       <c r="L63" t="n">
-        <v>79.29000000000001</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-58.56</v>
+        <v>-73.88</v>
       </c>
       <c r="K64" t="n">
-        <v>-20.53</v>
+        <v>-25.9</v>
       </c>
       <c r="L64" t="n">
-        <v>62.06</v>
+        <v>78.29000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>94.59</v>
+        <v>114.92</v>
       </c>
       <c r="K65" t="n">
-        <v>56.1</v>
+        <v>68.16</v>
       </c>
       <c r="L65" t="n">
-        <v>109.98</v>
+        <v>133.61</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>60.01</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>113.23</v>
+        <v>135.1</v>
       </c>
       <c r="L66" t="n">
-        <v>128.15</v>
+        <v>152.9</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>79.36</v>
+        <v>91.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-82.62</v>
+        <v>-95.54000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>114.56</v>
+        <v>132.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-178.11</v>
+        <v>-214.9</v>
       </c>
       <c r="K68" t="n">
-        <v>52.55</v>
+        <v>63.4</v>
       </c>
       <c r="L68" t="n">
-        <v>185.7</v>
+        <v>224.06</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-193.69</v>
+        <v>-230.81</v>
       </c>
       <c r="K69" t="n">
-        <v>-63.04</v>
+        <v>-75.12</v>
       </c>
       <c r="L69" t="n">
-        <v>203.7</v>
+        <v>242.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-238.05</v>
+        <v>-275.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-43.6</v>
+        <v>-50.41</v>
       </c>
       <c r="L70" t="n">
-        <v>242.01</v>
+        <v>279.82</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.85</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-348.69</v>
+        <v>-420.23</v>
       </c>
       <c r="L71" t="n">
-        <v>348.78</v>
+        <v>420.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-110.96</v>
+        <v>-146.36</v>
       </c>
       <c r="K72" t="n">
-        <v>187.75</v>
+        <v>247.65</v>
       </c>
       <c r="L72" t="n">
-        <v>218.09</v>
+        <v>287.66</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-64.01000000000001</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-188.35</v>
+        <v>-250.34</v>
       </c>
       <c r="L73" t="n">
-        <v>198.93</v>
+        <v>264.4</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-23.09</v>
+        <v>-24.11</v>
       </c>
       <c r="K74" t="n">
-        <v>-90.84999999999999</v>
+        <v>-94.89</v>
       </c>
       <c r="L74" t="n">
-        <v>93.73999999999999</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-74.78</v>
+        <v>-78.53</v>
       </c>
       <c r="K75" t="n">
-        <v>72.68000000000001</v>
+        <v>76.33</v>
       </c>
       <c r="L75" t="n">
-        <v>104.28</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>41.51</v>
+        <v>47.26</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.25</v>
+        <v>-54.93</v>
       </c>
       <c r="L76" t="n">
-        <v>63.65</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-64.8</v>
+        <v>-72.06999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-58.22</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>87.12</v>
+        <v>96.88</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.57</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-79.05</v>
+        <v>-90.37</v>
       </c>
       <c r="L78" t="n">
-        <v>79.52</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>8.74</v>
+        <v>10.4</v>
       </c>
       <c r="K79" t="n">
-        <v>67.27</v>
+        <v>80.08</v>
       </c>
       <c r="L79" t="n">
-        <v>67.83</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>84.58</v>
+        <v>96.42</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.73</v>
+        <v>-151.29</v>
       </c>
       <c r="L80" t="n">
-        <v>157.39</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-58.37</v>
+        <v>-69.72</v>
       </c>
       <c r="K81" t="n">
-        <v>127.57</v>
+        <v>152.38</v>
       </c>
       <c r="L81" t="n">
-        <v>140.29</v>
+        <v>167.57</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-117.74</v>
+        <v>-138.04</v>
       </c>
       <c r="K82" t="n">
-        <v>-68.95999999999999</v>
+        <v>-80.84999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>136.45</v>
+        <v>159.98</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-199.42</v>
+        <v>-233.89</v>
       </c>
       <c r="K83" t="n">
-        <v>-79.31</v>
+        <v>-93.02</v>
       </c>
       <c r="L83" t="n">
-        <v>214.61</v>
+        <v>251.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>113.14</v>
+        <v>139.64</v>
       </c>
       <c r="K84" t="n">
-        <v>-148.97</v>
+        <v>-183.87</v>
       </c>
       <c r="L84" t="n">
-        <v>187.06</v>
+        <v>230.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-45.48</v>
+        <v>-56.17</v>
       </c>
       <c r="K85" t="n">
-        <v>141.49</v>
+        <v>174.75</v>
       </c>
       <c r="L85" t="n">
-        <v>148.62</v>
+        <v>183.56</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-28.69</v>
+        <v>-39.5</v>
       </c>
       <c r="K86" t="n">
-        <v>-222.77</v>
+        <v>-306.76</v>
       </c>
       <c r="L86" t="n">
-        <v>224.61</v>
+        <v>309.3</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-207.35</v>
+        <v>-253.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-201.64</v>
+        <v>-246.53</v>
       </c>
       <c r="L87" t="n">
-        <v>289.22</v>
+        <v>353.61</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>158.52</v>
+        <v>219.13</v>
       </c>
       <c r="K88" t="n">
-        <v>-182.37</v>
+        <v>-252.1</v>
       </c>
       <c r="L88" t="n">
-        <v>241.64</v>
+        <v>334.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-05.xlsx
+++ b/output/2025-08-05.xlsx
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-82.91</v>
+        <v>-87.58</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="L17" t="n">
-        <v>82.91</v>
+        <v>87.58</v>
       </c>
     </row>
     <row r="18">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-40.35</v>
+        <v>-42.88</v>
       </c>
       <c r="K19" t="n">
-        <v>83.33</v>
+        <v>88.53</v>
       </c>
       <c r="L19" t="n">
-        <v>92.59</v>
+        <v>98.37</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.289999999999999</v>
+        <v>-10.08</v>
       </c>
       <c r="K29" t="n">
-        <v>91.37</v>
+        <v>99.17</v>
       </c>
       <c r="L29" t="n">
-        <v>91.84</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-81.48</v>
+        <v>-86.41</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.92</v>
+        <v>-47.63</v>
       </c>
       <c r="L30" t="n">
-        <v>93.04000000000001</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>65.58</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>58.67</v>
+        <v>63.3</v>
       </c>
       <c r="L31" t="n">
-        <v>87.98999999999999</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-12.7</v>
+        <v>-12.92</v>
       </c>
       <c r="K32" t="n">
-        <v>-74.04000000000001</v>
+        <v>-75.33</v>
       </c>
       <c r="L32" t="n">
-        <v>75.12</v>
+        <v>76.43000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-71.93000000000001</v>
+        <v>-75.34</v>
       </c>
       <c r="K33" t="n">
-        <v>74.95</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>103.88</v>
+        <v>108.81</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>120.74</v>
+        <v>158.84</v>
       </c>
       <c r="K34" t="n">
-        <v>40.49</v>
+        <v>53.26</v>
       </c>
       <c r="L34" t="n">
-        <v>127.35</v>
+        <v>167.54</v>
       </c>
     </row>
     <row r="35">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>91.37</v>
+        <v>111.54</v>
       </c>
       <c r="K45" t="n">
-        <v>-86.34999999999999</v>
+        <v>-105.41</v>
       </c>
       <c r="L45" t="n">
-        <v>125.72</v>
+        <v>153.47</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-45.27</v>
+        <v>-54.03</v>
       </c>
       <c r="K46" t="n">
-        <v>-72.69</v>
+        <v>-86.76000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>85.63</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-98.73999999999999</v>
+        <v>-112.9</v>
       </c>
       <c r="K47" t="n">
-        <v>59.01</v>
+        <v>67.48</v>
       </c>
       <c r="L47" t="n">
-        <v>115.03</v>
+        <v>131.53</v>
       </c>
     </row>
     <row r="48">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.04</v>
+        <v>-14.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-127.36</v>
+        <v>-128.13</v>
       </c>
       <c r="L49" t="n">
-        <v>128.13</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-49.91</v>
+        <v>-60.68</v>
       </c>
       <c r="K59" t="n">
-        <v>52.49</v>
+        <v>63.81</v>
       </c>
       <c r="L59" t="n">
-        <v>72.43000000000001</v>
+        <v>88.05</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.24</v>
+        <v>-32.63</v>
       </c>
       <c r="K60" t="n">
-        <v>44.33</v>
+        <v>47.83</v>
       </c>
       <c r="L60" t="n">
-        <v>53.66</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-68.5</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.25</v>
+        <v>-20.17</v>
       </c>
       <c r="L61" t="n">
-        <v>70.64</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-11.86</v>
+        <v>-13.09</v>
       </c>
       <c r="K63" t="n">
-        <v>92.2</v>
+        <v>101.79</v>
       </c>
       <c r="L63" t="n">
-        <v>92.95999999999999</v>
+        <v>102.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-73.88</v>
+        <v>-81.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-25.9</v>
+        <v>-28.51</v>
       </c>
       <c r="L64" t="n">
-        <v>78.29000000000001</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-24.11</v>
+        <v>-29.68</v>
       </c>
       <c r="K74" t="n">
-        <v>-94.89</v>
+        <v>-116.78</v>
       </c>
       <c r="L74" t="n">
-        <v>97.91</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.53</v>
+        <v>-103.14</v>
       </c>
       <c r="K75" t="n">
-        <v>76.33</v>
+        <v>100.25</v>
       </c>
       <c r="L75" t="n">
-        <v>109.51</v>
+        <v>143.84</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>47.26</v>
+        <v>56.63</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.93</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>72.45999999999999</v>
+        <v>86.83</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-72.06999999999999</v>
+        <v>-75.59</v>
       </c>
       <c r="K77" t="n">
-        <v>-64.73999999999999</v>
+        <v>-67.91</v>
       </c>
       <c r="L77" t="n">
-        <v>96.88</v>
+        <v>101.62</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.789999999999999</v>
+        <v>-10.54</v>
       </c>
       <c r="K78" t="n">
-        <v>-90.37</v>
+        <v>-97.28</v>
       </c>
       <c r="L78" t="n">
-        <v>90.90000000000001</v>
+        <v>97.84999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="K79" t="n">
-        <v>80.08</v>
+        <v>95.47</v>
       </c>
       <c r="L79" t="n">
-        <v>80.75</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="80">
